--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Методика" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'План'!$A$7:$S$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'План'!$A$7:$T$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Сосиска в тесте (30шт гофра)</a:t>
+              <a:t>Пирожок с картофелем (30 шт гофра)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -532,7 +532,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Манты с говядиной (1порц)</a:t>
+              <a:t>Маффин шоколадный (24шт)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -633,7 +633,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Пирожок с картофелем (30 шт гофра)</a:t>
+              <a:t>Круассан миндальный (10 шт гофра)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -734,7 +734,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Бризоль с рисом (1порц)</a:t>
+              <a:t>Пирожок с капустой (30 шт гофра)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -835,7 +835,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Блины с ветчиной и сыром (3шт)</a:t>
+              <a:t>Манты с говядиной (1порц)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -936,7 +936,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Самса с говядиной (30 шт гофра)</a:t>
+              <a:t>Сочник творожный (30шт гофра )</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1037,7 +1037,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Самса с курицей (30шт гофра )</a:t>
+              <a:t>Бризоль с рисом (1порц)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1138,7 +1138,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Круассан с индейкой (1шт)</a:t>
+              <a:t>Блины с ветчиной и сыром (3шт)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1239,7 +1239,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Клаб Сэндвич с курицей (1шт)</a:t>
+              <a:t>Самса с говядиной (30 шт гофра)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1340,7 +1340,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Круассан миндальный (10 шт гофра)</a:t>
+              <a:t>Самса с курицей (30шт гофра )</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1542,7 +1542,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Шницель куриный с картофельным пюре (1порц)</a:t>
+              <a:t>Круассан с индейкой (1шт)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1845,7 +1845,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Кимпаб с тунцом (1шт)</a:t>
+              <a:t>Пирожок с курицей и сыром (30 шт гофра)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1946,7 +1946,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Кимпаб с курицей (1шт)</a:t>
+              <a:t>Кимпаб с тунцом (1шт)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2047,7 +2047,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Курица с сыром и картофельным пюре (1порц)</a:t>
+              <a:t>Кимпаб с курицей (1шт)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2148,7 +2148,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Курица с сыром с рисом и паутини (1порц)</a:t>
+              <a:t>Курица с сыром и картофельным пюре (1порц)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2249,7 +2249,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Пирожок с курицей и сыром (30 шт гофра)</a:t>
+              <a:t>Курица с сыром с рисом и паутини (1порц)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3071,7 +3071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S28"/>
+  <dimension ref="A1:T28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3093,6 +3093,7 @@
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="58" customWidth="1" min="19" max="19"/>
+    <col width="46" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3235,6 +3236,11 @@
           <t>Обоснование</t>
         </is>
       </c>
+      <c r="T7" s="7" t="inlineStr">
+        <is>
+          <t>Карточки в iiko</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
@@ -3253,31 +3259,31 @@
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>9312930</v>
+        <v>11467170</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1325</v>
+        <v>1627</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>7027</v>
+        <v>7047</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>-0.01462037666214644</v>
+        <v>-0.005144146725738707</v>
       </c>
       <c r="H8" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.516</v>
+        <v>0.5148728308728309</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>0.5152439024390243</v>
+        <v>0.6096274315858885</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="M8" s="10">
         <f>ROUND(F8*(1+L8),0)</f>
@@ -3305,7 +3311,12 @@
       </c>
       <c r="S8" s="14" t="inlineStr">
         <is>
-          <t>за 6 мес цена упала на 1.5% при ориентире 4.0%; берут на 52% больше</t>
+          <t>за 6 мес цена упала на 0.5% при ориентире 4.0%; берут на 61% больше</t>
+        </is>
+      </c>
+      <c r="T8" s="14" t="inlineStr">
+        <is>
+          <t>Упак Брецель-дог (20шт) · RP* Упак Брецель-дог (20шт)</t>
         </is>
       </c>
     </row>
@@ -3326,31 +3337,31 @@
         </is>
       </c>
       <c r="D9" s="16" t="n">
-        <v>6611799</v>
+        <v>10019546</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>705</v>
+        <v>1070</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>9374</v>
+        <v>9361</v>
       </c>
       <c r="G9" s="17" t="n">
-        <v>0.02604835660919047</v>
+        <v>0.01606738290323895</v>
       </c>
       <c r="H9" s="18" t="n">
         <v>8</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>0.598</v>
+        <v>0.5969796702365556</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>0.6202143950995407</v>
+        <v>0.402183406113537</v>
       </c>
       <c r="K9" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="M9" s="16">
         <f>ROUND(F9*(1+L9),0)</f>
@@ -3378,7 +3389,12 @@
       </c>
       <c r="S9" s="19" t="inlineStr">
         <is>
-          <t>за 8 мес цена выросла на 2.6% при ориентире 5.3%; берут на 62% больше</t>
+          <t>за 8 мес цена выросла на 1.6% при ориентире 5.3%; берут на 40% больше</t>
+        </is>
+      </c>
+      <c r="T9" s="19" t="inlineStr">
+        <is>
+          <t>RP* Упак Сосиска в тесте  готов СМ (30шт гофра) · Упак Сосиска в тесте  готов СМ (30шт гофра)</t>
         </is>
       </c>
     </row>
@@ -3454,6 +3470,11 @@
           <t>цену уже подняли на 9.9% — этого хватает</t>
         </is>
       </c>
+      <c r="T10" s="14" t="inlineStr">
+        <is>
+          <t>Упак Гуйру цомян (1порц)</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
@@ -3472,7 +3493,7 @@
         </is>
       </c>
       <c r="D11" s="16" t="n">
-        <v>5380972</v>
+        <v>5381606</v>
       </c>
       <c r="E11" s="16" t="n">
         <v>5162</v>
@@ -3490,7 +3511,7 @@
         <v>0.466</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>0.06047116833310517</v>
+        <v>0.05843357025697093</v>
       </c>
       <c r="K11" s="17" t="n">
         <v>0</v>
@@ -3527,49 +3548,54 @@
           <t>цену уже подняли на 14.4% — этого хватает</t>
         </is>
       </c>
+      <c r="T11" s="19" t="inlineStr">
+        <is>
+          <t>Упак Плов по-ташкентски (1порц) · RP* Упак Плов по-ташкентски (1порц)</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Кимпаб с тунцом (1шт)</t>
+          <t>Пирожок с курицей и сыром (30 шт гофра)</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Япония</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>— не трогать</t>
+          <t>Выпечка_</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>1 — сейчас</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>5104472</v>
+        <v>5160362</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>5379</v>
+        <v>980</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>949</v>
+        <v>5267</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.1144551028227871</v>
+        <v>0.004644817839810855</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>0.539</v>
+        <v>0.4990455257437672</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>0.2232582821620803</v>
+        <v>0.4364613880742911</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="M12" s="10">
         <f>ROUND(F12*(1+L12),0)</f>
@@ -3597,14 +3623,19 @@
       </c>
       <c r="S12" s="14" t="inlineStr">
         <is>
-          <t>цену уже подняли на 11.4% — этого хватает</t>
+          <t>за 8 мес цена выросла на 0.5% при ориентире 5.3%; берут на 44% больше</t>
+        </is>
+      </c>
+      <c r="T12" s="14" t="inlineStr">
+        <is>
+          <t>RP* Упак Пирожок с курицей и сыром готов СМ (30 шт гофра) · Упак Пирожок с курицей и сыром готов СМ (30 шт гофра)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>Кимпаб с курицей (1шт)</t>
+          <t>Кимпаб с тунцом (1шт)</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
@@ -3618,25 +3649,25 @@
         </is>
       </c>
       <c r="D13" s="16" t="n">
-        <v>4336019</v>
+        <v>5104472</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>5350</v>
+        <v>5379</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>810</v>
+        <v>949</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.09497220501137482</v>
+        <v>0.1144551028227871</v>
       </c>
       <c r="H13" s="18" t="n">
         <v>8</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>0.491</v>
+        <v>0.5389999999999999</v>
       </c>
       <c r="J13" s="17" t="n">
-        <v>0.1162887745166225</v>
+        <v>0.2232582821620803</v>
       </c>
       <c r="K13" s="17" t="n">
         <v>0</v>
@@ -3670,19 +3701,24 @@
       </c>
       <c r="S13" s="19" t="inlineStr">
         <is>
-          <t>цену уже подняли на 9.5% — этого хватает</t>
+          <t>цену уже подняли на 11.4% — этого хватает</t>
+        </is>
+      </c>
+      <c r="T13" s="19" t="inlineStr">
+        <is>
+          <t>Упак Кимпаб с тунцом (1шт)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Курица с сыром и картофельным пюре (1порц)</t>
+          <t>Кимпаб с курицей (1шт)</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Горячее</t>
+          <t>Япония</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -3691,25 +3727,25 @@
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>4293422</v>
+        <v>4336019</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>3814</v>
+        <v>5350</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>1126</v>
+        <v>810</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>0.07968634845642675</v>
+        <v>0.09497220501137482</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>0.5760000000000001</v>
+        <v>0.491</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>0.1776268395595348</v>
+        <v>0.1162887745166225</v>
       </c>
       <c r="K14" s="11" t="n">
         <v>0</v>
@@ -3743,14 +3779,19 @@
       </c>
       <c r="S14" s="14" t="inlineStr">
         <is>
-          <t>признаков отставания цены нет</t>
+          <t>цену уже подняли на 9.5% — этого хватает</t>
+        </is>
+      </c>
+      <c r="T14" s="14" t="inlineStr">
+        <is>
+          <t>Упак Кимпаб с курицей (1шт)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>Курица с сыром с рисом и паутини (1порц)</t>
+          <t>Курица с сыром и картофельным пюре (1порц)</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -3764,25 +3805,25 @@
         </is>
       </c>
       <c r="D15" s="16" t="n">
-        <v>3800654</v>
+        <v>4293422</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>3515</v>
+        <v>3814</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>1081</v>
+        <v>1126</v>
       </c>
       <c r="G15" s="17" t="n">
-        <v>0.07050092845465161</v>
+        <v>0.07968634845642675</v>
       </c>
       <c r="H15" s="18" t="n">
         <v>8</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>0.581</v>
+        <v>0.5760000000000001</v>
       </c>
       <c r="J15" s="17" t="n">
-        <v>0.1870989530563998</v>
+        <v>0.1776268395595348</v>
       </c>
       <c r="K15" s="17" t="n">
         <v>0</v>
@@ -3819,49 +3860,54 @@
           <t>признаков отставания цены нет</t>
         </is>
       </c>
+      <c r="T15" s="19" t="inlineStr">
+        <is>
+          <t>Упак Курица с сыром и картофельным пюре (1порц)</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Пирожок с курицей и сыром (30 шт гофра)</t>
+          <t>Курица с сыром с рисом и паутини (1порц)</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Выпечка_</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>2 — следом</t>
+          <t>Горячее</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>— не трогать</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>3632550</v>
+        <v>3800654</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>680</v>
+        <v>3515</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>5339</v>
+        <v>1081</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>0.008803340664356396</v>
+        <v>0.07050092845465161</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>0.51</v>
+        <v>0.581</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>0.4557774607703282</v>
+        <v>0.1870989530563998</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="M16" s="10">
         <f>ROUND(F16*(1+L16),0)</f>
@@ -3889,14 +3935,19 @@
       </c>
       <c r="S16" s="14" t="inlineStr">
         <is>
-          <t>за 8 мес цена выросла на 0.9% при ориентире 5.3%; берут на 46% больше</t>
+          <t>признаков отставания цены нет</t>
+        </is>
+      </c>
+      <c r="T16" s="14" t="inlineStr">
+        <is>
+          <t>Упак Курица с сыром с рисом и паутини (1порц)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>Сосиска в тесте (30шт гофра)</t>
+          <t>Пирожок с картофелем (30 шт гофра)</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -3910,31 +3961,31 @@
         </is>
       </c>
       <c r="D17" s="16" t="n">
-        <v>3407747</v>
+        <v>3780853</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>365</v>
+        <v>826</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>9336</v>
+        <v>4577</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>-0.001173885973586253</v>
+        <v>0.07254732484211801</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I17" s="17" t="n">
-        <v>0.595</v>
+        <v>0.6023283970574894</v>
       </c>
       <c r="J17" s="17" t="n">
-        <v>0.1128048780487805</v>
+        <v>0.7662152530292229</v>
       </c>
       <c r="K17" s="17" t="n">
-        <v>0.055</v>
+        <v>0.015</v>
       </c>
       <c r="L17" s="13" t="n">
-        <v>0.055</v>
+        <v>0.015</v>
       </c>
       <c r="M17" s="16">
         <f>ROUND(F17*(1+L17),0)</f>
@@ -3962,52 +4013,57 @@
       </c>
       <c r="S17" s="19" t="inlineStr">
         <is>
-          <t>за 8 мес цена упала на 0.1% при ориентире 5.3%</t>
+          <t>берут на 77% больше</t>
+        </is>
+      </c>
+      <c r="T17" s="19" t="inlineStr">
+        <is>
+          <t>RP* Упак Пирожок с картофелем готов СМ (30 шт гофра) · Упак Пирожок с картофелем готов СМ (30 шт гофра)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Манты с говядиной (1порц)</t>
+          <t>Маффин шоколадный (24шт)</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Горячее</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>— не трогать</t>
+          <t>Выпечка_</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>2 — следом</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>2986476</v>
+        <v>3539168</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>3451</v>
+        <v>482</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>865</v>
+        <v>7343</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.09012158410248471</v>
+        <v>-0.003665392881112228</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>0.419</v>
+        <v>0.4849398251284082</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>-0.004902431990771894</v>
+        <v>0.130570758405004</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="L18" s="13" t="n">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="M18" s="10">
         <f>ROUND(F18*(1+L18),0)</f>
@@ -4035,14 +4091,19 @@
       </c>
       <c r="S18" s="14" t="inlineStr">
         <is>
-          <t>цену уже подняли на 9.0% — этого хватает</t>
+          <t>за 8 мес цена упала на 0.4% при ориентире 5.3%</t>
+        </is>
+      </c>
+      <c r="T18" s="14" t="inlineStr">
+        <is>
+          <t>Упак Маффин шоколадный (24шт) · RP* Упак Маффин шоколадный (24шт)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>Пирожок с картофелем (30 шт гофра)</t>
+          <t>Круассан миндальный (10 шт гофра)</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
@@ -4050,37 +4111,37 @@
           <t>Выпечка_</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
-        <is>
-          <t>— не трогать</t>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>2 — следом</t>
         </is>
       </c>
       <c r="D19" s="16" t="n">
-        <v>2940381</v>
+        <v>3374756</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>612</v>
+        <v>477</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>4805</v>
+        <v>7070</v>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.08843677289461338</v>
+        <v>0.02718255545943404</v>
       </c>
       <c r="H19" s="18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>0.617</v>
+        <v>0.5856715825776243</v>
       </c>
       <c r="J19" s="17" t="n">
-        <v>0.5223880597014925</v>
+        <v>0.4262948207171313</v>
       </c>
       <c r="K19" s="17" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="M19" s="16">
         <f>ROUND(F19*(1+L19),0)</f>
@@ -4108,52 +4169,57 @@
       </c>
       <c r="S19" s="19" t="inlineStr">
         <is>
-          <t>цену уже подняли на 8.8% — этого хватает</t>
+          <t>за 8 мес цена выросла на 2.7% при ориентире 5.3%; берут на 43% больше</t>
+        </is>
+      </c>
+      <c r="T19" s="19" t="inlineStr">
+        <is>
+          <t>RP* Упак Круассан миндальный готов СМ (10 шт гофра) · Упак Круассан миндальный готов СМ (10 шт гофра)</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Бризоль с рисом (1порц)</t>
+          <t>Пирожок с капустой (30 шт гофра)</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Горячее</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>1 — сейчас</t>
+          <t>Выпечка_</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>2 — следом + 2-й шаг</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>2634834</v>
+        <v>3210495</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>2227</v>
+        <v>756</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1183</v>
+        <v>4249</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0.02382420203660618</v>
+        <v>-0.01425098681656201</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>0.366</v>
+        <v>0.6249372417648992</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>0.3294866693195387</v>
+        <v>0.6239255014326648</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>0.075</v>
+        <v>0.08</v>
       </c>
       <c r="L20" s="13" t="n">
-        <v>0.075</v>
+        <v>0.08</v>
       </c>
       <c r="M20" s="10">
         <f>ROUND(F20*(1+L20),0)</f>
@@ -4181,19 +4247,24 @@
       </c>
       <c r="S20" s="14" t="inlineStr">
         <is>
-          <t>за 8 мес цена выросла на 2.4% при ориентире 5.3%; маржа 37% — тоньше заводской; берут на 33% больше</t>
+          <t>за 8 мес цена упала на 1.4% при ориентире 5.3%; берут на 62% больше. Расчёт просит 8.5% — остальное вторым шагом через квартал</t>
+        </is>
+      </c>
+      <c r="T20" s="14" t="inlineStr">
+        <is>
+          <t>RP* Упак Пирожок с капустой  готов СМ (30 шт гофра) · Упак Пирожок с капустой  готов СМ (30 шт гофра)</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Блины с ветчиной и сыром (3шт)</t>
+          <t>Манты с говядиной (1порц)</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Завтраки</t>
+          <t>Горячее</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -4202,25 +4273,25 @@
         </is>
       </c>
       <c r="D21" s="16" t="n">
-        <v>2632114</v>
+        <v>2987025</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>2835</v>
+        <v>3451</v>
       </c>
       <c r="F21" s="16" t="n">
-        <v>928</v>
+        <v>865</v>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.07048326431697016</v>
+        <v>0.09012158410248471</v>
       </c>
       <c r="H21" s="18" t="n">
         <v>8</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>0.493</v>
+        <v>0.419</v>
       </c>
       <c r="J21" s="17" t="n">
-        <v>0.06698444555945815</v>
+        <v>-0.007476993865030646</v>
       </c>
       <c r="K21" s="17" t="n">
         <v>0</v>
@@ -4254,14 +4325,19 @@
       </c>
       <c r="S21" s="19" t="inlineStr">
         <is>
-          <t>признаков отставания цены нет</t>
+          <t>цену уже подняли на 9.0% — этого хватает</t>
+        </is>
+      </c>
+      <c r="T21" s="19" t="inlineStr">
+        <is>
+          <t>Упак Манты с говядиной (1порц) · RP* Упак Манты с говядиной (1порц)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Самса с говядиной (30 шт гофра)</t>
+          <t>Сочник творожный (30шт гофра )</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -4271,29 +4347,29 @@
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>2 — следом + 2-й шаг</t>
+          <t>2 — следом</t>
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>2627782</v>
+        <v>2815730</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>385</v>
+        <v>409</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>6831</v>
+        <v>6890</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.02818816478082753</v>
+        <v>-0.01415503666138584</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>0.4429999999999999</v>
+        <v>0.611</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>0.7379518072289157</v>
+        <v>0.5880829015544042</v>
       </c>
       <c r="K22" s="11" t="n">
         <v>0.08</v>
@@ -4327,52 +4403,57 @@
       </c>
       <c r="S22" s="14" t="inlineStr">
         <is>
-          <t>за 8 мес цена упала на 2.8% при ориентире 5.3%; маржа 44% — тоньше заводской; берут на 74% больше. Расчёт просит 12.5% — остальное вторым шагом через квартал</t>
+          <t>за 8 мес цена упала на 1.4% при ориентире 5.3%; берут на 59% больше</t>
+        </is>
+      </c>
+      <c r="T22" s="14" t="inlineStr">
+        <is>
+          <t>RP* Упак Сочник творожный готов СМ (30шт гофра ) · Упак Сочник творожный готов СМ (30шт гофра )</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>Самса с курицей (30шт гофра )</t>
+          <t>Бризоль с рисом (1порц)</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>Выпечка_</t>
+          <t>Горячее</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
         <is>
-          <t>2 — следом + 2-й шаг</t>
+          <t>2 — следом</t>
         </is>
       </c>
       <c r="D23" s="16" t="n">
-        <v>2612647</v>
+        <v>2634834</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>385</v>
+        <v>2227</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>6786</v>
+        <v>1183</v>
       </c>
       <c r="G23" s="17" t="n">
-        <v>-0.02307711041129701</v>
+        <v>0.02382420203660618</v>
       </c>
       <c r="H23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>0.613</v>
+        <v>0.366</v>
       </c>
       <c r="J23" s="17" t="n">
-        <v>0.6176470588235294</v>
+        <v>0.3294866693195387</v>
       </c>
       <c r="K23" s="17" t="n">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="M23" s="16">
         <f>ROUND(F23*(1+L23),0)</f>
@@ -4400,52 +4481,57 @@
       </c>
       <c r="S23" s="19" t="inlineStr">
         <is>
-          <t>за 8 мес цена упала на 2.3% при ориентире 5.3%; берут на 62% больше. Расчёт просит 9.0% — остальное вторым шагом через квартал</t>
+          <t>за 8 мес цена выросла на 2.4% при ориентире 5.3%; маржа 37% — тоньше заводской; берут на 33% больше</t>
+        </is>
+      </c>
+      <c r="T23" s="19" t="inlineStr">
+        <is>
+          <t>Упак Бризоль с рисом (1порц)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Круассан с индейкой (1шт)</t>
+          <t>Блины с ветчиной и сыром (3шт)</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>СЭНДВИЧИ</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>2 — следом</t>
+          <t>Завтраки</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>— не трогать</t>
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>2604922</v>
+        <v>2632371</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>4286</v>
+        <v>2836</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>608</v>
+        <v>928</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>0.03115280716362023</v>
+        <v>0.07048326431697016</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>0.609</v>
+        <v>0.493</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>0.3193104863533758</v>
+        <v>0.06297638385605397</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="L24" s="13" t="n">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="M24" s="10">
         <f>ROUND(F24*(1+L24),0)</f>
@@ -4473,52 +4559,57 @@
       </c>
       <c r="S24" s="14" t="inlineStr">
         <is>
-          <t>за 8 мес цена выросла на 3.1% при ориентире 5.3%; берут на 32% больше</t>
+          <t>признаков отставания цены нет</t>
+        </is>
+      </c>
+      <c r="T24" s="14" t="inlineStr">
+        <is>
+          <t>Упак Блины с ветчиной и сыром (3шт) · RP* Упак Блины с ветчиной и сыром (3шт)</t>
         </is>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>Клаб Сэндвич с курицей (1шт)</t>
+          <t>Самса с говядиной (30 шт гофра)</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>СЭНДВИЧИ</t>
-        </is>
-      </c>
-      <c r="C25" s="20" t="inlineStr">
-        <is>
-          <t>— не трогать</t>
+          <t>Выпечка_</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>2 — следом + 2-й шаг</t>
         </is>
       </c>
       <c r="D25" s="16" t="n">
-        <v>2584803</v>
+        <v>2627782</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>4985</v>
+        <v>385</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>519</v>
+        <v>6831</v>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.05485859903578372</v>
+        <v>-0.02818816478082753</v>
       </c>
       <c r="H25" s="18" t="n">
         <v>8</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.4429999999999999</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>0.1839917662892883</v>
+        <v>0.7379518072289157</v>
       </c>
       <c r="K25" s="17" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L25" s="13" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="M25" s="16">
         <f>ROUND(F25*(1+L25),0)</f>
@@ -4546,14 +4637,19 @@
       </c>
       <c r="S25" s="19" t="inlineStr">
         <is>
-          <t>признаков отставания цены нет</t>
+          <t>за 8 мес цена упала на 2.8% при ориентире 5.3%; маржа 44% — тоньше заводской; берут на 74% больше. Расчёт просит 12.5% — остальное вторым шагом через квартал</t>
+        </is>
+      </c>
+      <c r="T25" s="19" t="inlineStr">
+        <is>
+          <t>Упак Самса с говядиной готов ФЗ СМ (30 шт гофра)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Круассан миндальный (10 шт гофра)</t>
+          <t>Самса с курицей (30шт гофра )</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -4563,35 +4659,35 @@
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>2 — следом</t>
+          <t>2 — следом + 2-й шаг</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>2571717</v>
+        <v>2612647</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>7272</v>
+        <v>6786</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>-0.003755966336836836</v>
+        <v>-0.02307711041129701</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>0.594</v>
+        <v>0.613</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>0.4357239512855211</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="L26" s="13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="M26" s="10">
         <f>ROUND(F26*(1+L26),0)</f>
@@ -4619,19 +4715,24 @@
       </c>
       <c r="S26" s="14" t="inlineStr">
         <is>
-          <t>за 8 мес цена упала на 0.4% при ориентире 5.3%; берут на 44% больше</t>
+          <t>за 8 мес цена упала на 2.3% при ориентире 5.3%; берут на 62% больше. Расчёт просит 9.0% — остальное вторым шагом через квартал</t>
+        </is>
+      </c>
+      <c r="T26" s="14" t="inlineStr">
+        <is>
+          <t>Упак Самса с курицей готов ФЗ СМ (30шт гофра )</t>
         </is>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>Шницель куриный с картофельным пюре (1порц)</t>
+          <t>Круассан с индейкой (1шт)</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Горячее</t>
+          <t>СЭНДВИЧИ</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -4640,31 +4741,31 @@
         </is>
       </c>
       <c r="D27" s="16" t="n">
-        <v>2553371</v>
+        <v>2604922</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>2918</v>
+        <v>4286</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>875</v>
+        <v>608</v>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.04001774330608066</v>
+        <v>0.03115280716362023</v>
       </c>
       <c r="H27" s="18" t="n">
         <v>8</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>0.544</v>
+        <v>0.609</v>
       </c>
       <c r="J27" s="17" t="n">
-        <v>0.4051364365971108</v>
+        <v>0.3193104863533758</v>
       </c>
       <c r="K27" s="17" t="n">
-        <v>0.03</v>
+        <v>0.035</v>
       </c>
       <c r="L27" s="13" t="n">
-        <v>0.03</v>
+        <v>0.035</v>
       </c>
       <c r="M27" s="16">
         <f>ROUND(F27*(1+L27),0)</f>
@@ -4692,7 +4793,12 @@
       </c>
       <c r="S27" s="19" t="inlineStr">
         <is>
-          <t>за 8 мес цена выросла на 4.0% при ориентире 5.3%; берут на 41% больше</t>
+          <t>за 8 мес цена выросла на 3.1% при ориентире 5.3%; берут на 32% больше</t>
+        </is>
+      </c>
+      <c r="T27" s="19" t="inlineStr">
+        <is>
+          <t>Упак Круассан с индейкой (1шт)</t>
         </is>
       </c>
     </row>
@@ -4741,9 +4847,10 @@
         <f>"Прирост к нынешней валовой прибыли этих позиций: "&amp;TEXT(O28/SUMPRODUCT(D8:D27,I8:I27),"0.0%")</f>
         <v/>
       </c>
+      <c r="T28" s="24" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A7:S27"/>
+  <autoFilter ref="A7:T27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4847,34 +4954,34 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>11525</v>
+        <v>10296</v>
       </c>
       <c r="D5" s="30" t="n">
-        <v>9202</v>
+        <v>7263</v>
       </c>
       <c r="E5" s="30" t="n">
-        <v>7146</v>
+        <v>7107</v>
       </c>
       <c r="F5" s="30" t="n">
-        <v>7116</v>
+        <v>7102</v>
       </c>
       <c r="G5" s="30" t="n">
-        <v>7070</v>
+        <v>7077</v>
       </c>
       <c r="H5" s="30" t="n">
-        <v>7055</v>
+        <v>7066</v>
       </c>
       <c r="I5" s="30" t="n">
-        <v>7005</v>
+        <v>7123</v>
       </c>
       <c r="J5" s="30" t="n">
-        <v>7012</v>
+        <v>7010</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 52%</t>
+          <t>Выпечка_ · маржа 51%</t>
         </is>
       </c>
       <c r="B6" s="29" t="inlineStr">
@@ -4883,28 +4990,28 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>40</v>
+        <v>170</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>25</v>
+        <v>118</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>422</v>
+        <v>563</v>
       </c>
       <c r="F6" s="32" t="n">
-        <v>982</v>
+        <v>1101</v>
       </c>
       <c r="G6" s="32" t="n">
-        <v>1220</v>
+        <v>1369</v>
       </c>
       <c r="H6" s="32" t="n">
-        <v>1406</v>
+        <v>1646</v>
       </c>
       <c r="I6" s="32" t="n">
-        <v>322</v>
+        <v>780</v>
       </c>
       <c r="J6" s="32" t="n">
-        <v>2248</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="21">
@@ -4919,28 +5026,28 @@
         </is>
       </c>
       <c r="C21" s="30" t="n">
-        <v>8717</v>
+        <v>8795</v>
       </c>
       <c r="D21" s="30" t="n">
-        <v>9156</v>
+        <v>9210</v>
       </c>
       <c r="E21" s="30" t="n">
-        <v>9296</v>
+        <v>9434</v>
       </c>
       <c r="F21" s="30" t="n">
-        <v>9286</v>
+        <v>9473</v>
       </c>
       <c r="G21" s="30" t="n">
-        <v>9431</v>
+        <v>9406</v>
       </c>
       <c r="H21" s="30" t="n">
-        <v>9394</v>
+        <v>9349</v>
       </c>
       <c r="I21" s="30" t="n">
-        <v>9408</v>
+        <v>9358</v>
       </c>
       <c r="J21" s="30" t="n">
-        <v>9266</v>
+        <v>9377</v>
       </c>
     </row>
     <row r="22">
@@ -4955,28 +5062,28 @@
         </is>
       </c>
       <c r="C22" s="32" t="n">
-        <v>239</v>
+        <v>838</v>
       </c>
       <c r="D22" s="32" t="n">
-        <v>355</v>
+        <v>628</v>
       </c>
       <c r="E22" s="32" t="n">
-        <v>502</v>
+        <v>869</v>
       </c>
       <c r="F22" s="32" t="n">
-        <v>384</v>
+        <v>707</v>
       </c>
       <c r="G22" s="32" t="n">
-        <v>420</v>
+        <v>714</v>
       </c>
       <c r="H22" s="32" t="n">
-        <v>599</v>
+        <v>943</v>
       </c>
       <c r="I22" s="32" t="n">
-        <v>1065</v>
+        <v>1315</v>
       </c>
       <c r="J22" s="32" t="n">
-        <v>452</v>
+        <v>953</v>
       </c>
     </row>
     <row r="37">
@@ -5069,7 +5176,7 @@
         <v>930</v>
       </c>
       <c r="E53" s="30" t="n">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="F53" s="30" t="n">
         <v>924</v>
@@ -5105,16 +5212,16 @@
         <v>3002</v>
       </c>
       <c r="E54" s="32" t="n">
-        <v>4634</v>
+        <v>4640</v>
       </c>
       <c r="F54" s="32" t="n">
-        <v>4201</v>
+        <v>4216</v>
       </c>
       <c r="G54" s="32" t="n">
-        <v>5767</v>
+        <v>5776</v>
       </c>
       <c r="H54" s="32" t="n">
-        <v>5177</v>
+        <v>5179</v>
       </c>
       <c r="I54" s="32" t="n">
         <v>4921</v>
@@ -5126,7 +5233,7 @@
     <row r="69">
       <c r="A69" s="28" t="inlineStr">
         <is>
-          <t>Кимпаб с тунцом (1шт)</t>
+          <t>Пирожок с курицей и сыром (30 шт гофра)</t>
         </is>
       </c>
       <c r="B69" s="29" t="inlineStr">
@@ -5135,34 +5242,34 @@
         </is>
       </c>
       <c r="C69" s="30" t="n">
-        <v>855</v>
+        <v>4975</v>
       </c>
       <c r="D69" s="30" t="n">
-        <v>871</v>
+        <v>5256</v>
       </c>
       <c r="E69" s="30" t="n">
-        <v>875</v>
+        <v>5348</v>
       </c>
       <c r="F69" s="30" t="n">
-        <v>874</v>
+        <v>5270</v>
       </c>
       <c r="G69" s="30" t="n">
-        <v>879</v>
+        <v>5354</v>
       </c>
       <c r="H69" s="30" t="n">
-        <v>878</v>
+        <v>5220</v>
       </c>
       <c r="I69" s="30" t="n">
-        <v>970</v>
+        <v>5294</v>
       </c>
       <c r="J69" s="30" t="n">
-        <v>1002</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Япония · маржа 54%</t>
+          <t>Выпечка_ · маржа 50%</t>
         </is>
       </c>
       <c r="B70" s="29" t="inlineStr">
@@ -5171,34 +5278,34 @@
         </is>
       </c>
       <c r="C70" s="32" t="n">
-        <v>4068</v>
+        <v>711</v>
       </c>
       <c r="D70" s="32" t="n">
-        <v>4158</v>
+        <v>584</v>
       </c>
       <c r="E70" s="32" t="n">
-        <v>3935</v>
+        <v>791</v>
       </c>
       <c r="F70" s="32" t="n">
-        <v>4522</v>
+        <v>567</v>
       </c>
       <c r="G70" s="32" t="n">
-        <v>4734</v>
+        <v>688</v>
       </c>
       <c r="H70" s="32" t="n">
-        <v>5532</v>
+        <v>879</v>
       </c>
       <c r="I70" s="32" t="n">
-        <v>5257</v>
+        <v>1123</v>
       </c>
       <c r="J70" s="32" t="n">
-        <v>5347</v>
+        <v>937</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="28" t="inlineStr">
         <is>
-          <t>Кимпаб с курицей (1шт)</t>
+          <t>Кимпаб с тунцом (1шт)</t>
         </is>
       </c>
       <c r="B85" s="29" t="inlineStr">
@@ -5207,34 +5314,34 @@
         </is>
       </c>
       <c r="C85" s="30" t="n">
-        <v>737</v>
+        <v>855</v>
       </c>
       <c r="D85" s="30" t="n">
-        <v>751</v>
+        <v>871</v>
       </c>
       <c r="E85" s="30" t="n">
-        <v>765</v>
+        <v>875</v>
       </c>
       <c r="F85" s="30" t="n">
-        <v>774</v>
+        <v>874</v>
       </c>
       <c r="G85" s="30" t="n">
-        <v>781</v>
+        <v>879</v>
       </c>
       <c r="H85" s="30" t="n">
-        <v>760</v>
+        <v>878</v>
       </c>
       <c r="I85" s="30" t="n">
-        <v>822</v>
+        <v>970</v>
       </c>
       <c r="J85" s="30" t="n">
-        <v>853</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="31" t="inlineStr">
         <is>
-          <t>Япония · маржа 49%</t>
+          <t>Япония · маржа 54%</t>
         </is>
       </c>
       <c r="B86" s="29" t="inlineStr">
@@ -5243,34 +5350,34 @@
         </is>
       </c>
       <c r="C86" s="32" t="n">
-        <v>4157</v>
+        <v>4068</v>
       </c>
       <c r="D86" s="32" t="n">
-        <v>4351</v>
+        <v>4158</v>
       </c>
       <c r="E86" s="32" t="n">
-        <v>4206</v>
+        <v>3935</v>
       </c>
       <c r="F86" s="32" t="n">
-        <v>4969</v>
+        <v>4522</v>
       </c>
       <c r="G86" s="32" t="n">
-        <v>5203</v>
+        <v>4734</v>
       </c>
       <c r="H86" s="32" t="n">
-        <v>5595</v>
+        <v>5532</v>
       </c>
       <c r="I86" s="32" t="n">
-        <v>5188</v>
+        <v>5257</v>
       </c>
       <c r="J86" s="32" t="n">
-        <v>5267</v>
+        <v>5347</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="28" t="inlineStr">
         <is>
-          <t>Курица с сыром и картофельным пюре (1порц)</t>
+          <t>Кимпаб с курицей (1шт)</t>
         </is>
       </c>
       <c r="B101" s="29" t="inlineStr">
@@ -5279,34 +5386,34 @@
         </is>
       </c>
       <c r="C101" s="30" t="n">
-        <v>1027</v>
+        <v>737</v>
       </c>
       <c r="D101" s="30" t="n">
-        <v>1042</v>
+        <v>751</v>
       </c>
       <c r="E101" s="30" t="n">
-        <v>1075</v>
+        <v>765</v>
       </c>
       <c r="F101" s="30" t="n">
-        <v>1076</v>
+        <v>774</v>
       </c>
       <c r="G101" s="30" t="n">
-        <v>1135</v>
+        <v>781</v>
       </c>
       <c r="H101" s="30" t="n">
-        <v>1117</v>
+        <v>760</v>
       </c>
       <c r="I101" s="30" t="n">
-        <v>1125</v>
+        <v>822</v>
       </c>
       <c r="J101" s="30" t="n">
-        <v>1137</v>
+        <v>853</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 58%</t>
+          <t>Япония · маржа 49%</t>
         </is>
       </c>
       <c r="B102" s="29" t="inlineStr">
@@ -5315,34 +5422,34 @@
         </is>
       </c>
       <c r="C102" s="32" t="n">
-        <v>2525</v>
+        <v>4157</v>
       </c>
       <c r="D102" s="32" t="n">
-        <v>2315</v>
+        <v>4351</v>
       </c>
       <c r="E102" s="32" t="n">
-        <v>2676</v>
+        <v>4206</v>
       </c>
       <c r="F102" s="32" t="n">
-        <v>2774</v>
+        <v>4969</v>
       </c>
       <c r="G102" s="32" t="n">
-        <v>4267</v>
+        <v>5203</v>
       </c>
       <c r="H102" s="32" t="n">
-        <v>4300</v>
+        <v>5595</v>
       </c>
       <c r="I102" s="32" t="n">
-        <v>3609</v>
+        <v>5188</v>
       </c>
       <c r="J102" s="32" t="n">
-        <v>3534</v>
+        <v>5267</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="28" t="inlineStr">
         <is>
-          <t>Курица с сыром с рисом и паутини (1порц)</t>
+          <t>Курица с сыром и картофельным пюре (1порц)</t>
         </is>
       </c>
       <c r="B117" s="29" t="inlineStr">
@@ -5351,28 +5458,28 @@
         </is>
       </c>
       <c r="C117" s="30" t="n">
-        <v>1003</v>
+        <v>1027</v>
       </c>
       <c r="D117" s="30" t="n">
-        <v>1020</v>
+        <v>1042</v>
       </c>
       <c r="E117" s="30" t="n">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="F117" s="30" t="n">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="G117" s="30" t="n">
-        <v>1064</v>
+        <v>1135</v>
       </c>
       <c r="H117" s="30" t="n">
-        <v>1043</v>
+        <v>1117</v>
       </c>
       <c r="I117" s="30" t="n">
-        <v>1092</v>
+        <v>1125</v>
       </c>
       <c r="J117" s="30" t="n">
-        <v>1115</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="118">
@@ -5387,34 +5494,34 @@
         </is>
       </c>
       <c r="C118" s="32" t="n">
-        <v>2254</v>
+        <v>2525</v>
       </c>
       <c r="D118" s="32" t="n">
-        <v>2108</v>
+        <v>2315</v>
       </c>
       <c r="E118" s="32" t="n">
-        <v>2608</v>
+        <v>2676</v>
       </c>
       <c r="F118" s="32" t="n">
-        <v>3048</v>
+        <v>2774</v>
       </c>
       <c r="G118" s="32" t="n">
-        <v>3227</v>
+        <v>4267</v>
       </c>
       <c r="H118" s="32" t="n">
-        <v>3859</v>
+        <v>4300</v>
       </c>
       <c r="I118" s="32" t="n">
-        <v>3501</v>
+        <v>3609</v>
       </c>
       <c r="J118" s="32" t="n">
-        <v>3185</v>
+        <v>3534</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="28" t="inlineStr">
         <is>
-          <t>Пирожок с курицей и сыром (30 шт гофра)</t>
+          <t>Курица с сыром с рисом и паутини (1порц)</t>
         </is>
       </c>
       <c r="B133" s="29" t="inlineStr">
@@ -5423,34 +5530,34 @@
         </is>
       </c>
       <c r="C133" s="30" t="n">
-        <v>5062</v>
+        <v>1003</v>
       </c>
       <c r="D133" s="30" t="n">
-        <v>5294</v>
+        <v>1020</v>
       </c>
       <c r="E133" s="30" t="n">
-        <v>5344</v>
+        <v>1071</v>
       </c>
       <c r="F133" s="30" t="n">
-        <v>5332</v>
+        <v>1074</v>
       </c>
       <c r="G133" s="30" t="n">
-        <v>5399</v>
+        <v>1064</v>
       </c>
       <c r="H133" s="30" t="n">
-        <v>5341</v>
+        <v>1043</v>
       </c>
       <c r="I133" s="30" t="n">
-        <v>5374</v>
+        <v>1092</v>
       </c>
       <c r="J133" s="30" t="n">
-        <v>5271</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 51%</t>
+          <t>Горячее · маржа 58%</t>
         </is>
       </c>
       <c r="B134" s="29" t="inlineStr">
@@ -5459,34 +5566,34 @@
         </is>
       </c>
       <c r="C134" s="32" t="n">
-        <v>228</v>
+        <v>2254</v>
       </c>
       <c r="D134" s="32" t="n">
-        <v>405</v>
+        <v>2108</v>
       </c>
       <c r="E134" s="32" t="n">
-        <v>547</v>
+        <v>2608</v>
       </c>
       <c r="F134" s="32" t="n">
-        <v>377</v>
+        <v>3048</v>
       </c>
       <c r="G134" s="32" t="n">
-        <v>478</v>
+        <v>3227</v>
       </c>
       <c r="H134" s="32" t="n">
-        <v>618</v>
+        <v>3859</v>
       </c>
       <c r="I134" s="32" t="n">
-        <v>937</v>
+        <v>3501</v>
       </c>
       <c r="J134" s="32" t="n">
-        <v>486</v>
+        <v>3185</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="28" t="inlineStr">
         <is>
-          <t>Сосиска в тесте (30шт гофра)</t>
+          <t>Пирожок с картофелем (30 шт гофра)</t>
         </is>
       </c>
       <c r="B149" s="29" t="inlineStr">
@@ -5495,28 +5602,28 @@
         </is>
       </c>
       <c r="C149" s="30" t="n">
-        <v>8827</v>
+        <v>5445</v>
       </c>
       <c r="D149" s="30" t="n">
-        <v>9282</v>
+        <v>872</v>
       </c>
       <c r="E149" s="30" t="n">
-        <v>9623</v>
+        <v>4427</v>
       </c>
       <c r="F149" s="30" t="n">
-        <v>9696</v>
+        <v>4820</v>
       </c>
       <c r="G149" s="30" t="n">
-        <v>9369</v>
+        <v>4804</v>
       </c>
       <c r="H149" s="30" t="n">
-        <v>9271</v>
+        <v>4116</v>
       </c>
       <c r="I149" s="30" t="n">
-        <v>9146</v>
+        <v>4801</v>
       </c>
       <c r="J149" s="30" t="n">
-        <v>9477</v>
+        <v>4748</v>
       </c>
     </row>
     <row r="150">
@@ -5531,34 +5638,34 @@
         </is>
       </c>
       <c r="C150" s="32" t="n">
-        <v>599</v>
+        <v>60</v>
       </c>
       <c r="D150" s="32" t="n">
-        <v>273</v>
+        <v>182</v>
       </c>
       <c r="E150" s="32" t="n">
-        <v>367</v>
+        <v>550</v>
       </c>
       <c r="F150" s="32" t="n">
-        <v>323</v>
+        <v>402</v>
       </c>
       <c r="G150" s="32" t="n">
-        <v>294</v>
+        <v>451</v>
       </c>
       <c r="H150" s="32" t="n">
-        <v>344</v>
+        <v>751</v>
       </c>
       <c r="I150" s="32" t="n">
-        <v>250</v>
+        <v>971</v>
       </c>
       <c r="J150" s="32" t="n">
-        <v>501</v>
+        <v>756</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="28" t="inlineStr">
         <is>
-          <t>Манты с говядиной (1порц)</t>
+          <t>Маффин шоколадный (24шт)</t>
         </is>
       </c>
       <c r="B165" s="29" t="inlineStr">
@@ -5567,34 +5674,34 @@
         </is>
       </c>
       <c r="C165" s="30" t="n">
-        <v>831</v>
+        <v>7362</v>
       </c>
       <c r="D165" s="30" t="n">
-        <v>801</v>
+        <v>7317</v>
       </c>
       <c r="E165" s="30" t="n">
-        <v>791</v>
+        <v>7431</v>
       </c>
       <c r="F165" s="30" t="n">
-        <v>795</v>
+        <v>7492</v>
       </c>
       <c r="G165" s="30" t="n">
-        <v>848</v>
+        <v>7496</v>
       </c>
       <c r="H165" s="30" t="n">
-        <v>790</v>
+        <v>7329</v>
       </c>
       <c r="I165" s="30" t="n">
-        <v>873</v>
+        <v>7335</v>
       </c>
       <c r="J165" s="30" t="n">
-        <v>939</v>
+        <v>7358</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 42%</t>
+          <t>Выпечка_ · маржа 48%</t>
         </is>
       </c>
       <c r="B166" s="29" t="inlineStr">
@@ -5603,34 +5710,34 @@
         </is>
       </c>
       <c r="C166" s="32" t="n">
-        <v>3204</v>
+        <v>293</v>
       </c>
       <c r="D166" s="32" t="n">
-        <v>3017</v>
+        <v>324</v>
       </c>
       <c r="E166" s="32" t="n">
-        <v>3920</v>
+        <v>387</v>
       </c>
       <c r="F166" s="32" t="n">
-        <v>3319</v>
+        <v>523</v>
       </c>
       <c r="G166" s="32" t="n">
-        <v>3164</v>
+        <v>369</v>
       </c>
       <c r="H166" s="32" t="n">
-        <v>3665</v>
+        <v>392</v>
       </c>
       <c r="I166" s="32" t="n">
-        <v>3234</v>
+        <v>456</v>
       </c>
       <c r="J166" s="32" t="n">
-        <v>3453</v>
+        <v>598</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="28" t="inlineStr">
         <is>
-          <t>Пирожок с картофелем (30 шт гофра)</t>
+          <t>Круассан миндальный (10 шт гофра)</t>
         </is>
       </c>
       <c r="B181" s="29" t="inlineStr">
@@ -5638,33 +5745,35 @@
           <t>Цена, ₸</t>
         </is>
       </c>
-      <c r="C181" s="30" t="n"/>
+      <c r="C181" s="30" t="n">
+        <v>6768</v>
+      </c>
       <c r="D181" s="30" t="n">
-        <v>88</v>
+        <v>6823</v>
       </c>
       <c r="E181" s="30" t="n">
-        <v>4400</v>
+        <v>7177</v>
       </c>
       <c r="F181" s="30" t="n">
-        <v>4765</v>
+        <v>7129</v>
       </c>
       <c r="G181" s="30" t="n">
-        <v>4871</v>
+        <v>7044</v>
       </c>
       <c r="H181" s="30" t="n">
-        <v>4789</v>
+        <v>7008</v>
       </c>
       <c r="I181" s="30" t="n">
-        <v>4832</v>
+        <v>7213</v>
       </c>
       <c r="J181" s="30" t="n">
-        <v>4768</v>
+        <v>6946</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 62%</t>
+          <t>Выпечка_ · маржа 59%</t>
         </is>
       </c>
       <c r="B182" s="29" t="inlineStr">
@@ -5673,34 +5782,34 @@
         </is>
       </c>
       <c r="C182" s="32" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="D182" s="32" t="n">
-        <v>155</v>
+        <v>265</v>
       </c>
       <c r="E182" s="32" t="n">
-        <v>506</v>
+        <v>335</v>
       </c>
       <c r="F182" s="32" t="n">
-        <v>330</v>
+        <v>376</v>
       </c>
       <c r="G182" s="32" t="n">
-        <v>370</v>
+        <v>293</v>
       </c>
       <c r="H182" s="32" t="n">
-        <v>507</v>
+        <v>421</v>
       </c>
       <c r="I182" s="32" t="n">
-        <v>875</v>
+        <v>567</v>
       </c>
       <c r="J182" s="32" t="n">
-        <v>454</v>
+        <v>444</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="28" t="inlineStr">
         <is>
-          <t>Бризоль с рисом (1порц)</t>
+          <t>Пирожок с капустой (30 шт гофра)</t>
         </is>
       </c>
       <c r="B197" s="29" t="inlineStr">
@@ -5709,34 +5818,34 @@
         </is>
       </c>
       <c r="C197" s="30" t="n">
-        <v>1149</v>
+        <v>4310</v>
       </c>
       <c r="D197" s="30" t="n">
-        <v>1154</v>
+        <v>4715</v>
       </c>
       <c r="E197" s="30" t="n">
-        <v>1226</v>
+        <v>4746</v>
       </c>
       <c r="F197" s="30" t="n">
-        <v>1202</v>
+        <v>4788</v>
       </c>
       <c r="G197" s="30" t="n">
-        <v>1207</v>
+        <v>4792</v>
       </c>
       <c r="H197" s="30" t="n">
-        <v>1188</v>
+        <v>3492</v>
       </c>
       <c r="I197" s="30" t="n">
-        <v>1179</v>
+        <v>4647</v>
       </c>
       <c r="J197" s="30" t="n">
-        <v>1182</v>
+        <v>4723</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 37%</t>
+          <t>Выпечка_ · маржа 62%</t>
         </is>
       </c>
       <c r="B198" s="29" t="inlineStr">
@@ -5745,34 +5854,34 @@
         </is>
       </c>
       <c r="C198" s="32" t="n">
-        <v>1835</v>
+        <v>381</v>
       </c>
       <c r="D198" s="32" t="n">
-        <v>1583</v>
+        <v>349</v>
       </c>
       <c r="E198" s="32" t="n">
-        <v>1421</v>
+        <v>496</v>
       </c>
       <c r="F198" s="32" t="n">
-        <v>1789</v>
+        <v>446</v>
       </c>
       <c r="G198" s="32" t="n">
-        <v>1816</v>
+        <v>454</v>
       </c>
       <c r="H198" s="32" t="n">
-        <v>2234</v>
+        <v>829</v>
       </c>
       <c r="I198" s="32" t="n">
-        <v>2204</v>
+        <v>724</v>
       </c>
       <c r="J198" s="32" t="n">
-        <v>2244</v>
+        <v>714</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="28" t="inlineStr">
         <is>
-          <t>Блины с ветчиной и сыром (3шт)</t>
+          <t>Манты с говядиной (1порц)</t>
         </is>
       </c>
       <c r="B213" s="29" t="inlineStr">
@@ -5781,34 +5890,34 @@
         </is>
       </c>
       <c r="C213" s="30" t="n">
-        <v>863</v>
+        <v>831</v>
       </c>
       <c r="D213" s="30" t="n">
-        <v>853</v>
+        <v>801</v>
       </c>
       <c r="E213" s="30" t="n">
-        <v>896</v>
+        <v>790</v>
       </c>
       <c r="F213" s="30" t="n">
-        <v>858</v>
+        <v>795</v>
       </c>
       <c r="G213" s="30" t="n">
-        <v>885</v>
+        <v>848</v>
       </c>
       <c r="H213" s="30" t="n">
-        <v>897</v>
+        <v>790</v>
       </c>
       <c r="I213" s="30" t="n">
-        <v>924</v>
+        <v>873</v>
       </c>
       <c r="J213" s="30" t="n">
-        <v>961</v>
+        <v>939</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="31" t="inlineStr">
         <is>
-          <t>Завтраки · маржа 49%</t>
+          <t>Горячее · маржа 42%</t>
         </is>
       </c>
       <c r="B214" s="29" t="inlineStr">
@@ -5817,34 +5926,34 @@
         </is>
       </c>
       <c r="C214" s="32" t="n">
-        <v>2211</v>
+        <v>3204</v>
       </c>
       <c r="D214" s="32" t="n">
-        <v>2131</v>
+        <v>3017</v>
       </c>
       <c r="E214" s="32" t="n">
-        <v>2922</v>
+        <v>3925</v>
       </c>
       <c r="F214" s="32" t="n">
-        <v>2412</v>
+        <v>3334</v>
       </c>
       <c r="G214" s="32" t="n">
-        <v>2638</v>
+        <v>3173</v>
       </c>
       <c r="H214" s="32" t="n">
-        <v>2729</v>
+        <v>3667</v>
       </c>
       <c r="I214" s="32" t="n">
-        <v>2832</v>
+        <v>3234</v>
       </c>
       <c r="J214" s="32" t="n">
-        <v>2945</v>
+        <v>3453</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="28" t="inlineStr">
         <is>
-          <t>Самса с говядиной (30 шт гофра)</t>
+          <t>Сочник творожный (30шт гофра )</t>
         </is>
       </c>
       <c r="B229" s="29" t="inlineStr">
@@ -5853,34 +5962,34 @@
         </is>
       </c>
       <c r="C229" s="30" t="n">
-        <v>7098</v>
+        <v>7012</v>
       </c>
       <c r="D229" s="30" t="n">
-        <v>6977</v>
+        <v>6983</v>
       </c>
       <c r="E229" s="30" t="n">
-        <v>7003</v>
+        <v>7182</v>
       </c>
       <c r="F229" s="30" t="n">
-        <v>6964</v>
+        <v>7137</v>
       </c>
       <c r="G229" s="30" t="n">
-        <v>6862</v>
+        <v>7249</v>
       </c>
       <c r="H229" s="30" t="n">
+        <v>6963</v>
+      </c>
+      <c r="I229" s="30" t="n">
         <v>6912</v>
       </c>
-      <c r="I229" s="30" t="n">
-        <v>6774</v>
-      </c>
       <c r="J229" s="30" t="n">
-        <v>6805</v>
+        <v>6814</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 44%</t>
+          <t>Выпечка_ · маржа 61%</t>
         </is>
       </c>
       <c r="B230" s="29" t="inlineStr">
@@ -5889,34 +5998,34 @@
         </is>
       </c>
       <c r="C230" s="32" t="n">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="D230" s="32" t="n">
-        <v>130</v>
+        <v>169</v>
       </c>
       <c r="E230" s="32" t="n">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="F230" s="32" t="n">
-        <v>210</v>
+        <v>306</v>
       </c>
       <c r="G230" s="32" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H230" s="32" t="n">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="I230" s="32" t="n">
-        <v>256</v>
+        <v>418</v>
       </c>
       <c r="J230" s="32" t="n">
-        <v>541</v>
+        <v>461</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="28" t="inlineStr">
         <is>
-          <t>Самса с курицей (30шт гофра )</t>
+          <t>Бризоль с рисом (1порц)</t>
         </is>
       </c>
       <c r="B245" s="29" t="inlineStr">
@@ -5925,34 +6034,34 @@
         </is>
       </c>
       <c r="C245" s="30" t="n">
-        <v>6935</v>
+        <v>1149</v>
       </c>
       <c r="D245" s="30" t="n">
-        <v>6925</v>
+        <v>1154</v>
       </c>
       <c r="E245" s="30" t="n">
-        <v>6901</v>
+        <v>1226</v>
       </c>
       <c r="F245" s="30" t="n">
-        <v>6983</v>
+        <v>1202</v>
       </c>
       <c r="G245" s="30" t="n">
-        <v>6703</v>
+        <v>1207</v>
       </c>
       <c r="H245" s="30" t="n">
-        <v>6897</v>
+        <v>1188</v>
       </c>
       <c r="I245" s="30" t="n">
-        <v>6710</v>
+        <v>1179</v>
       </c>
       <c r="J245" s="30" t="n">
-        <v>6765</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 61%</t>
+          <t>Горячее · маржа 37%</t>
         </is>
       </c>
       <c r="B246" s="29" t="inlineStr">
@@ -5961,34 +6070,34 @@
         </is>
       </c>
       <c r="C246" s="32" t="n">
-        <v>218</v>
+        <v>1835</v>
       </c>
       <c r="D246" s="32" t="n">
-        <v>161</v>
+        <v>1583</v>
       </c>
       <c r="E246" s="32" t="n">
-        <v>211</v>
+        <v>1421</v>
       </c>
       <c r="F246" s="32" t="n">
-        <v>253</v>
+        <v>1789</v>
       </c>
       <c r="G246" s="32" t="n">
-        <v>250</v>
+        <v>1816</v>
       </c>
       <c r="H246" s="32" t="n">
-        <v>301</v>
+        <v>2234</v>
       </c>
       <c r="I246" s="32" t="n">
-        <v>285</v>
+        <v>2204</v>
       </c>
       <c r="J246" s="32" t="n">
-        <v>569</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="28" t="inlineStr">
         <is>
-          <t>Круассан с индейкой (1шт)</t>
+          <t>Блины с ветчиной и сыром (3шт)</t>
         </is>
       </c>
       <c r="B261" s="29" t="inlineStr">
@@ -5997,34 +6106,34 @@
         </is>
       </c>
       <c r="C261" s="30" t="n">
-        <v>590</v>
+        <v>863</v>
       </c>
       <c r="D261" s="30" t="n">
-        <v>599</v>
+        <v>853</v>
       </c>
       <c r="E261" s="30" t="n">
-        <v>593</v>
+        <v>894</v>
       </c>
       <c r="F261" s="30" t="n">
-        <v>577</v>
+        <v>858</v>
       </c>
       <c r="G261" s="30" t="n">
-        <v>587</v>
+        <v>884</v>
       </c>
       <c r="H261" s="30" t="n">
-        <v>595</v>
+        <v>897</v>
       </c>
       <c r="I261" s="30" t="n">
-        <v>611</v>
+        <v>924</v>
       </c>
       <c r="J261" s="30" t="n">
-        <v>619</v>
+        <v>961</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="31" t="inlineStr">
         <is>
-          <t>СЭНДВИЧИ · маржа 61%</t>
+          <t>Завтраки · маржа 49%</t>
         </is>
       </c>
       <c r="B262" s="29" t="inlineStr">
@@ -6033,34 +6142,34 @@
         </is>
       </c>
       <c r="C262" s="32" t="n">
-        <v>2352</v>
+        <v>2211</v>
       </c>
       <c r="D262" s="32" t="n">
-        <v>2345</v>
+        <v>2131</v>
       </c>
       <c r="E262" s="32" t="n">
-        <v>2472</v>
+        <v>2928</v>
       </c>
       <c r="F262" s="32" t="n">
-        <v>3314</v>
+        <v>2427</v>
       </c>
       <c r="G262" s="32" t="n">
-        <v>3960</v>
+        <v>2648</v>
       </c>
       <c r="H262" s="32" t="n">
-        <v>4761</v>
+        <v>2730</v>
       </c>
       <c r="I262" s="32" t="n">
-        <v>4156</v>
+        <v>2832</v>
       </c>
       <c r="J262" s="32" t="n">
-        <v>3941</v>
+        <v>2945</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="28" t="inlineStr">
         <is>
-          <t>Клаб Сэндвич с курицей (1шт)</t>
+          <t>Самса с говядиной (30 шт гофра)</t>
         </is>
       </c>
       <c r="B277" s="29" t="inlineStr">
@@ -6069,34 +6178,34 @@
         </is>
       </c>
       <c r="C277" s="30" t="n">
-        <v>488</v>
+        <v>7098</v>
       </c>
       <c r="D277" s="30" t="n">
-        <v>489</v>
+        <v>6977</v>
       </c>
       <c r="E277" s="30" t="n">
-        <v>512</v>
+        <v>7003</v>
       </c>
       <c r="F277" s="30" t="n">
-        <v>506</v>
+        <v>6964</v>
       </c>
       <c r="G277" s="30" t="n">
-        <v>509</v>
+        <v>6862</v>
       </c>
       <c r="H277" s="30" t="n">
-        <v>514</v>
+        <v>6912</v>
       </c>
       <c r="I277" s="30" t="n">
-        <v>516</v>
+        <v>6774</v>
       </c>
       <c r="J277" s="30" t="n">
-        <v>524</v>
+        <v>6805</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="31" t="inlineStr">
         <is>
-          <t>СЭНДВИЧИ · маржа 56%</t>
+          <t>Выпечка_ · маржа 44%</t>
         </is>
       </c>
       <c r="B278" s="29" t="inlineStr">
@@ -6105,34 +6214,34 @@
         </is>
       </c>
       <c r="C278" s="32" t="n">
-        <v>3237</v>
+        <v>186</v>
       </c>
       <c r="D278" s="32" t="n">
-        <v>3273</v>
+        <v>130</v>
       </c>
       <c r="E278" s="32" t="n">
-        <v>4099</v>
+        <v>217</v>
       </c>
       <c r="F278" s="32" t="n">
-        <v>4262</v>
+        <v>210</v>
       </c>
       <c r="G278" s="32" t="n">
-        <v>4270</v>
+        <v>237</v>
       </c>
       <c r="H278" s="32" t="n">
-        <v>4191</v>
+        <v>357</v>
       </c>
       <c r="I278" s="32" t="n">
-        <v>5051</v>
+        <v>256</v>
       </c>
       <c r="J278" s="32" t="n">
-        <v>5713</v>
+        <v>541</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="28" t="inlineStr">
         <is>
-          <t>Круассан миндальный (10 шт гофра)</t>
+          <t>Самса с курицей (30шт гофра )</t>
         </is>
       </c>
       <c r="B293" s="29" t="inlineStr">
@@ -6141,34 +6250,34 @@
         </is>
       </c>
       <c r="C293" s="30" t="n">
-        <v>7232</v>
+        <v>6935</v>
       </c>
       <c r="D293" s="30" t="n">
-        <v>7166</v>
+        <v>6925</v>
       </c>
       <c r="E293" s="30" t="n">
-        <v>7239</v>
+        <v>6901</v>
       </c>
       <c r="F293" s="30" t="n">
-        <v>7196</v>
+        <v>6983</v>
       </c>
       <c r="G293" s="30" t="n">
-        <v>7412</v>
+        <v>6703</v>
       </c>
       <c r="H293" s="30" t="n">
-        <v>7205</v>
+        <v>6897</v>
       </c>
       <c r="I293" s="30" t="n">
-        <v>7374</v>
+        <v>6710</v>
       </c>
       <c r="J293" s="30" t="n">
-        <v>7155</v>
+        <v>6765</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 59%</t>
+          <t>Выпечка_ · маржа 61%</t>
         </is>
       </c>
       <c r="B294" s="29" t="inlineStr">
@@ -6177,34 +6286,34 @@
         </is>
       </c>
       <c r="C294" s="32" t="n">
-        <v>108</v>
+        <v>218</v>
       </c>
       <c r="D294" s="32" t="n">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="E294" s="32" t="n">
-        <v>245</v>
+        <v>211</v>
       </c>
       <c r="F294" s="32" t="n">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="G294" s="32" t="n">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="H294" s="32" t="n">
-        <v>335</v>
+        <v>301</v>
       </c>
       <c r="I294" s="32" t="n">
-        <v>488</v>
+        <v>285</v>
       </c>
       <c r="J294" s="32" t="n">
-        <v>238</v>
+        <v>569</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="28" t="inlineStr">
         <is>
-          <t>Шницель куриный с картофельным пюре (1порц)</t>
+          <t>Круассан с индейкой (1шт)</t>
         </is>
       </c>
       <c r="B309" s="29" t="inlineStr">
@@ -6213,34 +6322,34 @@
         </is>
       </c>
       <c r="C309" s="30" t="n">
-        <v>859</v>
+        <v>590</v>
       </c>
       <c r="D309" s="30" t="n">
-        <v>841</v>
+        <v>599</v>
       </c>
       <c r="E309" s="30" t="n">
-        <v>857</v>
+        <v>593</v>
       </c>
       <c r="F309" s="30" t="n">
-        <v>856</v>
+        <v>577</v>
       </c>
       <c r="G309" s="30" t="n">
-        <v>899</v>
+        <v>587</v>
       </c>
       <c r="H309" s="30" t="n">
-        <v>812</v>
+        <v>595</v>
       </c>
       <c r="I309" s="30" t="n">
-        <v>891</v>
+        <v>611</v>
       </c>
       <c r="J309" s="30" t="n">
-        <v>911</v>
+        <v>619</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 54%</t>
+          <t>СЭНДВИЧИ · маржа 61%</t>
         </is>
       </c>
       <c r="B310" s="29" t="inlineStr">
@@ -6249,28 +6358,28 @@
         </is>
       </c>
       <c r="C310" s="32" t="n">
-        <v>2443</v>
+        <v>2352</v>
       </c>
       <c r="D310" s="32" t="n">
-        <v>2194</v>
+        <v>2345</v>
       </c>
       <c r="E310" s="32" t="n">
-        <v>1988</v>
+        <v>2472</v>
       </c>
       <c r="F310" s="32" t="n">
-        <v>2128</v>
+        <v>3314</v>
       </c>
       <c r="G310" s="32" t="n">
-        <v>2114</v>
+        <v>3960</v>
       </c>
       <c r="H310" s="32" t="n">
-        <v>2619</v>
+        <v>4761</v>
       </c>
       <c r="I310" s="32" t="n">
-        <v>2763</v>
+        <v>4156</v>
       </c>
       <c r="J310" s="32" t="n">
-        <v>3372</v>
+        <v>3941</v>
       </c>
     </row>
   </sheetData>
@@ -6285,7 +6394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A21"/>
+  <dimension ref="A2:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -6383,29 +6492,46 @@
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="33" t="inlineStr">
         <is>
+          <t>Почему позиций двадцать, а карточек в iiko больше</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="70" customHeight="1">
+      <c r="A18" s="34" t="inlineStr">
+        <is>
+          <t>Часть позиций ведётся в iiko под двумя именами: обычным и с приставкой «RP*» — под ней ту же позицию берёт сеть АЗС. Это одно и то же изделие, поэтому в отчёте оно сведено в одну строку, а из каких карточек оно собрано, написано в последней колонке. Если считать карточки порознь, один товар распадается на две строки с разной историей цены, и в ТОП-20 попадают обе половинки. «Сырая» и «готовая» при этом остаются разными позициями.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="34" t="inlineStr"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="33" t="inlineStr">
+        <is>
           <t>Как считается «Цена ±»</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="34" t="inlineStr">
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>Медиана цены последних месяцев против медианы начала окна. Медиана, а не крайние точки, потому что первый месяц новой позиции — это пробная партия по розничной цене, и выход на опт выглядел бы обвалом. Месяцы, где позицию брали меньше четверти обычного объёма, из сравнения выброшены по той же причине.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="34" t="inlineStr">
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="34" t="inlineStr">
         <is>
           <t>Цена везде — выручка, делённая на количество, по всем клиентам сразу. Это фактическая цена отгрузки со всеми скидками, а не прайс.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="34" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="31" t="inlineStr">
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="34" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="inlineStr">
         <is>
           <t>Система «Пульс» · Фуд Завод · Ольга Герасименко, финансовый директор</t>
         </is>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="План" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены по месяцам" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Методика" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="План" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Цены по месяцам" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Методика" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'План'!$A$7:$T$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'План'!$A$7:$S$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -318,14 +318,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -343,7 +343,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="7C3AED"/>
               </a:solidFill>
@@ -354,7 +354,7 @@
             <symbol val="circle"/>
             <size val="6"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -395,8 +395,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -419,19 +419,19 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Пирожок с картофелем (30 шт гофра)</a:t>
+              <a:t>Сосиска в тесте (30шт гофра)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -444,7 +444,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="7C3AED"/>
               </a:solidFill>
@@ -455,7 +455,7 @@
             <symbol val="circle"/>
             <size val="6"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -496,8 +496,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -520,19 +520,19 @@
 </file>
 
 <file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Маффин шоколадный (24шт)</a:t>
+              <a:t>Манты с говядиной (1порц)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -545,7 +545,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="7C3AED"/>
               </a:solidFill>
@@ -556,7 +556,7 @@
             <symbol val="circle"/>
             <size val="6"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -597,8 +597,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -621,19 +621,19 @@
 </file>
 
 <file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Круассан миндальный (10 шт гофра)</a:t>
+              <a:t>Пирожок с картофелем (30 шт гофра)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -646,7 +646,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="7C3AED"/>
               </a:solidFill>
@@ -657,7 +657,7 @@
             <symbol val="circle"/>
             <size val="6"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -698,8 +698,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -722,19 +722,19 @@
 </file>
 
 <file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Пирожок с капустой (30 шт гофра)</a:t>
+              <a:t>Бризоль с рисом (1порц)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -747,7 +747,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="7C3AED"/>
               </a:solidFill>
@@ -758,7 +758,7 @@
             <symbol val="circle"/>
             <size val="6"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -799,8 +799,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -823,19 +823,19 @@
 </file>
 
 <file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Манты с говядиной (1порц)</a:t>
+              <a:t>Блины с ветчиной и сыром (3шт)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -848,7 +848,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="7C3AED"/>
               </a:solidFill>
@@ -859,7 +859,7 @@
             <symbol val="circle"/>
             <size val="6"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -900,8 +900,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -924,19 +924,19 @@
 </file>
 
 <file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Сочник творожный (30шт гофра )</a:t>
+              <a:t>Самса с говядиной (30 шт гофра)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -949,7 +949,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="7C3AED"/>
               </a:solidFill>
@@ -960,7 +960,7 @@
             <symbol val="circle"/>
             <size val="6"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1001,8 +1001,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1025,19 +1025,19 @@
 </file>
 
 <file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Бризоль с рисом (1порц)</a:t>
+              <a:t>Самса с курицей (30шт гофра )</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1050,7 +1050,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="7C3AED"/>
               </a:solidFill>
@@ -1061,7 +1061,7 @@
             <symbol val="circle"/>
             <size val="6"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1102,8 +1102,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1126,19 +1126,19 @@
 </file>
 
 <file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Блины с ветчиной и сыром (3шт)</a:t>
+              <a:t>Круассан с индейкой (1шт)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1151,7 +1151,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="7C3AED"/>
               </a:solidFill>
@@ -1162,7 +1162,7 @@
             <symbol val="circle"/>
             <size val="6"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1203,8 +1203,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1227,19 +1227,19 @@
 </file>
 
 <file path=xl/charts/chart18.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Самса с говядиной (30 шт гофра)</a:t>
+              <a:t>Клаб Сэндвич с курицей (1шт)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1252,7 +1252,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="7C3AED"/>
               </a:solidFill>
@@ -1263,7 +1263,7 @@
             <symbol val="circle"/>
             <size val="6"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1304,8 +1304,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1328,19 +1328,19 @@
 </file>
 
 <file path=xl/charts/chart19.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Самса с курицей (30шт гофра )</a:t>
+              <a:t>Круассан миндальный (10 шт гофра)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1353,7 +1353,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="7C3AED"/>
               </a:solidFill>
@@ -1364,7 +1364,7 @@
             <symbol val="circle"/>
             <size val="6"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1405,8 +1405,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1429,14 +1429,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1454,7 +1454,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="7C3AED"/>
               </a:solidFill>
@@ -1465,7 +1465,7 @@
             <symbol val="circle"/>
             <size val="6"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1506,8 +1506,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1530,19 +1530,19 @@
 </file>
 
 <file path=xl/charts/chart20.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Круассан с индейкой (1шт)</a:t>
+              <a:t>Шницель куриный с картофельным пюре (1порц)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1555,7 +1555,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="7C3AED"/>
               </a:solidFill>
@@ -1566,7 +1566,7 @@
             <symbol val="circle"/>
             <size val="6"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1607,8 +1607,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1631,14 +1631,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1656,7 +1656,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="7C3AED"/>
               </a:solidFill>
@@ -1667,7 +1667,7 @@
             <symbol val="circle"/>
             <size val="6"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1708,8 +1708,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1732,14 +1732,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1757,7 +1757,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="7C3AED"/>
               </a:solidFill>
@@ -1768,7 +1768,7 @@
             <symbol val="circle"/>
             <size val="6"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1809,8 +1809,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1833,19 +1833,19 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Пирожок с курицей и сыром (30 шт гофра)</a:t>
+              <a:t>Кимпаб с тунцом (1шт)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1858,7 +1858,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="7C3AED"/>
               </a:solidFill>
@@ -1869,7 +1869,7 @@
             <symbol val="circle"/>
             <size val="6"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1910,8 +1910,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1934,19 +1934,19 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Кимпаб с тунцом (1шт)</a:t>
+              <a:t>Кимпаб с курицей (1шт)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1959,7 +1959,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="7C3AED"/>
               </a:solidFill>
@@ -1970,7 +1970,7 @@
             <symbol val="circle"/>
             <size val="6"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2011,8 +2011,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -2035,19 +2035,19 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Кимпаб с курицей (1шт)</a:t>
+              <a:t>Курица с сыром и картофельным пюре (1порц)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2060,7 +2060,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="7C3AED"/>
               </a:solidFill>
@@ -2071,7 +2071,7 @@
             <symbol val="circle"/>
             <size val="6"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2112,8 +2112,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -2136,19 +2136,19 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Курица с сыром и картофельным пюре (1порц)</a:t>
+              <a:t>Курица с сыром с рисом и паутини (1порц)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2161,7 +2161,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="7C3AED"/>
               </a:solidFill>
@@ -2172,7 +2172,7 @@
             <symbol val="circle"/>
             <size val="6"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2213,8 +2213,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -2237,19 +2237,19 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Курица с сыром с рисом и паутини (1порц)</a:t>
+              <a:t>Пирожок с курицей и сыром (30 шт гофра)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2262,7 +2262,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln w="22000">
               <a:solidFill>
                 <a:srgbClr val="7C3AED"/>
               </a:solidFill>
@@ -2273,7 +2273,7 @@
             <symbol val="circle"/>
             <size val="6"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -2314,8 +2314,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -2338,7 +2338,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
@@ -2353,9 +2353,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2375,9 +2375,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2397,9 +2397,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2419,9 +2419,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2441,9 +2441,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <c:chart r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2463,9 +2463,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+          <c:chart r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2485,9 +2485,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+          <c:chart r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2507,9 +2507,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+          <c:chart r:id="rId8"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2529,9 +2529,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+          <c:chart r:id="rId9"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2551,9 +2551,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+          <c:chart r:id="rId10"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2573,9 +2573,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+          <c:chart r:id="rId11"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2595,9 +2595,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
+          <c:chart r:id="rId12"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2617,9 +2617,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
+          <c:chart r:id="rId13"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2639,9 +2639,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
+          <c:chart r:id="rId14"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2661,9 +2661,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
+          <c:chart r:id="rId15"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2683,9 +2683,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
+          <c:chart r:id="rId16"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2705,9 +2705,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId17"/>
+          <c:chart r:id="rId17"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2727,9 +2727,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId18"/>
+          <c:chart r:id="rId18"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2749,9 +2749,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19"/>
+          <c:chart r:id="rId19"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2771,9 +2771,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId20"/>
+          <c:chart r:id="rId20"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3071,7 +3071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T28"/>
+  <dimension ref="A1:S28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3093,7 +3093,6 @@
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="58" customWidth="1" min="19" max="19"/>
-    <col width="46" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3236,11 +3235,6 @@
           <t>Обоснование</t>
         </is>
       </c>
-      <c r="T7" s="7" t="inlineStr">
-        <is>
-          <t>Карточки в iiko</t>
-        </is>
-      </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
@@ -3259,31 +3253,31 @@
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>11467170</v>
+        <v>9312930</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1627</v>
+        <v>1325</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>7047</v>
+        <v>7027</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>-0.005144146725738707</v>
+        <v>-0.01462037666214644</v>
       </c>
       <c r="H8" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.5148728308728309</v>
+        <v>0.516</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>0.6096274315858885</v>
+        <v>0.5152439024390243</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M8" s="10">
         <f>ROUND(F8*(1+L8),0)</f>
@@ -3311,12 +3305,7 @@
       </c>
       <c r="S8" s="14" t="inlineStr">
         <is>
-          <t>за 6 мес цена упала на 0.5% при ориентире 4.0%; берут на 61% больше</t>
-        </is>
-      </c>
-      <c r="T8" s="14" t="inlineStr">
-        <is>
-          <t>Упак Брецель-дог (20шт) · RP* Упак Брецель-дог (20шт)</t>
+          <t>за 6 мес цена упала на 1.5% при ориентире 4.0%; берут на 52% больше</t>
         </is>
       </c>
     </row>
@@ -3337,31 +3326,31 @@
         </is>
       </c>
       <c r="D9" s="16" t="n">
-        <v>10019546</v>
+        <v>6611799</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>1070</v>
+        <v>705</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>9361</v>
+        <v>9374</v>
       </c>
       <c r="G9" s="17" t="n">
-        <v>0.01606738290323895</v>
+        <v>0.02604835660919047</v>
       </c>
       <c r="H9" s="18" t="n">
         <v>8</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>0.5969796702365556</v>
+        <v>0.598</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>0.402183406113537</v>
+        <v>0.6202143950995407</v>
       </c>
       <c r="K9" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="M9" s="16">
         <f>ROUND(F9*(1+L9),0)</f>
@@ -3389,12 +3378,7 @@
       </c>
       <c r="S9" s="19" t="inlineStr">
         <is>
-          <t>за 8 мес цена выросла на 1.6% при ориентире 5.3%; берут на 40% больше</t>
-        </is>
-      </c>
-      <c r="T9" s="19" t="inlineStr">
-        <is>
-          <t>RP* Упак Сосиска в тесте  готов СМ (30шт гофра) · Упак Сосиска в тесте  готов СМ (30шт гофра)</t>
+          <t>за 8 мес цена выросла на 2.6% при ориентире 5.3%; берут на 62% больше</t>
         </is>
       </c>
     </row>
@@ -3470,11 +3454,6 @@
           <t>цену уже подняли на 9.9% — этого хватает</t>
         </is>
       </c>
-      <c r="T10" s="14" t="inlineStr">
-        <is>
-          <t>Упак Гуйру цомян (1порц)</t>
-        </is>
-      </c>
     </row>
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
@@ -3493,7 +3472,7 @@
         </is>
       </c>
       <c r="D11" s="16" t="n">
-        <v>5381606</v>
+        <v>5380972</v>
       </c>
       <c r="E11" s="16" t="n">
         <v>5162</v>
@@ -3511,7 +3490,7 @@
         <v>0.466</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>0.05843357025697093</v>
+        <v>0.06047116833310517</v>
       </c>
       <c r="K11" s="17" t="n">
         <v>0</v>
@@ -3548,54 +3527,49 @@
           <t>цену уже подняли на 14.4% — этого хватает</t>
         </is>
       </c>
-      <c r="T11" s="19" t="inlineStr">
-        <is>
-          <t>Упак Плов по-ташкентски (1порц) · RP* Упак Плов по-ташкентски (1порц)</t>
-        </is>
-      </c>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Пирожок с курицей и сыром (30 шт гофра)</t>
+          <t>Кимпаб с тунцом (1шт)</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Выпечка_</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>1 — сейчас</t>
+          <t>Япония</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>— не трогать</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>5160362</v>
+        <v>5104472</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>980</v>
+        <v>5379</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>5267</v>
+        <v>949</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.004644817839810855</v>
+        <v>0.1144551028227871</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>0.4990455257437672</v>
+        <v>0.539</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>0.4364613880742911</v>
+        <v>0.2232582821620803</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>0.065</v>
+        <v>0</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>0.065</v>
+        <v>0</v>
       </c>
       <c r="M12" s="10">
         <f>ROUND(F12*(1+L12),0)</f>
@@ -3623,19 +3597,14 @@
       </c>
       <c r="S12" s="14" t="inlineStr">
         <is>
-          <t>за 8 мес цена выросла на 0.5% при ориентире 5.3%; берут на 44% больше</t>
-        </is>
-      </c>
-      <c r="T12" s="14" t="inlineStr">
-        <is>
-          <t>RP* Упак Пирожок с курицей и сыром готов СМ (30 шт гофра) · Упак Пирожок с курицей и сыром готов СМ (30 шт гофра)</t>
+          <t>цену уже подняли на 11.4% — этого хватает</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>Кимпаб с тунцом (1шт)</t>
+          <t>Кимпаб с курицей (1шт)</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
@@ -3649,25 +3618,25 @@
         </is>
       </c>
       <c r="D13" s="16" t="n">
-        <v>5104472</v>
+        <v>4336019</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>5379</v>
+        <v>5350</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>949</v>
+        <v>810</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.1144551028227871</v>
+        <v>0.09497220501137482</v>
       </c>
       <c r="H13" s="18" t="n">
         <v>8</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>0.5389999999999999</v>
+        <v>0.491</v>
       </c>
       <c r="J13" s="17" t="n">
-        <v>0.2232582821620803</v>
+        <v>0.1162887745166225</v>
       </c>
       <c r="K13" s="17" t="n">
         <v>0</v>
@@ -3701,24 +3670,19 @@
       </c>
       <c r="S13" s="19" t="inlineStr">
         <is>
-          <t>цену уже подняли на 11.4% — этого хватает</t>
-        </is>
-      </c>
-      <c r="T13" s="19" t="inlineStr">
-        <is>
-          <t>Упак Кимпаб с тунцом (1шт)</t>
+          <t>цену уже подняли на 9.5% — этого хватает</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Кимпаб с курицей (1шт)</t>
+          <t>Курица с сыром и картофельным пюре (1порц)</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Япония</t>
+          <t>Горячее</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -3727,25 +3691,25 @@
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>4336019</v>
+        <v>4293422</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>5350</v>
+        <v>3814</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>810</v>
+        <v>1126</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>0.09497220501137482</v>
+        <v>0.07968634845642675</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>0.491</v>
+        <v>0.5760000000000001</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>0.1162887745166225</v>
+        <v>0.1776268395595348</v>
       </c>
       <c r="K14" s="11" t="n">
         <v>0</v>
@@ -3779,19 +3743,14 @@
       </c>
       <c r="S14" s="14" t="inlineStr">
         <is>
-          <t>цену уже подняли на 9.5% — этого хватает</t>
-        </is>
-      </c>
-      <c r="T14" s="14" t="inlineStr">
-        <is>
-          <t>Упак Кимпаб с курицей (1шт)</t>
+          <t>признаков отставания цены нет</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>Курица с сыром и картофельным пюре (1порц)</t>
+          <t>Курица с сыром с рисом и паутини (1порц)</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -3805,25 +3764,25 @@
         </is>
       </c>
       <c r="D15" s="16" t="n">
-        <v>4293422</v>
+        <v>3800654</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>3814</v>
+        <v>3515</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>1126</v>
+        <v>1081</v>
       </c>
       <c r="G15" s="17" t="n">
-        <v>0.07968634845642675</v>
+        <v>0.07050092845465161</v>
       </c>
       <c r="H15" s="18" t="n">
         <v>8</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>0.5760000000000001</v>
+        <v>0.581</v>
       </c>
       <c r="J15" s="17" t="n">
-        <v>0.1776268395595348</v>
+        <v>0.1870989530563998</v>
       </c>
       <c r="K15" s="17" t="n">
         <v>0</v>
@@ -3860,54 +3819,49 @@
           <t>признаков отставания цены нет</t>
         </is>
       </c>
-      <c r="T15" s="19" t="inlineStr">
-        <is>
-          <t>Упак Курица с сыром и картофельным пюре (1порц)</t>
-        </is>
-      </c>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Курица с сыром с рисом и паутини (1порц)</t>
+          <t>Пирожок с курицей и сыром (30 шт гофра)</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Горячее</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>— не трогать</t>
+          <t>Выпечка_</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>2 — следом</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>3800654</v>
+        <v>3632550</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>3515</v>
+        <v>680</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>1081</v>
+        <v>5339</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>0.07050092845465161</v>
+        <v>0.008803340664356396</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>0.581</v>
+        <v>0.51</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>0.1870989530563998</v>
+        <v>0.4557774607703282</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="M16" s="10">
         <f>ROUND(F16*(1+L16),0)</f>
@@ -3935,19 +3889,14 @@
       </c>
       <c r="S16" s="14" t="inlineStr">
         <is>
-          <t>признаков отставания цены нет</t>
-        </is>
-      </c>
-      <c r="T16" s="14" t="inlineStr">
-        <is>
-          <t>Упак Курица с сыром с рисом и паутини (1порц)</t>
+          <t>за 8 мес цена выросла на 0.9% при ориентире 5.3%; берут на 46% больше</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>Пирожок с картофелем (30 шт гофра)</t>
+          <t>Сосиска в тесте (30шт гофра)</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -3961,31 +3910,31 @@
         </is>
       </c>
       <c r="D17" s="16" t="n">
-        <v>3780853</v>
+        <v>3407747</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>826</v>
+        <v>365</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>4577</v>
+        <v>9336</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.07254732484211801</v>
+        <v>-0.001173885973586253</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I17" s="17" t="n">
-        <v>0.6023283970574894</v>
+        <v>0.594</v>
       </c>
       <c r="J17" s="17" t="n">
-        <v>0.7662152530292229</v>
+        <v>0.1128048780487805</v>
       </c>
       <c r="K17" s="17" t="n">
-        <v>0.015</v>
+        <v>0.055</v>
       </c>
       <c r="L17" s="13" t="n">
-        <v>0.015</v>
+        <v>0.055</v>
       </c>
       <c r="M17" s="16">
         <f>ROUND(F17*(1+L17),0)</f>
@@ -4013,57 +3962,52 @@
       </c>
       <c r="S17" s="19" t="inlineStr">
         <is>
-          <t>берут на 77% больше</t>
-        </is>
-      </c>
-      <c r="T17" s="19" t="inlineStr">
-        <is>
-          <t>RP* Упак Пирожок с картофелем готов СМ (30 шт гофра) · Упак Пирожок с картофелем готов СМ (30 шт гофра)</t>
+          <t>за 8 мес цена упала на 0.1% при ориентире 5.3%</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Маффин шоколадный (24шт)</t>
+          <t>Манты с говядиной (1порц)</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Выпечка_</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>2 — следом</t>
+          <t>Горячее</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>— не трогать</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>3539168</v>
+        <v>2986476</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>482</v>
+        <v>3451</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>7343</v>
+        <v>865</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>-0.003665392881112228</v>
+        <v>0.09012158410248471</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>0.4849398251284082</v>
+        <v>0.419</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>0.130570758405004</v>
+        <v>-0.004902431990771894</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="L18" s="13" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="M18" s="10">
         <f>ROUND(F18*(1+L18),0)</f>
@@ -4091,19 +4035,14 @@
       </c>
       <c r="S18" s="14" t="inlineStr">
         <is>
-          <t>за 8 мес цена упала на 0.4% при ориентире 5.3%</t>
-        </is>
-      </c>
-      <c r="T18" s="14" t="inlineStr">
-        <is>
-          <t>Упак Маффин шоколадный (24шт) · RP* Упак Маффин шоколадный (24шт)</t>
+          <t>цену уже подняли на 9.0% — этого хватает</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>Круассан миндальный (10 шт гофра)</t>
+          <t>Пирожок с картофелем (30 шт гофра)</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
@@ -4111,37 +4050,37 @@
           <t>Выпечка_</t>
         </is>
       </c>
-      <c r="C19" s="21" t="inlineStr">
-        <is>
-          <t>2 — следом</t>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>— не трогать</t>
         </is>
       </c>
       <c r="D19" s="16" t="n">
-        <v>3374756</v>
+        <v>2940381</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>477</v>
+        <v>612</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>7070</v>
+        <v>4805</v>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.02718255545943404</v>
+        <v>0.08843677289461338</v>
       </c>
       <c r="H19" s="18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>0.5856715825776243</v>
+        <v>0.617</v>
       </c>
       <c r="J19" s="17" t="n">
-        <v>0.4262948207171313</v>
+        <v>0.5223880597014925</v>
       </c>
       <c r="K19" s="17" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="M19" s="16">
         <f>ROUND(F19*(1+L19),0)</f>
@@ -4169,57 +4108,52 @@
       </c>
       <c r="S19" s="19" t="inlineStr">
         <is>
-          <t>за 8 мес цена выросла на 2.7% при ориентире 5.3%; берут на 43% больше</t>
-        </is>
-      </c>
-      <c r="T19" s="19" t="inlineStr">
-        <is>
-          <t>RP* Упак Круассан миндальный готов СМ (10 шт гофра) · Упак Круассан миндальный готов СМ (10 шт гофра)</t>
+          <t>цену уже подняли на 8.8% — этого хватает</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Пирожок с капустой (30 шт гофра)</t>
+          <t>Бризоль с рисом (1порц)</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Выпечка_</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
-        <is>
-          <t>2 — следом + 2-й шаг</t>
+          <t>Горячее</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>1 — сейчас</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>3210495</v>
+        <v>2634834</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>756</v>
+        <v>2227</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>4249</v>
+        <v>1183</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>-0.01425098681656201</v>
+        <v>0.02382420203660618</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>0.6249372417648992</v>
+        <v>0.366</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>0.6239255014326648</v>
+        <v>0.3294866693195387</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="L20" s="13" t="n">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="M20" s="10">
         <f>ROUND(F20*(1+L20),0)</f>
@@ -4247,24 +4181,19 @@
       </c>
       <c r="S20" s="14" t="inlineStr">
         <is>
-          <t>за 8 мес цена упала на 1.4% при ориентире 5.3%; берут на 62% больше. Расчёт просит 8.5% — остальное вторым шагом через квартал</t>
-        </is>
-      </c>
-      <c r="T20" s="14" t="inlineStr">
-        <is>
-          <t>RP* Упак Пирожок с капустой  готов СМ (30 шт гофра) · Упак Пирожок с капустой  готов СМ (30 шт гофра)</t>
+          <t>за 8 мес цена выросла на 2.4% при ориентире 5.3%; маржа 37% — тоньше заводской; берут на 33% больше</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Манты с говядиной (1порц)</t>
+          <t>Блины с ветчиной и сыром (3шт)</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Горячее</t>
+          <t>Завтраки</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -4273,25 +4202,25 @@
         </is>
       </c>
       <c r="D21" s="16" t="n">
-        <v>2987025</v>
+        <v>2632114</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>3451</v>
+        <v>2835</v>
       </c>
       <c r="F21" s="16" t="n">
-        <v>865</v>
+        <v>928</v>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.09012158410248471</v>
+        <v>0.07048326431697016</v>
       </c>
       <c r="H21" s="18" t="n">
         <v>8</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>0.419</v>
+        <v>0.493</v>
       </c>
       <c r="J21" s="17" t="n">
-        <v>-0.007476993865030646</v>
+        <v>0.06698444555945815</v>
       </c>
       <c r="K21" s="17" t="n">
         <v>0</v>
@@ -4325,19 +4254,14 @@
       </c>
       <c r="S21" s="19" t="inlineStr">
         <is>
-          <t>цену уже подняли на 9.0% — этого хватает</t>
-        </is>
-      </c>
-      <c r="T21" s="19" t="inlineStr">
-        <is>
-          <t>Упак Манты с говядиной (1порц) · RP* Упак Манты с говядиной (1порц)</t>
+          <t>признаков отставания цены нет</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Сочник творожный (30шт гофра )</t>
+          <t>Самса с говядиной (30 шт гофра)</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -4347,29 +4271,29 @@
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>2 — следом</t>
+          <t>2 — следом + 2-й шаг</t>
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>2815730</v>
+        <v>2627782</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>409</v>
+        <v>385</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>6890</v>
+        <v>6831</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.01415503666138584</v>
+        <v>-0.02818816478082753</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>0.611</v>
+        <v>0.4429999999999999</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>0.5880829015544042</v>
+        <v>0.7379518072289157</v>
       </c>
       <c r="K22" s="11" t="n">
         <v>0.08</v>
@@ -4403,57 +4327,52 @@
       </c>
       <c r="S22" s="14" t="inlineStr">
         <is>
-          <t>за 8 мес цена упала на 1.4% при ориентире 5.3%; берут на 59% больше</t>
-        </is>
-      </c>
-      <c r="T22" s="14" t="inlineStr">
-        <is>
-          <t>RP* Упак Сочник творожный готов СМ (30шт гофра ) · Упак Сочник творожный готов СМ (30шт гофра )</t>
+          <t>за 8 мес цена упала на 2.8% при ориентире 5.3%; маржа 44% — тоньше заводской; берут на 74% больше. Расчёт просит 12.5% — остальное вторым шагом через квартал</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>Бризоль с рисом (1порц)</t>
+          <t>Самса с курицей (30шт гофра )</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>Горячее</t>
+          <t>Выпечка_</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
         <is>
-          <t>2 — следом</t>
+          <t>2 — следом + 2-й шаг</t>
         </is>
       </c>
       <c r="D23" s="16" t="n">
-        <v>2634834</v>
+        <v>2612647</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>2227</v>
+        <v>385</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>1183</v>
+        <v>6786</v>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.02382420203660618</v>
+        <v>-0.02307711041129701</v>
       </c>
       <c r="H23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>0.366</v>
+        <v>0.613</v>
       </c>
       <c r="J23" s="17" t="n">
-        <v>0.3294866693195387</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="K23" s="17" t="n">
-        <v>0.075</v>
+        <v>0.08</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>0.075</v>
+        <v>0.08</v>
       </c>
       <c r="M23" s="16">
         <f>ROUND(F23*(1+L23),0)</f>
@@ -4481,57 +4400,52 @@
       </c>
       <c r="S23" s="19" t="inlineStr">
         <is>
-          <t>за 8 мес цена выросла на 2.4% при ориентире 5.3%; маржа 37% — тоньше заводской; берут на 33% больше</t>
-        </is>
-      </c>
-      <c r="T23" s="19" t="inlineStr">
-        <is>
-          <t>Упак Бризоль с рисом (1порц)</t>
+          <t>за 8 мес цена упала на 2.3% при ориентире 5.3%; берут на 62% больше. Расчёт просит 9.0% — остальное вторым шагом через квартал</t>
         </is>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Блины с ветчиной и сыром (3шт)</t>
+          <t>Круассан с индейкой (1шт)</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Завтраки</t>
-        </is>
-      </c>
-      <c r="C24" s="20" t="inlineStr">
-        <is>
-          <t>— не трогать</t>
+          <t>СЭНДВИЧИ</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>2 — следом</t>
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>2632371</v>
+        <v>2604922</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>2836</v>
+        <v>4286</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>928</v>
+        <v>608</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>0.07048326431697016</v>
+        <v>0.03115280716362023</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>0.493</v>
+        <v>0.609</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>0.06297638385605397</v>
+        <v>0.3193104863533758</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="L24" s="13" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="M24" s="10">
         <f>ROUND(F24*(1+L24),0)</f>
@@ -4559,57 +4473,52 @@
       </c>
       <c r="S24" s="14" t="inlineStr">
         <is>
-          <t>признаков отставания цены нет</t>
-        </is>
-      </c>
-      <c r="T24" s="14" t="inlineStr">
-        <is>
-          <t>Упак Блины с ветчиной и сыром (3шт) · RP* Упак Блины с ветчиной и сыром (3шт)</t>
+          <t>за 8 мес цена выросла на 3.1% при ориентире 5.3%; берут на 32% больше</t>
         </is>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>Самса с говядиной (30 шт гофра)</t>
+          <t>Клаб Сэндвич с курицей (1шт)</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>Выпечка_</t>
-        </is>
-      </c>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>2 — следом + 2-й шаг</t>
+          <t>СЭНДВИЧИ</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>— не трогать</t>
         </is>
       </c>
       <c r="D25" s="16" t="n">
-        <v>2627782</v>
+        <v>2584803</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>385</v>
+        <v>4985</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>6831</v>
+        <v>519</v>
       </c>
       <c r="G25" s="17" t="n">
-        <v>-0.02818816478082753</v>
+        <v>0.05485859903578372</v>
       </c>
       <c r="H25" s="18" t="n">
         <v>8</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>0.4429999999999999</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>0.7379518072289157</v>
+        <v>0.1839917662892883</v>
       </c>
       <c r="K25" s="17" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L25" s="13" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="M25" s="16">
         <f>ROUND(F25*(1+L25),0)</f>
@@ -4637,19 +4546,14 @@
       </c>
       <c r="S25" s="19" t="inlineStr">
         <is>
-          <t>за 8 мес цена упала на 2.8% при ориентире 5.3%; маржа 44% — тоньше заводской; берут на 74% больше. Расчёт просит 12.5% — остальное вторым шагом через квартал</t>
-        </is>
-      </c>
-      <c r="T25" s="19" t="inlineStr">
-        <is>
-          <t>Упак Самса с говядиной готов ФЗ СМ (30 шт гофра)</t>
+          <t>признаков отставания цены нет</t>
         </is>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Самса с курицей (30шт гофра )</t>
+          <t>Круассан миндальный (10 шт гофра)</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -4659,35 +4563,35 @@
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>2 — следом + 2-й шаг</t>
+          <t>2 — следом</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>2612647</v>
+        <v>2571717</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>385</v>
+        <v>354</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>6786</v>
+        <v>7272</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>-0.02307711041129701</v>
+        <v>-0.003755966336836836</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>0.613</v>
+        <v>0.594</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>0.6176470588235294</v>
+        <v>0.4357239512855211</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L26" s="13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M26" s="10">
         <f>ROUND(F26*(1+L26),0)</f>
@@ -4715,24 +4619,19 @@
       </c>
       <c r="S26" s="14" t="inlineStr">
         <is>
-          <t>за 8 мес цена упала на 2.3% при ориентире 5.3%; берут на 62% больше. Расчёт просит 9.0% — остальное вторым шагом через квартал</t>
-        </is>
-      </c>
-      <c r="T26" s="14" t="inlineStr">
-        <is>
-          <t>Упак Самса с курицей готов ФЗ СМ (30шт гофра )</t>
+          <t>за 8 мес цена упала на 0.4% при ориентире 5.3%; берут на 44% больше</t>
         </is>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>Круассан с индейкой (1шт)</t>
+          <t>Шницель куриный с картофельным пюре (1порц)</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>СЭНДВИЧИ</t>
+          <t>Горячее</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -4741,31 +4640,31 @@
         </is>
       </c>
       <c r="D27" s="16" t="n">
-        <v>2604922</v>
+        <v>2553371</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>4286</v>
+        <v>2918</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>608</v>
+        <v>875</v>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.03115280716362023</v>
+        <v>0.04001774330608066</v>
       </c>
       <c r="H27" s="18" t="n">
         <v>8</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>0.609</v>
+        <v>0.544</v>
       </c>
       <c r="J27" s="17" t="n">
-        <v>0.3193104863533758</v>
+        <v>0.4051364365971108</v>
       </c>
       <c r="K27" s="17" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="L27" s="13" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="M27" s="16">
         <f>ROUND(F27*(1+L27),0)</f>
@@ -4793,12 +4692,7 @@
       </c>
       <c r="S27" s="19" t="inlineStr">
         <is>
-          <t>за 8 мес цена выросла на 3.1% при ориентире 5.3%; берут на 32% больше</t>
-        </is>
-      </c>
-      <c r="T27" s="19" t="inlineStr">
-        <is>
-          <t>Упак Круассан с индейкой (1шт)</t>
+          <t>за 8 мес цена выросла на 4.0% при ориентире 5.3%; берут на 41% больше</t>
         </is>
       </c>
     </row>
@@ -4847,10 +4741,9 @@
         <f>"Прирост к нынешней валовой прибыли этих позиций: "&amp;TEXT(O28/SUMPRODUCT(D8:D27,I8:I27),"0.0%")</f>
         <v/>
       </c>
-      <c r="T28" s="24" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A7:T27"/>
+  <autoFilter ref="A7:S27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4954,34 +4847,34 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>10296</v>
+        <v>11525</v>
       </c>
       <c r="D5" s="30" t="n">
-        <v>7263</v>
+        <v>9202</v>
       </c>
       <c r="E5" s="30" t="n">
-        <v>7107</v>
+        <v>7146</v>
       </c>
       <c r="F5" s="30" t="n">
-        <v>7102</v>
+        <v>7116</v>
       </c>
       <c r="G5" s="30" t="n">
-        <v>7077</v>
+        <v>7070</v>
       </c>
       <c r="H5" s="30" t="n">
-        <v>7066</v>
+        <v>7055</v>
       </c>
       <c r="I5" s="30" t="n">
-        <v>7123</v>
+        <v>7005</v>
       </c>
       <c r="J5" s="30" t="n">
-        <v>7010</v>
+        <v>7012</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 51%</t>
+          <t>Выпечка_ · маржа 52%</t>
         </is>
       </c>
       <c r="B6" s="29" t="inlineStr">
@@ -4990,28 +4883,28 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>170</v>
+        <v>40</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>118</v>
+        <v>25</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>563</v>
+        <v>422</v>
       </c>
       <c r="F6" s="32" t="n">
-        <v>1101</v>
+        <v>982</v>
       </c>
       <c r="G6" s="32" t="n">
-        <v>1369</v>
+        <v>1220</v>
       </c>
       <c r="H6" s="32" t="n">
-        <v>1646</v>
+        <v>1406</v>
       </c>
       <c r="I6" s="32" t="n">
-        <v>780</v>
+        <v>322</v>
       </c>
       <c r="J6" s="32" t="n">
-        <v>2456</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="21">
@@ -5026,28 +4919,28 @@
         </is>
       </c>
       <c r="C21" s="30" t="n">
-        <v>8795</v>
+        <v>8717</v>
       </c>
       <c r="D21" s="30" t="n">
-        <v>9210</v>
+        <v>9156</v>
       </c>
       <c r="E21" s="30" t="n">
-        <v>9434</v>
+        <v>9296</v>
       </c>
       <c r="F21" s="30" t="n">
-        <v>9473</v>
+        <v>9286</v>
       </c>
       <c r="G21" s="30" t="n">
-        <v>9406</v>
+        <v>9431</v>
       </c>
       <c r="H21" s="30" t="n">
-        <v>9349</v>
+        <v>9394</v>
       </c>
       <c r="I21" s="30" t="n">
-        <v>9358</v>
+        <v>9408</v>
       </c>
       <c r="J21" s="30" t="n">
-        <v>9377</v>
+        <v>9266</v>
       </c>
     </row>
     <row r="22">
@@ -5062,28 +4955,28 @@
         </is>
       </c>
       <c r="C22" s="32" t="n">
-        <v>838</v>
+        <v>239</v>
       </c>
       <c r="D22" s="32" t="n">
-        <v>628</v>
+        <v>355</v>
       </c>
       <c r="E22" s="32" t="n">
-        <v>869</v>
+        <v>502</v>
       </c>
       <c r="F22" s="32" t="n">
-        <v>707</v>
+        <v>384</v>
       </c>
       <c r="G22" s="32" t="n">
-        <v>714</v>
+        <v>420</v>
       </c>
       <c r="H22" s="32" t="n">
-        <v>943</v>
+        <v>599</v>
       </c>
       <c r="I22" s="32" t="n">
-        <v>1315</v>
+        <v>1065</v>
       </c>
       <c r="J22" s="32" t="n">
-        <v>953</v>
+        <v>452</v>
       </c>
     </row>
     <row r="37">
@@ -5176,7 +5069,7 @@
         <v>930</v>
       </c>
       <c r="E53" s="30" t="n">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="F53" s="30" t="n">
         <v>924</v>
@@ -5212,16 +5105,16 @@
         <v>3002</v>
       </c>
       <c r="E54" s="32" t="n">
-        <v>4640</v>
+        <v>4634</v>
       </c>
       <c r="F54" s="32" t="n">
-        <v>4216</v>
+        <v>4201</v>
       </c>
       <c r="G54" s="32" t="n">
-        <v>5776</v>
+        <v>5767</v>
       </c>
       <c r="H54" s="32" t="n">
-        <v>5179</v>
+        <v>5177</v>
       </c>
       <c r="I54" s="32" t="n">
         <v>4921</v>
@@ -5233,7 +5126,7 @@
     <row r="69">
       <c r="A69" s="28" t="inlineStr">
         <is>
-          <t>Пирожок с курицей и сыром (30 шт гофра)</t>
+          <t>Кимпаб с тунцом (1шт)</t>
         </is>
       </c>
       <c r="B69" s="29" t="inlineStr">
@@ -5242,34 +5135,34 @@
         </is>
       </c>
       <c r="C69" s="30" t="n">
-        <v>4975</v>
+        <v>855</v>
       </c>
       <c r="D69" s="30" t="n">
-        <v>5256</v>
+        <v>871</v>
       </c>
       <c r="E69" s="30" t="n">
-        <v>5348</v>
+        <v>875</v>
       </c>
       <c r="F69" s="30" t="n">
-        <v>5270</v>
+        <v>874</v>
       </c>
       <c r="G69" s="30" t="n">
-        <v>5354</v>
+        <v>879</v>
       </c>
       <c r="H69" s="30" t="n">
-        <v>5220</v>
+        <v>878</v>
       </c>
       <c r="I69" s="30" t="n">
-        <v>5294</v>
+        <v>970</v>
       </c>
       <c r="J69" s="30" t="n">
-        <v>5280</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 50%</t>
+          <t>Япония · маржа 54%</t>
         </is>
       </c>
       <c r="B70" s="29" t="inlineStr">
@@ -5278,34 +5171,34 @@
         </is>
       </c>
       <c r="C70" s="32" t="n">
-        <v>711</v>
+        <v>4068</v>
       </c>
       <c r="D70" s="32" t="n">
-        <v>584</v>
+        <v>4158</v>
       </c>
       <c r="E70" s="32" t="n">
-        <v>791</v>
+        <v>3935</v>
       </c>
       <c r="F70" s="32" t="n">
-        <v>567</v>
+        <v>4522</v>
       </c>
       <c r="G70" s="32" t="n">
-        <v>688</v>
+        <v>4734</v>
       </c>
       <c r="H70" s="32" t="n">
-        <v>879</v>
+        <v>5532</v>
       </c>
       <c r="I70" s="32" t="n">
-        <v>1123</v>
+        <v>5257</v>
       </c>
       <c r="J70" s="32" t="n">
-        <v>937</v>
+        <v>5347</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="28" t="inlineStr">
         <is>
-          <t>Кимпаб с тунцом (1шт)</t>
+          <t>Кимпаб с курицей (1шт)</t>
         </is>
       </c>
       <c r="B85" s="29" t="inlineStr">
@@ -5314,34 +5207,34 @@
         </is>
       </c>
       <c r="C85" s="30" t="n">
-        <v>855</v>
+        <v>737</v>
       </c>
       <c r="D85" s="30" t="n">
-        <v>871</v>
+        <v>751</v>
       </c>
       <c r="E85" s="30" t="n">
-        <v>875</v>
+        <v>765</v>
       </c>
       <c r="F85" s="30" t="n">
-        <v>874</v>
+        <v>774</v>
       </c>
       <c r="G85" s="30" t="n">
-        <v>879</v>
+        <v>781</v>
       </c>
       <c r="H85" s="30" t="n">
-        <v>878</v>
+        <v>760</v>
       </c>
       <c r="I85" s="30" t="n">
-        <v>970</v>
+        <v>822</v>
       </c>
       <c r="J85" s="30" t="n">
-        <v>1002</v>
+        <v>853</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="31" t="inlineStr">
         <is>
-          <t>Япония · маржа 54%</t>
+          <t>Япония · маржа 49%</t>
         </is>
       </c>
       <c r="B86" s="29" t="inlineStr">
@@ -5350,34 +5243,34 @@
         </is>
       </c>
       <c r="C86" s="32" t="n">
-        <v>4068</v>
+        <v>4157</v>
       </c>
       <c r="D86" s="32" t="n">
-        <v>4158</v>
+        <v>4351</v>
       </c>
       <c r="E86" s="32" t="n">
-        <v>3935</v>
+        <v>4206</v>
       </c>
       <c r="F86" s="32" t="n">
-        <v>4522</v>
+        <v>4969</v>
       </c>
       <c r="G86" s="32" t="n">
-        <v>4734</v>
+        <v>5203</v>
       </c>
       <c r="H86" s="32" t="n">
-        <v>5532</v>
+        <v>5595</v>
       </c>
       <c r="I86" s="32" t="n">
-        <v>5257</v>
+        <v>5188</v>
       </c>
       <c r="J86" s="32" t="n">
-        <v>5347</v>
+        <v>5267</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="28" t="inlineStr">
         <is>
-          <t>Кимпаб с курицей (1шт)</t>
+          <t>Курица с сыром и картофельным пюре (1порц)</t>
         </is>
       </c>
       <c r="B101" s="29" t="inlineStr">
@@ -5386,34 +5279,34 @@
         </is>
       </c>
       <c r="C101" s="30" t="n">
-        <v>737</v>
+        <v>1027</v>
       </c>
       <c r="D101" s="30" t="n">
-        <v>751</v>
+        <v>1042</v>
       </c>
       <c r="E101" s="30" t="n">
-        <v>765</v>
+        <v>1075</v>
       </c>
       <c r="F101" s="30" t="n">
-        <v>774</v>
+        <v>1076</v>
       </c>
       <c r="G101" s="30" t="n">
-        <v>781</v>
+        <v>1135</v>
       </c>
       <c r="H101" s="30" t="n">
-        <v>760</v>
+        <v>1117</v>
       </c>
       <c r="I101" s="30" t="n">
-        <v>822</v>
+        <v>1125</v>
       </c>
       <c r="J101" s="30" t="n">
-        <v>853</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="31" t="inlineStr">
         <is>
-          <t>Япония · маржа 49%</t>
+          <t>Горячее · маржа 58%</t>
         </is>
       </c>
       <c r="B102" s="29" t="inlineStr">
@@ -5422,34 +5315,34 @@
         </is>
       </c>
       <c r="C102" s="32" t="n">
-        <v>4157</v>
+        <v>2525</v>
       </c>
       <c r="D102" s="32" t="n">
-        <v>4351</v>
+        <v>2315</v>
       </c>
       <c r="E102" s="32" t="n">
-        <v>4206</v>
+        <v>2676</v>
       </c>
       <c r="F102" s="32" t="n">
-        <v>4969</v>
+        <v>2774</v>
       </c>
       <c r="G102" s="32" t="n">
-        <v>5203</v>
+        <v>4267</v>
       </c>
       <c r="H102" s="32" t="n">
-        <v>5595</v>
+        <v>4300</v>
       </c>
       <c r="I102" s="32" t="n">
-        <v>5188</v>
+        <v>3609</v>
       </c>
       <c r="J102" s="32" t="n">
-        <v>5267</v>
+        <v>3534</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="28" t="inlineStr">
         <is>
-          <t>Курица с сыром и картофельным пюре (1порц)</t>
+          <t>Курица с сыром с рисом и паутини (1порц)</t>
         </is>
       </c>
       <c r="B117" s="29" t="inlineStr">
@@ -5458,28 +5351,28 @@
         </is>
       </c>
       <c r="C117" s="30" t="n">
-        <v>1027</v>
+        <v>1003</v>
       </c>
       <c r="D117" s="30" t="n">
-        <v>1042</v>
+        <v>1020</v>
       </c>
       <c r="E117" s="30" t="n">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="F117" s="30" t="n">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="G117" s="30" t="n">
-        <v>1135</v>
+        <v>1064</v>
       </c>
       <c r="H117" s="30" t="n">
-        <v>1117</v>
+        <v>1043</v>
       </c>
       <c r="I117" s="30" t="n">
-        <v>1125</v>
+        <v>1092</v>
       </c>
       <c r="J117" s="30" t="n">
-        <v>1137</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="118">
@@ -5494,34 +5387,34 @@
         </is>
       </c>
       <c r="C118" s="32" t="n">
-        <v>2525</v>
+        <v>2254</v>
       </c>
       <c r="D118" s="32" t="n">
-        <v>2315</v>
+        <v>2108</v>
       </c>
       <c r="E118" s="32" t="n">
-        <v>2676</v>
+        <v>2608</v>
       </c>
       <c r="F118" s="32" t="n">
-        <v>2774</v>
+        <v>3048</v>
       </c>
       <c r="G118" s="32" t="n">
-        <v>4267</v>
+        <v>3227</v>
       </c>
       <c r="H118" s="32" t="n">
-        <v>4300</v>
+        <v>3859</v>
       </c>
       <c r="I118" s="32" t="n">
-        <v>3609</v>
+        <v>3501</v>
       </c>
       <c r="J118" s="32" t="n">
-        <v>3534</v>
+        <v>3185</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="28" t="inlineStr">
         <is>
-          <t>Курица с сыром с рисом и паутини (1порц)</t>
+          <t>Пирожок с курицей и сыром (30 шт гофра)</t>
         </is>
       </c>
       <c r="B133" s="29" t="inlineStr">
@@ -5530,34 +5423,34 @@
         </is>
       </c>
       <c r="C133" s="30" t="n">
-        <v>1003</v>
+        <v>5062</v>
       </c>
       <c r="D133" s="30" t="n">
-        <v>1020</v>
+        <v>5294</v>
       </c>
       <c r="E133" s="30" t="n">
-        <v>1071</v>
+        <v>5344</v>
       </c>
       <c r="F133" s="30" t="n">
-        <v>1074</v>
+        <v>5332</v>
       </c>
       <c r="G133" s="30" t="n">
-        <v>1064</v>
+        <v>5399</v>
       </c>
       <c r="H133" s="30" t="n">
-        <v>1043</v>
+        <v>5341</v>
       </c>
       <c r="I133" s="30" t="n">
-        <v>1092</v>
+        <v>5374</v>
       </c>
       <c r="J133" s="30" t="n">
-        <v>1115</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 58%</t>
+          <t>Выпечка_ · маржа 51%</t>
         </is>
       </c>
       <c r="B134" s="29" t="inlineStr">
@@ -5566,34 +5459,34 @@
         </is>
       </c>
       <c r="C134" s="32" t="n">
-        <v>2254</v>
+        <v>228</v>
       </c>
       <c r="D134" s="32" t="n">
-        <v>2108</v>
+        <v>405</v>
       </c>
       <c r="E134" s="32" t="n">
-        <v>2608</v>
+        <v>547</v>
       </c>
       <c r="F134" s="32" t="n">
-        <v>3048</v>
+        <v>377</v>
       </c>
       <c r="G134" s="32" t="n">
-        <v>3227</v>
+        <v>478</v>
       </c>
       <c r="H134" s="32" t="n">
-        <v>3859</v>
+        <v>618</v>
       </c>
       <c r="I134" s="32" t="n">
-        <v>3501</v>
+        <v>937</v>
       </c>
       <c r="J134" s="32" t="n">
-        <v>3185</v>
+        <v>486</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="28" t="inlineStr">
         <is>
-          <t>Пирожок с картофелем (30 шт гофра)</t>
+          <t>Сосиска в тесте (30шт гофра)</t>
         </is>
       </c>
       <c r="B149" s="29" t="inlineStr">
@@ -5602,34 +5495,34 @@
         </is>
       </c>
       <c r="C149" s="30" t="n">
-        <v>5445</v>
+        <v>8827</v>
       </c>
       <c r="D149" s="30" t="n">
-        <v>872</v>
+        <v>9282</v>
       </c>
       <c r="E149" s="30" t="n">
-        <v>4427</v>
+        <v>9623</v>
       </c>
       <c r="F149" s="30" t="n">
-        <v>4820</v>
+        <v>9696</v>
       </c>
       <c r="G149" s="30" t="n">
-        <v>4804</v>
+        <v>9369</v>
       </c>
       <c r="H149" s="30" t="n">
-        <v>4116</v>
+        <v>9271</v>
       </c>
       <c r="I149" s="30" t="n">
-        <v>4801</v>
+        <v>9146</v>
       </c>
       <c r="J149" s="30" t="n">
-        <v>4748</v>
+        <v>9477</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 60%</t>
+          <t>Выпечка_ · маржа 59%</t>
         </is>
       </c>
       <c r="B150" s="29" t="inlineStr">
@@ -5638,34 +5531,34 @@
         </is>
       </c>
       <c r="C150" s="32" t="n">
-        <v>60</v>
+        <v>599</v>
       </c>
       <c r="D150" s="32" t="n">
-        <v>182</v>
+        <v>273</v>
       </c>
       <c r="E150" s="32" t="n">
-        <v>550</v>
+        <v>367</v>
       </c>
       <c r="F150" s="32" t="n">
-        <v>402</v>
+        <v>323</v>
       </c>
       <c r="G150" s="32" t="n">
-        <v>451</v>
+        <v>294</v>
       </c>
       <c r="H150" s="32" t="n">
-        <v>751</v>
+        <v>344</v>
       </c>
       <c r="I150" s="32" t="n">
-        <v>971</v>
+        <v>250</v>
       </c>
       <c r="J150" s="32" t="n">
-        <v>756</v>
+        <v>501</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="28" t="inlineStr">
         <is>
-          <t>Маффин шоколадный (24шт)</t>
+          <t>Манты с говядиной (1порц)</t>
         </is>
       </c>
       <c r="B165" s="29" t="inlineStr">
@@ -5674,34 +5567,34 @@
         </is>
       </c>
       <c r="C165" s="30" t="n">
-        <v>7362</v>
+        <v>831</v>
       </c>
       <c r="D165" s="30" t="n">
-        <v>7317</v>
+        <v>801</v>
       </c>
       <c r="E165" s="30" t="n">
-        <v>7431</v>
+        <v>791</v>
       </c>
       <c r="F165" s="30" t="n">
-        <v>7492</v>
+        <v>795</v>
       </c>
       <c r="G165" s="30" t="n">
-        <v>7496</v>
+        <v>848</v>
       </c>
       <c r="H165" s="30" t="n">
-        <v>7329</v>
+        <v>790</v>
       </c>
       <c r="I165" s="30" t="n">
-        <v>7335</v>
+        <v>873</v>
       </c>
       <c r="J165" s="30" t="n">
-        <v>7358</v>
+        <v>939</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 48%</t>
+          <t>Горячее · маржа 42%</t>
         </is>
       </c>
       <c r="B166" s="29" t="inlineStr">
@@ -5710,34 +5603,34 @@
         </is>
       </c>
       <c r="C166" s="32" t="n">
-        <v>293</v>
+        <v>3204</v>
       </c>
       <c r="D166" s="32" t="n">
-        <v>324</v>
+        <v>3017</v>
       </c>
       <c r="E166" s="32" t="n">
-        <v>387</v>
+        <v>3920</v>
       </c>
       <c r="F166" s="32" t="n">
-        <v>523</v>
+        <v>3319</v>
       </c>
       <c r="G166" s="32" t="n">
-        <v>369</v>
+        <v>3164</v>
       </c>
       <c r="H166" s="32" t="n">
-        <v>392</v>
+        <v>3665</v>
       </c>
       <c r="I166" s="32" t="n">
-        <v>456</v>
+        <v>3234</v>
       </c>
       <c r="J166" s="32" t="n">
-        <v>598</v>
+        <v>3453</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="28" t="inlineStr">
         <is>
-          <t>Круассан миндальный (10 шт гофра)</t>
+          <t>Пирожок с картофелем (30 шт гофра)</t>
         </is>
       </c>
       <c r="B181" s="29" t="inlineStr">
@@ -5745,35 +5638,33 @@
           <t>Цена, ₸</t>
         </is>
       </c>
-      <c r="C181" s="30" t="n">
-        <v>6768</v>
-      </c>
+      <c r="C181" s="30" t="n"/>
       <c r="D181" s="30" t="n">
-        <v>6823</v>
+        <v>88</v>
       </c>
       <c r="E181" s="30" t="n">
-        <v>7177</v>
+        <v>4400</v>
       </c>
       <c r="F181" s="30" t="n">
-        <v>7129</v>
+        <v>4765</v>
       </c>
       <c r="G181" s="30" t="n">
-        <v>7044</v>
+        <v>4871</v>
       </c>
       <c r="H181" s="30" t="n">
-        <v>7008</v>
+        <v>4789</v>
       </c>
       <c r="I181" s="30" t="n">
-        <v>7213</v>
+        <v>4832</v>
       </c>
       <c r="J181" s="30" t="n">
-        <v>6946</v>
+        <v>4768</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 59%</t>
+          <t>Выпечка_ · маржа 62%</t>
         </is>
       </c>
       <c r="B182" s="29" t="inlineStr">
@@ -5782,34 +5673,34 @@
         </is>
       </c>
       <c r="C182" s="32" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="D182" s="32" t="n">
-        <v>265</v>
+        <v>155</v>
       </c>
       <c r="E182" s="32" t="n">
-        <v>335</v>
+        <v>506</v>
       </c>
       <c r="F182" s="32" t="n">
-        <v>376</v>
+        <v>330</v>
       </c>
       <c r="G182" s="32" t="n">
-        <v>293</v>
+        <v>370</v>
       </c>
       <c r="H182" s="32" t="n">
-        <v>421</v>
+        <v>507</v>
       </c>
       <c r="I182" s="32" t="n">
-        <v>567</v>
+        <v>875</v>
       </c>
       <c r="J182" s="32" t="n">
-        <v>444</v>
+        <v>454</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="28" t="inlineStr">
         <is>
-          <t>Пирожок с капустой (30 шт гофра)</t>
+          <t>Бризоль с рисом (1порц)</t>
         </is>
       </c>
       <c r="B197" s="29" t="inlineStr">
@@ -5818,34 +5709,34 @@
         </is>
       </c>
       <c r="C197" s="30" t="n">
-        <v>4310</v>
+        <v>1149</v>
       </c>
       <c r="D197" s="30" t="n">
-        <v>4715</v>
+        <v>1154</v>
       </c>
       <c r="E197" s="30" t="n">
-        <v>4746</v>
+        <v>1226</v>
       </c>
       <c r="F197" s="30" t="n">
-        <v>4788</v>
+        <v>1202</v>
       </c>
       <c r="G197" s="30" t="n">
-        <v>4792</v>
+        <v>1207</v>
       </c>
       <c r="H197" s="30" t="n">
-        <v>3492</v>
+        <v>1188</v>
       </c>
       <c r="I197" s="30" t="n">
-        <v>4647</v>
+        <v>1179</v>
       </c>
       <c r="J197" s="30" t="n">
-        <v>4723</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 62%</t>
+          <t>Горячее · маржа 37%</t>
         </is>
       </c>
       <c r="B198" s="29" t="inlineStr">
@@ -5854,34 +5745,34 @@
         </is>
       </c>
       <c r="C198" s="32" t="n">
-        <v>381</v>
+        <v>1835</v>
       </c>
       <c r="D198" s="32" t="n">
-        <v>349</v>
+        <v>1583</v>
       </c>
       <c r="E198" s="32" t="n">
-        <v>496</v>
+        <v>1421</v>
       </c>
       <c r="F198" s="32" t="n">
-        <v>446</v>
+        <v>1789</v>
       </c>
       <c r="G198" s="32" t="n">
-        <v>454</v>
+        <v>1816</v>
       </c>
       <c r="H198" s="32" t="n">
-        <v>829</v>
+        <v>2234</v>
       </c>
       <c r="I198" s="32" t="n">
-        <v>724</v>
+        <v>2204</v>
       </c>
       <c r="J198" s="32" t="n">
-        <v>714</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="28" t="inlineStr">
         <is>
-          <t>Манты с говядиной (1порц)</t>
+          <t>Блины с ветчиной и сыром (3шт)</t>
         </is>
       </c>
       <c r="B213" s="29" t="inlineStr">
@@ -5890,34 +5781,34 @@
         </is>
       </c>
       <c r="C213" s="30" t="n">
-        <v>831</v>
+        <v>863</v>
       </c>
       <c r="D213" s="30" t="n">
-        <v>801</v>
+        <v>853</v>
       </c>
       <c r="E213" s="30" t="n">
-        <v>790</v>
+        <v>896</v>
       </c>
       <c r="F213" s="30" t="n">
-        <v>795</v>
+        <v>858</v>
       </c>
       <c r="G213" s="30" t="n">
-        <v>848</v>
+        <v>885</v>
       </c>
       <c r="H213" s="30" t="n">
-        <v>790</v>
+        <v>897</v>
       </c>
       <c r="I213" s="30" t="n">
-        <v>873</v>
+        <v>924</v>
       </c>
       <c r="J213" s="30" t="n">
-        <v>939</v>
+        <v>961</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 42%</t>
+          <t>Завтраки · маржа 49%</t>
         </is>
       </c>
       <c r="B214" s="29" t="inlineStr">
@@ -5926,34 +5817,34 @@
         </is>
       </c>
       <c r="C214" s="32" t="n">
-        <v>3204</v>
+        <v>2211</v>
       </c>
       <c r="D214" s="32" t="n">
-        <v>3017</v>
+        <v>2131</v>
       </c>
       <c r="E214" s="32" t="n">
-        <v>3925</v>
+        <v>2922</v>
       </c>
       <c r="F214" s="32" t="n">
-        <v>3334</v>
+        <v>2412</v>
       </c>
       <c r="G214" s="32" t="n">
-        <v>3173</v>
+        <v>2638</v>
       </c>
       <c r="H214" s="32" t="n">
-        <v>3667</v>
+        <v>2729</v>
       </c>
       <c r="I214" s="32" t="n">
-        <v>3234</v>
+        <v>2832</v>
       </c>
       <c r="J214" s="32" t="n">
-        <v>3453</v>
+        <v>2945</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="28" t="inlineStr">
         <is>
-          <t>Сочник творожный (30шт гофра )</t>
+          <t>Самса с говядиной (30 шт гофра)</t>
         </is>
       </c>
       <c r="B229" s="29" t="inlineStr">
@@ -5962,34 +5853,34 @@
         </is>
       </c>
       <c r="C229" s="30" t="n">
-        <v>7012</v>
+        <v>7098</v>
       </c>
       <c r="D229" s="30" t="n">
-        <v>6983</v>
+        <v>6977</v>
       </c>
       <c r="E229" s="30" t="n">
-        <v>7182</v>
+        <v>7003</v>
       </c>
       <c r="F229" s="30" t="n">
-        <v>7137</v>
+        <v>6964</v>
       </c>
       <c r="G229" s="30" t="n">
-        <v>7249</v>
+        <v>6862</v>
       </c>
       <c r="H229" s="30" t="n">
-        <v>6963</v>
+        <v>6912</v>
       </c>
       <c r="I229" s="30" t="n">
-        <v>6912</v>
+        <v>6774</v>
       </c>
       <c r="J229" s="30" t="n">
-        <v>6814</v>
+        <v>6805</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 61%</t>
+          <t>Выпечка_ · маржа 44%</t>
         </is>
       </c>
       <c r="B230" s="29" t="inlineStr">
@@ -5998,34 +5889,34 @@
         </is>
       </c>
       <c r="C230" s="32" t="n">
+        <v>186</v>
+      </c>
+      <c r="D230" s="32" t="n">
+        <v>130</v>
+      </c>
+      <c r="E230" s="32" t="n">
+        <v>217</v>
+      </c>
+      <c r="F230" s="32" t="n">
         <v>210</v>
       </c>
-      <c r="D230" s="32" t="n">
-        <v>169</v>
-      </c>
-      <c r="E230" s="32" t="n">
-        <v>231</v>
-      </c>
-      <c r="F230" s="32" t="n">
-        <v>306</v>
-      </c>
       <c r="G230" s="32" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H230" s="32" t="n">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="I230" s="32" t="n">
-        <v>418</v>
+        <v>256</v>
       </c>
       <c r="J230" s="32" t="n">
-        <v>461</v>
+        <v>541</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="28" t="inlineStr">
         <is>
-          <t>Бризоль с рисом (1порц)</t>
+          <t>Самса с курицей (30шт гофра )</t>
         </is>
       </c>
       <c r="B245" s="29" t="inlineStr">
@@ -6034,34 +5925,34 @@
         </is>
       </c>
       <c r="C245" s="30" t="n">
-        <v>1149</v>
+        <v>6935</v>
       </c>
       <c r="D245" s="30" t="n">
-        <v>1154</v>
+        <v>6925</v>
       </c>
       <c r="E245" s="30" t="n">
-        <v>1226</v>
+        <v>6901</v>
       </c>
       <c r="F245" s="30" t="n">
-        <v>1202</v>
+        <v>6983</v>
       </c>
       <c r="G245" s="30" t="n">
-        <v>1207</v>
+        <v>6703</v>
       </c>
       <c r="H245" s="30" t="n">
-        <v>1188</v>
+        <v>6897</v>
       </c>
       <c r="I245" s="30" t="n">
-        <v>1179</v>
+        <v>6710</v>
       </c>
       <c r="J245" s="30" t="n">
-        <v>1182</v>
+        <v>6765</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 37%</t>
+          <t>Выпечка_ · маржа 61%</t>
         </is>
       </c>
       <c r="B246" s="29" t="inlineStr">
@@ -6070,34 +5961,34 @@
         </is>
       </c>
       <c r="C246" s="32" t="n">
-        <v>1835</v>
+        <v>218</v>
       </c>
       <c r="D246" s="32" t="n">
-        <v>1583</v>
+        <v>161</v>
       </c>
       <c r="E246" s="32" t="n">
-        <v>1421</v>
+        <v>211</v>
       </c>
       <c r="F246" s="32" t="n">
-        <v>1789</v>
+        <v>253</v>
       </c>
       <c r="G246" s="32" t="n">
-        <v>1816</v>
+        <v>250</v>
       </c>
       <c r="H246" s="32" t="n">
-        <v>2234</v>
+        <v>301</v>
       </c>
       <c r="I246" s="32" t="n">
-        <v>2204</v>
+        <v>285</v>
       </c>
       <c r="J246" s="32" t="n">
-        <v>2244</v>
+        <v>569</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="28" t="inlineStr">
         <is>
-          <t>Блины с ветчиной и сыром (3шт)</t>
+          <t>Круассан с индейкой (1шт)</t>
         </is>
       </c>
       <c r="B261" s="29" t="inlineStr">
@@ -6106,34 +5997,34 @@
         </is>
       </c>
       <c r="C261" s="30" t="n">
-        <v>863</v>
+        <v>590</v>
       </c>
       <c r="D261" s="30" t="n">
-        <v>853</v>
+        <v>599</v>
       </c>
       <c r="E261" s="30" t="n">
-        <v>894</v>
+        <v>593</v>
       </c>
       <c r="F261" s="30" t="n">
-        <v>858</v>
+        <v>577</v>
       </c>
       <c r="G261" s="30" t="n">
-        <v>884</v>
+        <v>587</v>
       </c>
       <c r="H261" s="30" t="n">
-        <v>897</v>
+        <v>595</v>
       </c>
       <c r="I261" s="30" t="n">
-        <v>924</v>
+        <v>611</v>
       </c>
       <c r="J261" s="30" t="n">
-        <v>961</v>
+        <v>619</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="31" t="inlineStr">
         <is>
-          <t>Завтраки · маржа 49%</t>
+          <t>СЭНДВИЧИ · маржа 61%</t>
         </is>
       </c>
       <c r="B262" s="29" t="inlineStr">
@@ -6142,34 +6033,34 @@
         </is>
       </c>
       <c r="C262" s="32" t="n">
-        <v>2211</v>
+        <v>2352</v>
       </c>
       <c r="D262" s="32" t="n">
-        <v>2131</v>
+        <v>2345</v>
       </c>
       <c r="E262" s="32" t="n">
-        <v>2928</v>
+        <v>2472</v>
       </c>
       <c r="F262" s="32" t="n">
-        <v>2427</v>
+        <v>3314</v>
       </c>
       <c r="G262" s="32" t="n">
-        <v>2648</v>
+        <v>3960</v>
       </c>
       <c r="H262" s="32" t="n">
-        <v>2730</v>
+        <v>4761</v>
       </c>
       <c r="I262" s="32" t="n">
-        <v>2832</v>
+        <v>4156</v>
       </c>
       <c r="J262" s="32" t="n">
-        <v>2945</v>
+        <v>3941</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="28" t="inlineStr">
         <is>
-          <t>Самса с говядиной (30 шт гофра)</t>
+          <t>Клаб Сэндвич с курицей (1шт)</t>
         </is>
       </c>
       <c r="B277" s="29" t="inlineStr">
@@ -6178,34 +6069,34 @@
         </is>
       </c>
       <c r="C277" s="30" t="n">
-        <v>7098</v>
+        <v>488</v>
       </c>
       <c r="D277" s="30" t="n">
-        <v>6977</v>
+        <v>489</v>
       </c>
       <c r="E277" s="30" t="n">
-        <v>7003</v>
+        <v>512</v>
       </c>
       <c r="F277" s="30" t="n">
-        <v>6964</v>
+        <v>506</v>
       </c>
       <c r="G277" s="30" t="n">
-        <v>6862</v>
+        <v>509</v>
       </c>
       <c r="H277" s="30" t="n">
-        <v>6912</v>
+        <v>514</v>
       </c>
       <c r="I277" s="30" t="n">
-        <v>6774</v>
+        <v>516</v>
       </c>
       <c r="J277" s="30" t="n">
-        <v>6805</v>
+        <v>524</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 44%</t>
+          <t>СЭНДВИЧИ · маржа 56%</t>
         </is>
       </c>
       <c r="B278" s="29" t="inlineStr">
@@ -6214,34 +6105,34 @@
         </is>
       </c>
       <c r="C278" s="32" t="n">
-        <v>186</v>
+        <v>3237</v>
       </c>
       <c r="D278" s="32" t="n">
-        <v>130</v>
+        <v>3273</v>
       </c>
       <c r="E278" s="32" t="n">
-        <v>217</v>
+        <v>4099</v>
       </c>
       <c r="F278" s="32" t="n">
-        <v>210</v>
+        <v>4262</v>
       </c>
       <c r="G278" s="32" t="n">
-        <v>237</v>
+        <v>4270</v>
       </c>
       <c r="H278" s="32" t="n">
-        <v>357</v>
+        <v>4191</v>
       </c>
       <c r="I278" s="32" t="n">
-        <v>256</v>
+        <v>5051</v>
       </c>
       <c r="J278" s="32" t="n">
-        <v>541</v>
+        <v>5713</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="28" t="inlineStr">
         <is>
-          <t>Самса с курицей (30шт гофра )</t>
+          <t>Круассан миндальный (10 шт гофра)</t>
         </is>
       </c>
       <c r="B293" s="29" t="inlineStr">
@@ -6250,34 +6141,34 @@
         </is>
       </c>
       <c r="C293" s="30" t="n">
-        <v>6935</v>
+        <v>7232</v>
       </c>
       <c r="D293" s="30" t="n">
-        <v>6925</v>
+        <v>7166</v>
       </c>
       <c r="E293" s="30" t="n">
-        <v>6901</v>
+        <v>7239</v>
       </c>
       <c r="F293" s="30" t="n">
-        <v>6983</v>
+        <v>7196</v>
       </c>
       <c r="G293" s="30" t="n">
-        <v>6703</v>
+        <v>7412</v>
       </c>
       <c r="H293" s="30" t="n">
-        <v>6897</v>
+        <v>7205</v>
       </c>
       <c r="I293" s="30" t="n">
-        <v>6710</v>
+        <v>7374</v>
       </c>
       <c r="J293" s="30" t="n">
-        <v>6765</v>
+        <v>7155</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 61%</t>
+          <t>Выпечка_ · маржа 59%</t>
         </is>
       </c>
       <c r="B294" s="29" t="inlineStr">
@@ -6286,34 +6177,34 @@
         </is>
       </c>
       <c r="C294" s="32" t="n">
-        <v>218</v>
+        <v>108</v>
       </c>
       <c r="D294" s="32" t="n">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="E294" s="32" t="n">
-        <v>211</v>
+        <v>245</v>
       </c>
       <c r="F294" s="32" t="n">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="G294" s="32" t="n">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="H294" s="32" t="n">
-        <v>301</v>
+        <v>335</v>
       </c>
       <c r="I294" s="32" t="n">
-        <v>285</v>
+        <v>488</v>
       </c>
       <c r="J294" s="32" t="n">
-        <v>569</v>
+        <v>238</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="28" t="inlineStr">
         <is>
-          <t>Круассан с индейкой (1шт)</t>
+          <t>Шницель куриный с картофельным пюре (1порц)</t>
         </is>
       </c>
       <c r="B309" s="29" t="inlineStr">
@@ -6322,34 +6213,34 @@
         </is>
       </c>
       <c r="C309" s="30" t="n">
-        <v>590</v>
+        <v>859</v>
       </c>
       <c r="D309" s="30" t="n">
-        <v>599</v>
+        <v>841</v>
       </c>
       <c r="E309" s="30" t="n">
-        <v>593</v>
+        <v>857</v>
       </c>
       <c r="F309" s="30" t="n">
-        <v>577</v>
+        <v>856</v>
       </c>
       <c r="G309" s="30" t="n">
-        <v>587</v>
+        <v>899</v>
       </c>
       <c r="H309" s="30" t="n">
-        <v>595</v>
+        <v>812</v>
       </c>
       <c r="I309" s="30" t="n">
-        <v>611</v>
+        <v>891</v>
       </c>
       <c r="J309" s="30" t="n">
-        <v>619</v>
+        <v>911</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="31" t="inlineStr">
         <is>
-          <t>СЭНДВИЧИ · маржа 61%</t>
+          <t>Горячее · маржа 54%</t>
         </is>
       </c>
       <c r="B310" s="29" t="inlineStr">
@@ -6358,28 +6249,28 @@
         </is>
       </c>
       <c r="C310" s="32" t="n">
-        <v>2352</v>
+        <v>2443</v>
       </c>
       <c r="D310" s="32" t="n">
-        <v>2345</v>
+        <v>2194</v>
       </c>
       <c r="E310" s="32" t="n">
-        <v>2472</v>
+        <v>1988</v>
       </c>
       <c r="F310" s="32" t="n">
-        <v>3314</v>
+        <v>2128</v>
       </c>
       <c r="G310" s="32" t="n">
-        <v>3960</v>
+        <v>2114</v>
       </c>
       <c r="H310" s="32" t="n">
-        <v>4761</v>
+        <v>2619</v>
       </c>
       <c r="I310" s="32" t="n">
-        <v>4156</v>
+        <v>2763</v>
       </c>
       <c r="J310" s="32" t="n">
-        <v>3941</v>
+        <v>3372</v>
       </c>
     </row>
   </sheetData>
@@ -6394,7 +6285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A24"/>
+  <dimension ref="A2:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -6492,46 +6383,29 @@
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="33" t="inlineStr">
         <is>
-          <t>Почему позиций двадцать, а карточек в iiko больше</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="70" customHeight="1">
+          <t>Как считается «Цена ±»</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
       <c r="A18" s="34" t="inlineStr">
         <is>
-          <t>Часть позиций ведётся в iiko под двумя именами: обычным и с приставкой «RP*» — под ней ту же позицию берёт сеть АЗС. Это одно и то же изделие, поэтому в отчёте оно сведено в одну строку, а из каких карточек оно собрано, написано в последней колонке. Если считать карточки порознь, один товар распадается на две строки с разной историей цены, и в ТОП-20 попадают обе половинки. «Сырая» и «готовая» при этом остаются разными позициями.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="34" t="inlineStr"/>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="33" t="inlineStr">
-        <is>
-          <t>Как считается «Цена ±»</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="34" t="inlineStr">
-        <is>
           <t>Медиана цены последних месяцев против медианы начала окна. Медиана, а не крайние точки, потому что первый месяц новой позиции — это пробная партия по розничной цене, и выход на опт выглядел бы обвалом. Месяцы, где позицию брали меньше четверти обычного объёма, из сравнения выброшены по той же причине.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="34" t="inlineStr">
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>Цена везде — выручка, делённая на количество, по всем клиентам сразу. Это фактическая цена отгрузки со всеми скидками, а не прайс.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="34" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="31" t="inlineStr">
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="34" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>Система «Пульс» · Фуд Завод · Ольга Герасименко, финансовый директор</t>
         </is>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Методика" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'План'!$A$7:$S$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'План'!$A$7:$T$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Сосиска в тесте (30шт гофра)</a:t>
+              <a:t>Пирожок с картофелем (30 шт гофра)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -532,7 +532,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Манты с говядиной (1порц)</a:t>
+              <a:t>Маффин шоколадный (24шт)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -633,7 +633,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Пирожок с картофелем (30 шт гофра)</a:t>
+              <a:t>Круассан миндальный (10 шт гофра)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -734,7 +734,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Бризоль с рисом (1порц)</a:t>
+              <a:t>Пирожок с капустой (30 шт гофра)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -835,7 +835,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Блины с ветчиной и сыром (3шт)</a:t>
+              <a:t>Манты с говядиной (1порц)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -936,7 +936,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Самса с говядиной (30 шт гофра)</a:t>
+              <a:t>Сочник творожный (30шт гофра )</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1037,7 +1037,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Самса с курицей (30шт гофра )</a:t>
+              <a:t>Бризоль с рисом (1порц)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1138,7 +1138,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Круассан с индейкой (1шт)</a:t>
+              <a:t>Блины с ветчиной и сыром (3шт)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1239,7 +1239,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Клаб Сэндвич с курицей (1шт)</a:t>
+              <a:t>Самса с говядиной (30 шт гофра)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1340,7 +1340,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Круассан миндальный (10 шт гофра)</a:t>
+              <a:t>Самса с курицей (30шт гофра )</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1542,7 +1542,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Шницель куриный с картофельным пюре (1порц)</a:t>
+              <a:t>Круассан с индейкой (1шт)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1845,7 +1845,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Кимпаб с тунцом (1шт)</a:t>
+              <a:t>Пирожок с курицей и сыром (30 шт гофра)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1946,7 +1946,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Кимпаб с курицей (1шт)</a:t>
+              <a:t>Кимпаб с тунцом (1шт)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2047,7 +2047,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Курица с сыром и картофельным пюре (1порц)</a:t>
+              <a:t>Кимпаб с курицей (1шт)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2148,7 +2148,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Курица с сыром с рисом и паутини (1порц)</a:t>
+              <a:t>Курица с сыром и картофельным пюре (1порц)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2249,7 +2249,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Пирожок с курицей и сыром (30 шт гофра)</a:t>
+              <a:t>Курица с сыром с рисом и паутини (1порц)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3071,7 +3071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S28"/>
+  <dimension ref="A1:T28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3093,6 +3093,7 @@
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="58" customWidth="1" min="19" max="19"/>
+    <col width="46" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3235,6 +3236,11 @@
           <t>Обоснование</t>
         </is>
       </c>
+      <c r="T7" s="7" t="inlineStr">
+        <is>
+          <t>Карточки в iiko</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
@@ -3253,31 +3259,31 @@
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>9312930</v>
+        <v>11467170</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1325</v>
+        <v>1627</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>7027</v>
+        <v>7047</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>-0.01462037666214644</v>
+        <v>-0.005144146725738707</v>
       </c>
       <c r="H8" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.516</v>
+        <v>0.5148728308728309</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>0.5152439024390243</v>
+        <v>0.6096274315858885</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="M8" s="10">
         <f>ROUND(F8*(1+L8),0)</f>
@@ -3305,7 +3311,12 @@
       </c>
       <c r="S8" s="14" t="inlineStr">
         <is>
-          <t>за 6 мес цена упала на 1.5% при ориентире 4.0%; берут на 52% больше</t>
+          <t>за 6 мес цена упала на 0.5% при ориентире 4.0%; берут на 61% больше</t>
+        </is>
+      </c>
+      <c r="T8" s="14" t="inlineStr">
+        <is>
+          <t>Упак Брецель-дог (20шт) · RP* Упак Брецель-дог (20шт)</t>
         </is>
       </c>
     </row>
@@ -3326,31 +3337,31 @@
         </is>
       </c>
       <c r="D9" s="16" t="n">
-        <v>6611799</v>
+        <v>10019546</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>705</v>
+        <v>1070</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>9374</v>
+        <v>9361</v>
       </c>
       <c r="G9" s="17" t="n">
-        <v>0.02604835660919047</v>
+        <v>0.01606738290323895</v>
       </c>
       <c r="H9" s="18" t="n">
         <v>8</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>0.598</v>
+        <v>0.5966395603154074</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>0.6202143950995407</v>
+        <v>0.402183406113537</v>
       </c>
       <c r="K9" s="17" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="M9" s="16">
         <f>ROUND(F9*(1+L9),0)</f>
@@ -3378,7 +3389,12 @@
       </c>
       <c r="S9" s="19" t="inlineStr">
         <is>
-          <t>за 8 мес цена выросла на 2.6% при ориентире 5.3%; берут на 62% больше</t>
+          <t>за 8 мес цена выросла на 1.6% при ориентире 5.3%; берут на 40% больше</t>
+        </is>
+      </c>
+      <c r="T9" s="19" t="inlineStr">
+        <is>
+          <t>RP* Упак Сосиска в тесте  готов СМ (30шт гофра) · Упак Сосиска в тесте  готов СМ (30шт гофра)</t>
         </is>
       </c>
     </row>
@@ -3454,6 +3470,11 @@
           <t>цену уже подняли на 9.9% — этого хватает</t>
         </is>
       </c>
+      <c r="T10" s="14" t="inlineStr">
+        <is>
+          <t>Упак Гуйру цомян (1порц)</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
@@ -3472,7 +3493,7 @@
         </is>
       </c>
       <c r="D11" s="16" t="n">
-        <v>5380972</v>
+        <v>5381606</v>
       </c>
       <c r="E11" s="16" t="n">
         <v>5162</v>
@@ -3490,7 +3511,7 @@
         <v>0.466</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>0.06047116833310517</v>
+        <v>0.05843357025697093</v>
       </c>
       <c r="K11" s="17" t="n">
         <v>0</v>
@@ -3527,49 +3548,54 @@
           <t>цену уже подняли на 14.4% — этого хватает</t>
         </is>
       </c>
+      <c r="T11" s="19" t="inlineStr">
+        <is>
+          <t>Упак Плов по-ташкентски (1порц) · RP* Упак Плов по-ташкентски (1порц)</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Кимпаб с тунцом (1шт)</t>
+          <t>Пирожок с курицей и сыром (30 шт гофра)</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Япония</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>— не трогать</t>
+          <t>Выпечка_</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>1 — сейчас</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>5104472</v>
+        <v>5160362</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>5379</v>
+        <v>980</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>949</v>
+        <v>5267</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.1144551028227871</v>
+        <v>0.004644817839810855</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>0.539</v>
+        <v>0.4990455257437672</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>0.2232582821620803</v>
+        <v>0.4364613880742911</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="M12" s="10">
         <f>ROUND(F12*(1+L12),0)</f>
@@ -3597,14 +3623,19 @@
       </c>
       <c r="S12" s="14" t="inlineStr">
         <is>
-          <t>цену уже подняли на 11.4% — этого хватает</t>
+          <t>за 8 мес цена выросла на 0.5% при ориентире 5.3%; берут на 44% больше</t>
+        </is>
+      </c>
+      <c r="T12" s="14" t="inlineStr">
+        <is>
+          <t>RP* Упак Пирожок с курицей и сыром готов СМ (30 шт гофра) · Упак Пирожок с курицей и сыром готов СМ (30 шт гофра)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>Кимпаб с курицей (1шт)</t>
+          <t>Кимпаб с тунцом (1шт)</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
@@ -3618,25 +3649,25 @@
         </is>
       </c>
       <c r="D13" s="16" t="n">
-        <v>4336019</v>
+        <v>5104472</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>5350</v>
+        <v>5379</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>810</v>
+        <v>949</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>0.09497220501137482</v>
+        <v>0.1144551028227871</v>
       </c>
       <c r="H13" s="18" t="n">
         <v>8</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>0.491</v>
+        <v>0.5389999999999999</v>
       </c>
       <c r="J13" s="17" t="n">
-        <v>0.1162887745166225</v>
+        <v>0.2232582821620803</v>
       </c>
       <c r="K13" s="17" t="n">
         <v>0</v>
@@ -3670,19 +3701,24 @@
       </c>
       <c r="S13" s="19" t="inlineStr">
         <is>
-          <t>цену уже подняли на 9.5% — этого хватает</t>
+          <t>цену уже подняли на 11.4% — этого хватает</t>
+        </is>
+      </c>
+      <c r="T13" s="19" t="inlineStr">
+        <is>
+          <t>Упак Кимпаб с тунцом (1шт)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Курица с сыром и картофельным пюре (1порц)</t>
+          <t>Кимпаб с курицей (1шт)</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Горячее</t>
+          <t>Япония</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -3691,25 +3727,25 @@
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>4293422</v>
+        <v>4336019</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>3814</v>
+        <v>5350</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>1126</v>
+        <v>810</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>0.07968634845642675</v>
+        <v>0.09497220501137482</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>0.5760000000000001</v>
+        <v>0.491</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>0.1776268395595348</v>
+        <v>0.1162887745166225</v>
       </c>
       <c r="K14" s="11" t="n">
         <v>0</v>
@@ -3743,14 +3779,19 @@
       </c>
       <c r="S14" s="14" t="inlineStr">
         <is>
-          <t>признаков отставания цены нет</t>
+          <t>цену уже подняли на 9.5% — этого хватает</t>
+        </is>
+      </c>
+      <c r="T14" s="14" t="inlineStr">
+        <is>
+          <t>Упак Кимпаб с курицей (1шт)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>Курица с сыром с рисом и паутини (1порц)</t>
+          <t>Курица с сыром и картофельным пюре (1порц)</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -3764,25 +3805,25 @@
         </is>
       </c>
       <c r="D15" s="16" t="n">
-        <v>3800654</v>
+        <v>4293422</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>3515</v>
+        <v>3814</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>1081</v>
+        <v>1126</v>
       </c>
       <c r="G15" s="17" t="n">
-        <v>0.07050092845465161</v>
+        <v>0.07968634845642675</v>
       </c>
       <c r="H15" s="18" t="n">
         <v>8</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>0.581</v>
+        <v>0.5760000000000001</v>
       </c>
       <c r="J15" s="17" t="n">
-        <v>0.1870989530563998</v>
+        <v>0.1776268395595348</v>
       </c>
       <c r="K15" s="17" t="n">
         <v>0</v>
@@ -3819,49 +3860,54 @@
           <t>признаков отставания цены нет</t>
         </is>
       </c>
+      <c r="T15" s="19" t="inlineStr">
+        <is>
+          <t>Упак Курица с сыром и картофельным пюре (1порц)</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Пирожок с курицей и сыром (30 шт гофра)</t>
+          <t>Курица с сыром с рисом и паутини (1порц)</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Выпечка_</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>2 — следом</t>
+          <t>Горячее</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>— не трогать</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>3632550</v>
+        <v>3800654</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>680</v>
+        <v>3515</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>5339</v>
+        <v>1081</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>0.008803340664356396</v>
+        <v>0.07050092845465161</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>0.51</v>
+        <v>0.581</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>0.4557774607703282</v>
+        <v>0.1870989530563998</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="M16" s="10">
         <f>ROUND(F16*(1+L16),0)</f>
@@ -3889,14 +3935,19 @@
       </c>
       <c r="S16" s="14" t="inlineStr">
         <is>
-          <t>за 8 мес цена выросла на 0.9% при ориентире 5.3%; берут на 46% больше</t>
+          <t>признаков отставания цены нет</t>
+        </is>
+      </c>
+      <c r="T16" s="14" t="inlineStr">
+        <is>
+          <t>Упак Курица с сыром с рисом и паутини (1порц)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>Сосиска в тесте (30шт гофра)</t>
+          <t>Пирожок с картофелем (30 шт гофра)</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
@@ -3910,31 +3961,31 @@
         </is>
       </c>
       <c r="D17" s="16" t="n">
-        <v>3407747</v>
+        <v>3780853</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>365</v>
+        <v>826</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>9336</v>
+        <v>4577</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>-0.001173885973586253</v>
+        <v>0.07254732484211801</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I17" s="17" t="n">
-        <v>0.594</v>
+        <v>0.6023283970574894</v>
       </c>
       <c r="J17" s="17" t="n">
-        <v>0.1128048780487805</v>
+        <v>0.7662152530292229</v>
       </c>
       <c r="K17" s="17" t="n">
-        <v>0.055</v>
+        <v>0.015</v>
       </c>
       <c r="L17" s="13" t="n">
-        <v>0.055</v>
+        <v>0.015</v>
       </c>
       <c r="M17" s="16">
         <f>ROUND(F17*(1+L17),0)</f>
@@ -3962,52 +4013,57 @@
       </c>
       <c r="S17" s="19" t="inlineStr">
         <is>
-          <t>за 8 мес цена упала на 0.1% при ориентире 5.3%</t>
+          <t>берут на 77% больше</t>
+        </is>
+      </c>
+      <c r="T17" s="19" t="inlineStr">
+        <is>
+          <t>RP* Упак Пирожок с картофелем готов СМ (30 шт гофра) · Упак Пирожок с картофелем готов СМ (30 шт гофра)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Манты с говядиной (1порц)</t>
+          <t>Маффин шоколадный (24шт)</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Горячее</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>— не трогать</t>
+          <t>Выпечка_</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>2 — следом</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>2986476</v>
+        <v>3539168</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>3451</v>
+        <v>482</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>865</v>
+        <v>7343</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0.09012158410248471</v>
+        <v>-0.003665392881112228</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>0.419</v>
+        <v>0.4849398251284082</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>-0.004902431990771894</v>
+        <v>0.130570758405004</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="L18" s="13" t="n">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="M18" s="10">
         <f>ROUND(F18*(1+L18),0)</f>
@@ -4035,14 +4091,19 @@
       </c>
       <c r="S18" s="14" t="inlineStr">
         <is>
-          <t>цену уже подняли на 9.0% — этого хватает</t>
+          <t>за 8 мес цена упала на 0.4% при ориентире 5.3%</t>
+        </is>
+      </c>
+      <c r="T18" s="14" t="inlineStr">
+        <is>
+          <t>Упак Маффин шоколадный (24шт) · RP* Упак Маффин шоколадный (24шт)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>Пирожок с картофелем (30 шт гофра)</t>
+          <t>Круассан миндальный (10 шт гофра)</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
@@ -4050,37 +4111,37 @@
           <t>Выпечка_</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
-        <is>
-          <t>— не трогать</t>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>2 — следом</t>
         </is>
       </c>
       <c r="D19" s="16" t="n">
-        <v>2940381</v>
+        <v>3374756</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>612</v>
+        <v>477</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>4805</v>
+        <v>7070</v>
       </c>
       <c r="G19" s="17" t="n">
-        <v>0.08843677289461338</v>
+        <v>0.02718255545943404</v>
       </c>
       <c r="H19" s="18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>0.617</v>
+        <v>0.5856715825776243</v>
       </c>
       <c r="J19" s="17" t="n">
-        <v>0.5223880597014925</v>
+        <v>0.4262948207171313</v>
       </c>
       <c r="K19" s="17" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="M19" s="16">
         <f>ROUND(F19*(1+L19),0)</f>
@@ -4108,52 +4169,57 @@
       </c>
       <c r="S19" s="19" t="inlineStr">
         <is>
-          <t>цену уже подняли на 8.8% — этого хватает</t>
+          <t>за 8 мес цена выросла на 2.7% при ориентире 5.3%; берут на 43% больше</t>
+        </is>
+      </c>
+      <c r="T19" s="19" t="inlineStr">
+        <is>
+          <t>RP* Упак Круассан миндальный готов СМ (10 шт гофра) · Упак Круассан миндальный готов СМ (10 шт гофра)</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Бризоль с рисом (1порц)</t>
+          <t>Пирожок с капустой (30 шт гофра)</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Горячее</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>1 — сейчас</t>
+          <t>Выпечка_</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>2 — следом + 2-й шаг</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>2634834</v>
+        <v>3210495</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>2227</v>
+        <v>756</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>1183</v>
+        <v>4249</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0.02382420203660618</v>
+        <v>-0.01425098681656201</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>0.366</v>
+        <v>0.624043653704491</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>0.3294866693195387</v>
+        <v>0.6239255014326648</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>0.075</v>
+        <v>0.08</v>
       </c>
       <c r="L20" s="13" t="n">
-        <v>0.075</v>
+        <v>0.08</v>
       </c>
       <c r="M20" s="10">
         <f>ROUND(F20*(1+L20),0)</f>
@@ -4181,19 +4247,24 @@
       </c>
       <c r="S20" s="14" t="inlineStr">
         <is>
-          <t>за 8 мес цена выросла на 2.4% при ориентире 5.3%; маржа 37% — тоньше заводской; берут на 33% больше</t>
+          <t>за 8 мес цена упала на 1.4% при ориентире 5.3%; берут на 62% больше. Расчёт просит 8.5% — остальное вторым шагом через квартал</t>
+        </is>
+      </c>
+      <c r="T20" s="14" t="inlineStr">
+        <is>
+          <t>RP* Упак Пирожок с капустой  готов СМ (30 шт гофра) · Упак Пирожок с капустой  готов СМ (30 шт гофра)</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Блины с ветчиной и сыром (3шт)</t>
+          <t>Манты с говядиной (1порц)</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Завтраки</t>
+          <t>Горячее</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -4202,25 +4273,25 @@
         </is>
       </c>
       <c r="D21" s="16" t="n">
-        <v>2632114</v>
+        <v>2987025</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>2835</v>
+        <v>3451</v>
       </c>
       <c r="F21" s="16" t="n">
-        <v>928</v>
+        <v>865</v>
       </c>
       <c r="G21" s="17" t="n">
-        <v>0.07048326431697016</v>
+        <v>0.09012158410248471</v>
       </c>
       <c r="H21" s="18" t="n">
         <v>8</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>0.493</v>
+        <v>0.419</v>
       </c>
       <c r="J21" s="17" t="n">
-        <v>0.06698444555945815</v>
+        <v>-0.007476993865030646</v>
       </c>
       <c r="K21" s="17" t="n">
         <v>0</v>
@@ -4254,14 +4325,19 @@
       </c>
       <c r="S21" s="19" t="inlineStr">
         <is>
-          <t>признаков отставания цены нет</t>
+          <t>цену уже подняли на 9.0% — этого хватает</t>
+        </is>
+      </c>
+      <c r="T21" s="19" t="inlineStr">
+        <is>
+          <t>Упак Манты с говядиной (1порц) · RP* Упак Манты с говядиной (1порц)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Самса с говядиной (30 шт гофра)</t>
+          <t>Сочник творожный (30шт гофра )</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -4271,29 +4347,29 @@
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>2 — следом + 2-й шаг</t>
+          <t>2 — следом</t>
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>2627782</v>
+        <v>2815730</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>385</v>
+        <v>409</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>6831</v>
+        <v>6890</v>
       </c>
       <c r="G22" s="11" t="n">
-        <v>-0.02818816478082753</v>
+        <v>-0.01415503666138584</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>0.4429999999999999</v>
+        <v>0.611</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>0.7379518072289157</v>
+        <v>0.5880829015544042</v>
       </c>
       <c r="K22" s="11" t="n">
         <v>0.08</v>
@@ -4327,52 +4403,57 @@
       </c>
       <c r="S22" s="14" t="inlineStr">
         <is>
-          <t>за 8 мес цена упала на 2.8% при ориентире 5.3%; маржа 44% — тоньше заводской; берут на 74% больше. Расчёт просит 12.5% — остальное вторым шагом через квартал</t>
+          <t>за 8 мес цена упала на 1.4% при ориентире 5.3%; берут на 59% больше</t>
+        </is>
+      </c>
+      <c r="T22" s="14" t="inlineStr">
+        <is>
+          <t>RP* Упак Сочник творожный готов СМ (30шт гофра ) · Упак Сочник творожный готов СМ (30шт гофра )</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>Самса с курицей (30шт гофра )</t>
+          <t>Бризоль с рисом (1порц)</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>Выпечка_</t>
+          <t>Горячее</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
         <is>
-          <t>2 — следом + 2-й шаг</t>
+          <t>2 — следом</t>
         </is>
       </c>
       <c r="D23" s="16" t="n">
-        <v>2612647</v>
+        <v>2634834</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>385</v>
+        <v>2227</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>6786</v>
+        <v>1183</v>
       </c>
       <c r="G23" s="17" t="n">
-        <v>-0.02307711041129701</v>
+        <v>0.02382420203660618</v>
       </c>
       <c r="H23" s="18" t="n">
         <v>8</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>0.613</v>
+        <v>0.366</v>
       </c>
       <c r="J23" s="17" t="n">
-        <v>0.6176470588235294</v>
+        <v>0.3294866693195387</v>
       </c>
       <c r="K23" s="17" t="n">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="M23" s="16">
         <f>ROUND(F23*(1+L23),0)</f>
@@ -4400,52 +4481,57 @@
       </c>
       <c r="S23" s="19" t="inlineStr">
         <is>
-          <t>за 8 мес цена упала на 2.3% при ориентире 5.3%; берут на 62% больше. Расчёт просит 9.0% — остальное вторым шагом через квартал</t>
+          <t>за 8 мес цена выросла на 2.4% при ориентире 5.3%; маржа 37% — тоньше заводской; берут на 33% больше</t>
+        </is>
+      </c>
+      <c r="T23" s="19" t="inlineStr">
+        <is>
+          <t>Упак Бризоль с рисом (1порц)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Круассан с индейкой (1шт)</t>
+          <t>Блины с ветчиной и сыром (3шт)</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>СЭНДВИЧИ</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>2 — следом</t>
+          <t>Завтраки</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>— не трогать</t>
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>2604922</v>
+        <v>2632371</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>4286</v>
+        <v>2836</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>608</v>
+        <v>928</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>0.03115280716362023</v>
+        <v>0.07048326431697016</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>0.609</v>
+        <v>0.493</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>0.3193104863533758</v>
+        <v>0.06297638385605397</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="L24" s="13" t="n">
-        <v>0.035</v>
+        <v>0</v>
       </c>
       <c r="M24" s="10">
         <f>ROUND(F24*(1+L24),0)</f>
@@ -4473,52 +4559,57 @@
       </c>
       <c r="S24" s="14" t="inlineStr">
         <is>
-          <t>за 8 мес цена выросла на 3.1% при ориентире 5.3%; берут на 32% больше</t>
+          <t>признаков отставания цены нет</t>
+        </is>
+      </c>
+      <c r="T24" s="14" t="inlineStr">
+        <is>
+          <t>Упак Блины с ветчиной и сыром (3шт) · RP* Упак Блины с ветчиной и сыром (3шт)</t>
         </is>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>Клаб Сэндвич с курицей (1шт)</t>
+          <t>Самса с говядиной (30 шт гофра)</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>СЭНДВИЧИ</t>
-        </is>
-      </c>
-      <c r="C25" s="20" t="inlineStr">
-        <is>
-          <t>— не трогать</t>
+          <t>Выпечка_</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>2 — следом + 2-й шаг</t>
         </is>
       </c>
       <c r="D25" s="16" t="n">
-        <v>2584803</v>
+        <v>2627782</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>4985</v>
+        <v>385</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>519</v>
+        <v>6831</v>
       </c>
       <c r="G25" s="17" t="n">
-        <v>0.05485859903578372</v>
+        <v>-0.02818816478082753</v>
       </c>
       <c r="H25" s="18" t="n">
         <v>8</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.4429999999999999</v>
       </c>
       <c r="J25" s="17" t="n">
-        <v>0.1839917662892883</v>
+        <v>0.7379518072289157</v>
       </c>
       <c r="K25" s="17" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L25" s="13" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="M25" s="16">
         <f>ROUND(F25*(1+L25),0)</f>
@@ -4546,14 +4637,19 @@
       </c>
       <c r="S25" s="19" t="inlineStr">
         <is>
-          <t>признаков отставания цены нет</t>
+          <t>за 8 мес цена упала на 2.8% при ориентире 5.3%; маржа 44% — тоньше заводской; берут на 74% больше. Расчёт просит 12.5% — остальное вторым шагом через квартал</t>
+        </is>
+      </c>
+      <c r="T25" s="19" t="inlineStr">
+        <is>
+          <t>Упак Самса с говядиной готов ФЗ СМ (30 шт гофра)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Круассан миндальный (10 шт гофра)</t>
+          <t>Самса с курицей (30шт гофра )</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -4563,35 +4659,35 @@
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>2 — следом</t>
+          <t>2 — следом + 2-й шаг</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>2571717</v>
+        <v>2612647</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>354</v>
+        <v>385</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>7272</v>
+        <v>6786</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>-0.003755966336836836</v>
+        <v>-0.02307711041129701</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>0.594</v>
+        <v>0.613</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>0.4357239512855211</v>
+        <v>0.6176470588235294</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="L26" s="13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="M26" s="10">
         <f>ROUND(F26*(1+L26),0)</f>
@@ -4619,19 +4715,24 @@
       </c>
       <c r="S26" s="14" t="inlineStr">
         <is>
-          <t>за 8 мес цена упала на 0.4% при ориентире 5.3%; берут на 44% больше</t>
+          <t>за 8 мес цена упала на 2.3% при ориентире 5.3%; берут на 62% больше. Расчёт просит 9.0% — остальное вторым шагом через квартал</t>
+        </is>
+      </c>
+      <c r="T26" s="14" t="inlineStr">
+        <is>
+          <t>Упак Самса с курицей готов ФЗ СМ (30шт гофра )</t>
         </is>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>Шницель куриный с картофельным пюре (1порц)</t>
+          <t>Круассан с индейкой (1шт)</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Горячее</t>
+          <t>СЭНДВИЧИ</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -4640,31 +4741,31 @@
         </is>
       </c>
       <c r="D27" s="16" t="n">
-        <v>2553371</v>
+        <v>2604922</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>2918</v>
+        <v>4286</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>875</v>
+        <v>608</v>
       </c>
       <c r="G27" s="17" t="n">
-        <v>0.04001774330608066</v>
+        <v>0.03115280716362023</v>
       </c>
       <c r="H27" s="18" t="n">
         <v>8</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>0.544</v>
+        <v>0.609</v>
       </c>
       <c r="J27" s="17" t="n">
-        <v>0.4051364365971108</v>
+        <v>0.3193104863533758</v>
       </c>
       <c r="K27" s="17" t="n">
-        <v>0.03</v>
+        <v>0.035</v>
       </c>
       <c r="L27" s="13" t="n">
-        <v>0.03</v>
+        <v>0.035</v>
       </c>
       <c r="M27" s="16">
         <f>ROUND(F27*(1+L27),0)</f>
@@ -4692,7 +4793,12 @@
       </c>
       <c r="S27" s="19" t="inlineStr">
         <is>
-          <t>за 8 мес цена выросла на 4.0% при ориентире 5.3%; берут на 41% больше</t>
+          <t>за 8 мес цена выросла на 3.1% при ориентире 5.3%; берут на 32% больше</t>
+        </is>
+      </c>
+      <c r="T27" s="19" t="inlineStr">
+        <is>
+          <t>Упак Круассан с индейкой (1шт)</t>
         </is>
       </c>
     </row>
@@ -4741,9 +4847,10 @@
         <f>"Прирост к нынешней валовой прибыли этих позиций: "&amp;TEXT(O28/SUMPRODUCT(D8:D27,I8:I27),"0.0%")</f>
         <v/>
       </c>
+      <c r="T28" s="24" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A7:S27"/>
+  <autoFilter ref="A7:T27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4847,34 +4954,34 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>11525</v>
+        <v>10296</v>
       </c>
       <c r="D5" s="30" t="n">
-        <v>9202</v>
+        <v>7263</v>
       </c>
       <c r="E5" s="30" t="n">
-        <v>7146</v>
+        <v>7107</v>
       </c>
       <c r="F5" s="30" t="n">
-        <v>7116</v>
+        <v>7102</v>
       </c>
       <c r="G5" s="30" t="n">
-        <v>7070</v>
+        <v>7077</v>
       </c>
       <c r="H5" s="30" t="n">
-        <v>7055</v>
+        <v>7066</v>
       </c>
       <c r="I5" s="30" t="n">
-        <v>7005</v>
+        <v>7123</v>
       </c>
       <c r="J5" s="30" t="n">
-        <v>7012</v>
+        <v>7010</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 52%</t>
+          <t>Выпечка_ · маржа 51%</t>
         </is>
       </c>
       <c r="B6" s="29" t="inlineStr">
@@ -4883,28 +4990,28 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>40</v>
+        <v>170</v>
       </c>
       <c r="D6" s="32" t="n">
-        <v>25</v>
+        <v>118</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>422</v>
+        <v>563</v>
       </c>
       <c r="F6" s="32" t="n">
-        <v>982</v>
+        <v>1101</v>
       </c>
       <c r="G6" s="32" t="n">
-        <v>1220</v>
+        <v>1369</v>
       </c>
       <c r="H6" s="32" t="n">
-        <v>1406</v>
+        <v>1646</v>
       </c>
       <c r="I6" s="32" t="n">
-        <v>322</v>
+        <v>780</v>
       </c>
       <c r="J6" s="32" t="n">
-        <v>2248</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="21">
@@ -4919,28 +5026,28 @@
         </is>
       </c>
       <c r="C21" s="30" t="n">
-        <v>8717</v>
+        <v>8795</v>
       </c>
       <c r="D21" s="30" t="n">
-        <v>9156</v>
+        <v>9210</v>
       </c>
       <c r="E21" s="30" t="n">
-        <v>9296</v>
+        <v>9434</v>
       </c>
       <c r="F21" s="30" t="n">
-        <v>9286</v>
+        <v>9473</v>
       </c>
       <c r="G21" s="30" t="n">
-        <v>9431</v>
+        <v>9406</v>
       </c>
       <c r="H21" s="30" t="n">
-        <v>9394</v>
+        <v>9349</v>
       </c>
       <c r="I21" s="30" t="n">
-        <v>9408</v>
+        <v>9358</v>
       </c>
       <c r="J21" s="30" t="n">
-        <v>9266</v>
+        <v>9377</v>
       </c>
     </row>
     <row r="22">
@@ -4955,28 +5062,28 @@
         </is>
       </c>
       <c r="C22" s="32" t="n">
-        <v>239</v>
+        <v>838</v>
       </c>
       <c r="D22" s="32" t="n">
-        <v>355</v>
+        <v>628</v>
       </c>
       <c r="E22" s="32" t="n">
-        <v>502</v>
+        <v>869</v>
       </c>
       <c r="F22" s="32" t="n">
-        <v>384</v>
+        <v>707</v>
       </c>
       <c r="G22" s="32" t="n">
-        <v>420</v>
+        <v>714</v>
       </c>
       <c r="H22" s="32" t="n">
-        <v>599</v>
+        <v>943</v>
       </c>
       <c r="I22" s="32" t="n">
-        <v>1065</v>
+        <v>1315</v>
       </c>
       <c r="J22" s="32" t="n">
-        <v>452</v>
+        <v>953</v>
       </c>
     </row>
     <row r="37">
@@ -5069,7 +5176,7 @@
         <v>930</v>
       </c>
       <c r="E53" s="30" t="n">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="F53" s="30" t="n">
         <v>924</v>
@@ -5105,16 +5212,16 @@
         <v>3002</v>
       </c>
       <c r="E54" s="32" t="n">
-        <v>4634</v>
+        <v>4640</v>
       </c>
       <c r="F54" s="32" t="n">
-        <v>4201</v>
+        <v>4216</v>
       </c>
       <c r="G54" s="32" t="n">
-        <v>5767</v>
+        <v>5776</v>
       </c>
       <c r="H54" s="32" t="n">
-        <v>5177</v>
+        <v>5179</v>
       </c>
       <c r="I54" s="32" t="n">
         <v>4921</v>
@@ -5126,7 +5233,7 @@
     <row r="69">
       <c r="A69" s="28" t="inlineStr">
         <is>
-          <t>Кимпаб с тунцом (1шт)</t>
+          <t>Пирожок с курицей и сыром (30 шт гофра)</t>
         </is>
       </c>
       <c r="B69" s="29" t="inlineStr">
@@ -5135,34 +5242,34 @@
         </is>
       </c>
       <c r="C69" s="30" t="n">
-        <v>855</v>
+        <v>4975</v>
       </c>
       <c r="D69" s="30" t="n">
-        <v>871</v>
+        <v>5256</v>
       </c>
       <c r="E69" s="30" t="n">
-        <v>875</v>
+        <v>5348</v>
       </c>
       <c r="F69" s="30" t="n">
-        <v>874</v>
+        <v>5270</v>
       </c>
       <c r="G69" s="30" t="n">
-        <v>879</v>
+        <v>5354</v>
       </c>
       <c r="H69" s="30" t="n">
-        <v>878</v>
+        <v>5220</v>
       </c>
       <c r="I69" s="30" t="n">
-        <v>970</v>
+        <v>5294</v>
       </c>
       <c r="J69" s="30" t="n">
-        <v>1002</v>
+        <v>5280</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Япония · маржа 54%</t>
+          <t>Выпечка_ · маржа 50%</t>
         </is>
       </c>
       <c r="B70" s="29" t="inlineStr">
@@ -5171,34 +5278,34 @@
         </is>
       </c>
       <c r="C70" s="32" t="n">
-        <v>4068</v>
+        <v>711</v>
       </c>
       <c r="D70" s="32" t="n">
-        <v>4158</v>
+        <v>584</v>
       </c>
       <c r="E70" s="32" t="n">
-        <v>3935</v>
+        <v>791</v>
       </c>
       <c r="F70" s="32" t="n">
-        <v>4522</v>
+        <v>567</v>
       </c>
       <c r="G70" s="32" t="n">
-        <v>4734</v>
+        <v>688</v>
       </c>
       <c r="H70" s="32" t="n">
-        <v>5532</v>
+        <v>879</v>
       </c>
       <c r="I70" s="32" t="n">
-        <v>5257</v>
+        <v>1123</v>
       </c>
       <c r="J70" s="32" t="n">
-        <v>5347</v>
+        <v>937</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="28" t="inlineStr">
         <is>
-          <t>Кимпаб с курицей (1шт)</t>
+          <t>Кимпаб с тунцом (1шт)</t>
         </is>
       </c>
       <c r="B85" s="29" t="inlineStr">
@@ -5207,34 +5314,34 @@
         </is>
       </c>
       <c r="C85" s="30" t="n">
-        <v>737</v>
+        <v>855</v>
       </c>
       <c r="D85" s="30" t="n">
-        <v>751</v>
+        <v>871</v>
       </c>
       <c r="E85" s="30" t="n">
-        <v>765</v>
+        <v>875</v>
       </c>
       <c r="F85" s="30" t="n">
-        <v>774</v>
+        <v>874</v>
       </c>
       <c r="G85" s="30" t="n">
-        <v>781</v>
+        <v>879</v>
       </c>
       <c r="H85" s="30" t="n">
-        <v>760</v>
+        <v>878</v>
       </c>
       <c r="I85" s="30" t="n">
-        <v>822</v>
+        <v>970</v>
       </c>
       <c r="J85" s="30" t="n">
-        <v>853</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="31" t="inlineStr">
         <is>
-          <t>Япония · маржа 49%</t>
+          <t>Япония · маржа 54%</t>
         </is>
       </c>
       <c r="B86" s="29" t="inlineStr">
@@ -5243,34 +5350,34 @@
         </is>
       </c>
       <c r="C86" s="32" t="n">
-        <v>4157</v>
+        <v>4068</v>
       </c>
       <c r="D86" s="32" t="n">
-        <v>4351</v>
+        <v>4158</v>
       </c>
       <c r="E86" s="32" t="n">
-        <v>4206</v>
+        <v>3935</v>
       </c>
       <c r="F86" s="32" t="n">
-        <v>4969</v>
+        <v>4522</v>
       </c>
       <c r="G86" s="32" t="n">
-        <v>5203</v>
+        <v>4734</v>
       </c>
       <c r="H86" s="32" t="n">
-        <v>5595</v>
+        <v>5532</v>
       </c>
       <c r="I86" s="32" t="n">
-        <v>5188</v>
+        <v>5257</v>
       </c>
       <c r="J86" s="32" t="n">
-        <v>5267</v>
+        <v>5347</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="28" t="inlineStr">
         <is>
-          <t>Курица с сыром и картофельным пюре (1порц)</t>
+          <t>Кимпаб с курицей (1шт)</t>
         </is>
       </c>
       <c r="B101" s="29" t="inlineStr">
@@ -5279,34 +5386,34 @@
         </is>
       </c>
       <c r="C101" s="30" t="n">
-        <v>1027</v>
+        <v>737</v>
       </c>
       <c r="D101" s="30" t="n">
-        <v>1042</v>
+        <v>751</v>
       </c>
       <c r="E101" s="30" t="n">
-        <v>1075</v>
+        <v>765</v>
       </c>
       <c r="F101" s="30" t="n">
-        <v>1076</v>
+        <v>774</v>
       </c>
       <c r="G101" s="30" t="n">
-        <v>1135</v>
+        <v>781</v>
       </c>
       <c r="H101" s="30" t="n">
-        <v>1117</v>
+        <v>760</v>
       </c>
       <c r="I101" s="30" t="n">
-        <v>1125</v>
+        <v>822</v>
       </c>
       <c r="J101" s="30" t="n">
-        <v>1137</v>
+        <v>853</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 58%</t>
+          <t>Япония · маржа 49%</t>
         </is>
       </c>
       <c r="B102" s="29" t="inlineStr">
@@ -5315,34 +5422,34 @@
         </is>
       </c>
       <c r="C102" s="32" t="n">
-        <v>2525</v>
+        <v>4157</v>
       </c>
       <c r="D102" s="32" t="n">
-        <v>2315</v>
+        <v>4351</v>
       </c>
       <c r="E102" s="32" t="n">
-        <v>2676</v>
+        <v>4206</v>
       </c>
       <c r="F102" s="32" t="n">
-        <v>2774</v>
+        <v>4969</v>
       </c>
       <c r="G102" s="32" t="n">
-        <v>4267</v>
+        <v>5203</v>
       </c>
       <c r="H102" s="32" t="n">
-        <v>4300</v>
+        <v>5595</v>
       </c>
       <c r="I102" s="32" t="n">
-        <v>3609</v>
+        <v>5188</v>
       </c>
       <c r="J102" s="32" t="n">
-        <v>3534</v>
+        <v>5267</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="28" t="inlineStr">
         <is>
-          <t>Курица с сыром с рисом и паутини (1порц)</t>
+          <t>Курица с сыром и картофельным пюре (1порц)</t>
         </is>
       </c>
       <c r="B117" s="29" t="inlineStr">
@@ -5351,28 +5458,28 @@
         </is>
       </c>
       <c r="C117" s="30" t="n">
-        <v>1003</v>
+        <v>1027</v>
       </c>
       <c r="D117" s="30" t="n">
-        <v>1020</v>
+        <v>1042</v>
       </c>
       <c r="E117" s="30" t="n">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="F117" s="30" t="n">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="G117" s="30" t="n">
-        <v>1064</v>
+        <v>1135</v>
       </c>
       <c r="H117" s="30" t="n">
-        <v>1043</v>
+        <v>1117</v>
       </c>
       <c r="I117" s="30" t="n">
-        <v>1092</v>
+        <v>1125</v>
       </c>
       <c r="J117" s="30" t="n">
-        <v>1115</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="118">
@@ -5387,34 +5494,34 @@
         </is>
       </c>
       <c r="C118" s="32" t="n">
-        <v>2254</v>
+        <v>2525</v>
       </c>
       <c r="D118" s="32" t="n">
-        <v>2108</v>
+        <v>2315</v>
       </c>
       <c r="E118" s="32" t="n">
-        <v>2608</v>
+        <v>2676</v>
       </c>
       <c r="F118" s="32" t="n">
-        <v>3048</v>
+        <v>2774</v>
       </c>
       <c r="G118" s="32" t="n">
-        <v>3227</v>
+        <v>4267</v>
       </c>
       <c r="H118" s="32" t="n">
-        <v>3859</v>
+        <v>4300</v>
       </c>
       <c r="I118" s="32" t="n">
-        <v>3501</v>
+        <v>3609</v>
       </c>
       <c r="J118" s="32" t="n">
-        <v>3185</v>
+        <v>3534</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="28" t="inlineStr">
         <is>
-          <t>Пирожок с курицей и сыром (30 шт гофра)</t>
+          <t>Курица с сыром с рисом и паутини (1порц)</t>
         </is>
       </c>
       <c r="B133" s="29" t="inlineStr">
@@ -5423,34 +5530,34 @@
         </is>
       </c>
       <c r="C133" s="30" t="n">
-        <v>5062</v>
+        <v>1003</v>
       </c>
       <c r="D133" s="30" t="n">
-        <v>5294</v>
+        <v>1020</v>
       </c>
       <c r="E133" s="30" t="n">
-        <v>5344</v>
+        <v>1071</v>
       </c>
       <c r="F133" s="30" t="n">
-        <v>5332</v>
+        <v>1074</v>
       </c>
       <c r="G133" s="30" t="n">
-        <v>5399</v>
+        <v>1064</v>
       </c>
       <c r="H133" s="30" t="n">
-        <v>5341</v>
+        <v>1043</v>
       </c>
       <c r="I133" s="30" t="n">
-        <v>5374</v>
+        <v>1092</v>
       </c>
       <c r="J133" s="30" t="n">
-        <v>5271</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 51%</t>
+          <t>Горячее · маржа 58%</t>
         </is>
       </c>
       <c r="B134" s="29" t="inlineStr">
@@ -5459,34 +5566,34 @@
         </is>
       </c>
       <c r="C134" s="32" t="n">
-        <v>228</v>
+        <v>2254</v>
       </c>
       <c r="D134" s="32" t="n">
-        <v>405</v>
+        <v>2108</v>
       </c>
       <c r="E134" s="32" t="n">
-        <v>547</v>
+        <v>2608</v>
       </c>
       <c r="F134" s="32" t="n">
-        <v>377</v>
+        <v>3048</v>
       </c>
       <c r="G134" s="32" t="n">
-        <v>478</v>
+        <v>3227</v>
       </c>
       <c r="H134" s="32" t="n">
-        <v>618</v>
+        <v>3859</v>
       </c>
       <c r="I134" s="32" t="n">
-        <v>937</v>
+        <v>3501</v>
       </c>
       <c r="J134" s="32" t="n">
-        <v>486</v>
+        <v>3185</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="28" t="inlineStr">
         <is>
-          <t>Сосиска в тесте (30шт гофра)</t>
+          <t>Пирожок с картофелем (30 шт гофра)</t>
         </is>
       </c>
       <c r="B149" s="29" t="inlineStr">
@@ -5495,34 +5602,34 @@
         </is>
       </c>
       <c r="C149" s="30" t="n">
-        <v>8827</v>
+        <v>5445</v>
       </c>
       <c r="D149" s="30" t="n">
-        <v>9282</v>
+        <v>872</v>
       </c>
       <c r="E149" s="30" t="n">
-        <v>9623</v>
+        <v>4427</v>
       </c>
       <c r="F149" s="30" t="n">
-        <v>9696</v>
+        <v>4820</v>
       </c>
       <c r="G149" s="30" t="n">
-        <v>9369</v>
+        <v>4804</v>
       </c>
       <c r="H149" s="30" t="n">
-        <v>9271</v>
+        <v>4116</v>
       </c>
       <c r="I149" s="30" t="n">
-        <v>9146</v>
+        <v>4801</v>
       </c>
       <c r="J149" s="30" t="n">
-        <v>9477</v>
+        <v>4748</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 59%</t>
+          <t>Выпечка_ · маржа 60%</t>
         </is>
       </c>
       <c r="B150" s="29" t="inlineStr">
@@ -5531,34 +5638,34 @@
         </is>
       </c>
       <c r="C150" s="32" t="n">
-        <v>599</v>
+        <v>60</v>
       </c>
       <c r="D150" s="32" t="n">
-        <v>273</v>
+        <v>182</v>
       </c>
       <c r="E150" s="32" t="n">
-        <v>367</v>
+        <v>550</v>
       </c>
       <c r="F150" s="32" t="n">
-        <v>323</v>
+        <v>402</v>
       </c>
       <c r="G150" s="32" t="n">
-        <v>294</v>
+        <v>451</v>
       </c>
       <c r="H150" s="32" t="n">
-        <v>344</v>
+        <v>751</v>
       </c>
       <c r="I150" s="32" t="n">
-        <v>250</v>
+        <v>971</v>
       </c>
       <c r="J150" s="32" t="n">
-        <v>501</v>
+        <v>756</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="28" t="inlineStr">
         <is>
-          <t>Манты с говядиной (1порц)</t>
+          <t>Маффин шоколадный (24шт)</t>
         </is>
       </c>
       <c r="B165" s="29" t="inlineStr">
@@ -5567,34 +5674,34 @@
         </is>
       </c>
       <c r="C165" s="30" t="n">
-        <v>831</v>
+        <v>7362</v>
       </c>
       <c r="D165" s="30" t="n">
-        <v>801</v>
+        <v>7317</v>
       </c>
       <c r="E165" s="30" t="n">
-        <v>791</v>
+        <v>7431</v>
       </c>
       <c r="F165" s="30" t="n">
-        <v>795</v>
+        <v>7492</v>
       </c>
       <c r="G165" s="30" t="n">
-        <v>848</v>
+        <v>7496</v>
       </c>
       <c r="H165" s="30" t="n">
-        <v>790</v>
+        <v>7329</v>
       </c>
       <c r="I165" s="30" t="n">
-        <v>873</v>
+        <v>7335</v>
       </c>
       <c r="J165" s="30" t="n">
-        <v>939</v>
+        <v>7358</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 42%</t>
+          <t>Выпечка_ · маржа 48%</t>
         </is>
       </c>
       <c r="B166" s="29" t="inlineStr">
@@ -5603,34 +5710,34 @@
         </is>
       </c>
       <c r="C166" s="32" t="n">
-        <v>3204</v>
+        <v>293</v>
       </c>
       <c r="D166" s="32" t="n">
-        <v>3017</v>
+        <v>324</v>
       </c>
       <c r="E166" s="32" t="n">
-        <v>3920</v>
+        <v>387</v>
       </c>
       <c r="F166" s="32" t="n">
-        <v>3319</v>
+        <v>523</v>
       </c>
       <c r="G166" s="32" t="n">
-        <v>3164</v>
+        <v>369</v>
       </c>
       <c r="H166" s="32" t="n">
-        <v>3665</v>
+        <v>392</v>
       </c>
       <c r="I166" s="32" t="n">
-        <v>3234</v>
+        <v>456</v>
       </c>
       <c r="J166" s="32" t="n">
-        <v>3453</v>
+        <v>598</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="28" t="inlineStr">
         <is>
-          <t>Пирожок с картофелем (30 шт гофра)</t>
+          <t>Круассан миндальный (10 шт гофра)</t>
         </is>
       </c>
       <c r="B181" s="29" t="inlineStr">
@@ -5638,33 +5745,35 @@
           <t>Цена, ₸</t>
         </is>
       </c>
-      <c r="C181" s="30" t="n"/>
+      <c r="C181" s="30" t="n">
+        <v>6768</v>
+      </c>
       <c r="D181" s="30" t="n">
-        <v>88</v>
+        <v>6823</v>
       </c>
       <c r="E181" s="30" t="n">
-        <v>4400</v>
+        <v>7177</v>
       </c>
       <c r="F181" s="30" t="n">
-        <v>4765</v>
+        <v>7129</v>
       </c>
       <c r="G181" s="30" t="n">
-        <v>4871</v>
+        <v>7044</v>
       </c>
       <c r="H181" s="30" t="n">
-        <v>4789</v>
+        <v>7008</v>
       </c>
       <c r="I181" s="30" t="n">
-        <v>4832</v>
+        <v>7213</v>
       </c>
       <c r="J181" s="30" t="n">
-        <v>4768</v>
+        <v>6946</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 62%</t>
+          <t>Выпечка_ · маржа 59%</t>
         </is>
       </c>
       <c r="B182" s="29" t="inlineStr">
@@ -5673,34 +5782,34 @@
         </is>
       </c>
       <c r="C182" s="32" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="D182" s="32" t="n">
-        <v>155</v>
+        <v>265</v>
       </c>
       <c r="E182" s="32" t="n">
-        <v>506</v>
+        <v>335</v>
       </c>
       <c r="F182" s="32" t="n">
-        <v>330</v>
+        <v>376</v>
       </c>
       <c r="G182" s="32" t="n">
-        <v>370</v>
+        <v>293</v>
       </c>
       <c r="H182" s="32" t="n">
-        <v>507</v>
+        <v>421</v>
       </c>
       <c r="I182" s="32" t="n">
-        <v>875</v>
+        <v>567</v>
       </c>
       <c r="J182" s="32" t="n">
-        <v>454</v>
+        <v>444</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="28" t="inlineStr">
         <is>
-          <t>Бризоль с рисом (1порц)</t>
+          <t>Пирожок с капустой (30 шт гофра)</t>
         </is>
       </c>
       <c r="B197" s="29" t="inlineStr">
@@ -5709,34 +5818,34 @@
         </is>
       </c>
       <c r="C197" s="30" t="n">
-        <v>1149</v>
+        <v>4310</v>
       </c>
       <c r="D197" s="30" t="n">
-        <v>1154</v>
+        <v>4715</v>
       </c>
       <c r="E197" s="30" t="n">
-        <v>1226</v>
+        <v>4746</v>
       </c>
       <c r="F197" s="30" t="n">
-        <v>1202</v>
+        <v>4788</v>
       </c>
       <c r="G197" s="30" t="n">
-        <v>1207</v>
+        <v>4792</v>
       </c>
       <c r="H197" s="30" t="n">
-        <v>1188</v>
+        <v>3492</v>
       </c>
       <c r="I197" s="30" t="n">
-        <v>1179</v>
+        <v>4647</v>
       </c>
       <c r="J197" s="30" t="n">
-        <v>1182</v>
+        <v>4723</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 37%</t>
+          <t>Выпечка_ · маржа 62%</t>
         </is>
       </c>
       <c r="B198" s="29" t="inlineStr">
@@ -5745,34 +5854,34 @@
         </is>
       </c>
       <c r="C198" s="32" t="n">
-        <v>1835</v>
+        <v>381</v>
       </c>
       <c r="D198" s="32" t="n">
-        <v>1583</v>
+        <v>349</v>
       </c>
       <c r="E198" s="32" t="n">
-        <v>1421</v>
+        <v>496</v>
       </c>
       <c r="F198" s="32" t="n">
-        <v>1789</v>
+        <v>446</v>
       </c>
       <c r="G198" s="32" t="n">
-        <v>1816</v>
+        <v>454</v>
       </c>
       <c r="H198" s="32" t="n">
-        <v>2234</v>
+        <v>829</v>
       </c>
       <c r="I198" s="32" t="n">
-        <v>2204</v>
+        <v>724</v>
       </c>
       <c r="J198" s="32" t="n">
-        <v>2244</v>
+        <v>714</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="28" t="inlineStr">
         <is>
-          <t>Блины с ветчиной и сыром (3шт)</t>
+          <t>Манты с говядиной (1порц)</t>
         </is>
       </c>
       <c r="B213" s="29" t="inlineStr">
@@ -5781,34 +5890,34 @@
         </is>
       </c>
       <c r="C213" s="30" t="n">
-        <v>863</v>
+        <v>831</v>
       </c>
       <c r="D213" s="30" t="n">
-        <v>853</v>
+        <v>801</v>
       </c>
       <c r="E213" s="30" t="n">
-        <v>896</v>
+        <v>790</v>
       </c>
       <c r="F213" s="30" t="n">
-        <v>858</v>
+        <v>795</v>
       </c>
       <c r="G213" s="30" t="n">
-        <v>885</v>
+        <v>848</v>
       </c>
       <c r="H213" s="30" t="n">
-        <v>897</v>
+        <v>790</v>
       </c>
       <c r="I213" s="30" t="n">
-        <v>924</v>
+        <v>873</v>
       </c>
       <c r="J213" s="30" t="n">
-        <v>961</v>
+        <v>939</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="31" t="inlineStr">
         <is>
-          <t>Завтраки · маржа 49%</t>
+          <t>Горячее · маржа 42%</t>
         </is>
       </c>
       <c r="B214" s="29" t="inlineStr">
@@ -5817,34 +5926,34 @@
         </is>
       </c>
       <c r="C214" s="32" t="n">
-        <v>2211</v>
+        <v>3204</v>
       </c>
       <c r="D214" s="32" t="n">
-        <v>2131</v>
+        <v>3017</v>
       </c>
       <c r="E214" s="32" t="n">
-        <v>2922</v>
+        <v>3925</v>
       </c>
       <c r="F214" s="32" t="n">
-        <v>2412</v>
+        <v>3334</v>
       </c>
       <c r="G214" s="32" t="n">
-        <v>2638</v>
+        <v>3173</v>
       </c>
       <c r="H214" s="32" t="n">
-        <v>2729</v>
+        <v>3667</v>
       </c>
       <c r="I214" s="32" t="n">
-        <v>2832</v>
+        <v>3234</v>
       </c>
       <c r="J214" s="32" t="n">
-        <v>2945</v>
+        <v>3453</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="28" t="inlineStr">
         <is>
-          <t>Самса с говядиной (30 шт гофра)</t>
+          <t>Сочник творожный (30шт гофра )</t>
         </is>
       </c>
       <c r="B229" s="29" t="inlineStr">
@@ -5853,34 +5962,34 @@
         </is>
       </c>
       <c r="C229" s="30" t="n">
-        <v>7098</v>
+        <v>7012</v>
       </c>
       <c r="D229" s="30" t="n">
-        <v>6977</v>
+        <v>6983</v>
       </c>
       <c r="E229" s="30" t="n">
-        <v>7003</v>
+        <v>7182</v>
       </c>
       <c r="F229" s="30" t="n">
-        <v>6964</v>
+        <v>7137</v>
       </c>
       <c r="G229" s="30" t="n">
-        <v>6862</v>
+        <v>7249</v>
       </c>
       <c r="H229" s="30" t="n">
+        <v>6963</v>
+      </c>
+      <c r="I229" s="30" t="n">
         <v>6912</v>
       </c>
-      <c r="I229" s="30" t="n">
-        <v>6774</v>
-      </c>
       <c r="J229" s="30" t="n">
-        <v>6805</v>
+        <v>6814</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 44%</t>
+          <t>Выпечка_ · маржа 61%</t>
         </is>
       </c>
       <c r="B230" s="29" t="inlineStr">
@@ -5889,34 +5998,34 @@
         </is>
       </c>
       <c r="C230" s="32" t="n">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="D230" s="32" t="n">
-        <v>130</v>
+        <v>169</v>
       </c>
       <c r="E230" s="32" t="n">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="F230" s="32" t="n">
-        <v>210</v>
+        <v>306</v>
       </c>
       <c r="G230" s="32" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H230" s="32" t="n">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="I230" s="32" t="n">
-        <v>256</v>
+        <v>418</v>
       </c>
       <c r="J230" s="32" t="n">
-        <v>541</v>
+        <v>461</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="28" t="inlineStr">
         <is>
-          <t>Самса с курицей (30шт гофра )</t>
+          <t>Бризоль с рисом (1порц)</t>
         </is>
       </c>
       <c r="B245" s="29" t="inlineStr">
@@ -5925,34 +6034,34 @@
         </is>
       </c>
       <c r="C245" s="30" t="n">
-        <v>6935</v>
+        <v>1149</v>
       </c>
       <c r="D245" s="30" t="n">
-        <v>6925</v>
+        <v>1154</v>
       </c>
       <c r="E245" s="30" t="n">
-        <v>6901</v>
+        <v>1226</v>
       </c>
       <c r="F245" s="30" t="n">
-        <v>6983</v>
+        <v>1202</v>
       </c>
       <c r="G245" s="30" t="n">
-        <v>6703</v>
+        <v>1207</v>
       </c>
       <c r="H245" s="30" t="n">
-        <v>6897</v>
+        <v>1188</v>
       </c>
       <c r="I245" s="30" t="n">
-        <v>6710</v>
+        <v>1179</v>
       </c>
       <c r="J245" s="30" t="n">
-        <v>6765</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 61%</t>
+          <t>Горячее · маржа 37%</t>
         </is>
       </c>
       <c r="B246" s="29" t="inlineStr">
@@ -5961,34 +6070,34 @@
         </is>
       </c>
       <c r="C246" s="32" t="n">
-        <v>218</v>
+        <v>1835</v>
       </c>
       <c r="D246" s="32" t="n">
-        <v>161</v>
+        <v>1583</v>
       </c>
       <c r="E246" s="32" t="n">
-        <v>211</v>
+        <v>1421</v>
       </c>
       <c r="F246" s="32" t="n">
-        <v>253</v>
+        <v>1789</v>
       </c>
       <c r="G246" s="32" t="n">
-        <v>250</v>
+        <v>1816</v>
       </c>
       <c r="H246" s="32" t="n">
-        <v>301</v>
+        <v>2234</v>
       </c>
       <c r="I246" s="32" t="n">
-        <v>285</v>
+        <v>2204</v>
       </c>
       <c r="J246" s="32" t="n">
-        <v>569</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="28" t="inlineStr">
         <is>
-          <t>Круассан с индейкой (1шт)</t>
+          <t>Блины с ветчиной и сыром (3шт)</t>
         </is>
       </c>
       <c r="B261" s="29" t="inlineStr">
@@ -5997,34 +6106,34 @@
         </is>
       </c>
       <c r="C261" s="30" t="n">
-        <v>590</v>
+        <v>863</v>
       </c>
       <c r="D261" s="30" t="n">
-        <v>599</v>
+        <v>853</v>
       </c>
       <c r="E261" s="30" t="n">
-        <v>593</v>
+        <v>894</v>
       </c>
       <c r="F261" s="30" t="n">
-        <v>577</v>
+        <v>858</v>
       </c>
       <c r="G261" s="30" t="n">
-        <v>587</v>
+        <v>884</v>
       </c>
       <c r="H261" s="30" t="n">
-        <v>595</v>
+        <v>897</v>
       </c>
       <c r="I261" s="30" t="n">
-        <v>611</v>
+        <v>924</v>
       </c>
       <c r="J261" s="30" t="n">
-        <v>619</v>
+        <v>961</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="31" t="inlineStr">
         <is>
-          <t>СЭНДВИЧИ · маржа 61%</t>
+          <t>Завтраки · маржа 49%</t>
         </is>
       </c>
       <c r="B262" s="29" t="inlineStr">
@@ -6033,34 +6142,34 @@
         </is>
       </c>
       <c r="C262" s="32" t="n">
-        <v>2352</v>
+        <v>2211</v>
       </c>
       <c r="D262" s="32" t="n">
-        <v>2345</v>
+        <v>2131</v>
       </c>
       <c r="E262" s="32" t="n">
-        <v>2472</v>
+        <v>2928</v>
       </c>
       <c r="F262" s="32" t="n">
-        <v>3314</v>
+        <v>2427</v>
       </c>
       <c r="G262" s="32" t="n">
-        <v>3960</v>
+        <v>2648</v>
       </c>
       <c r="H262" s="32" t="n">
-        <v>4761</v>
+        <v>2730</v>
       </c>
       <c r="I262" s="32" t="n">
-        <v>4156</v>
+        <v>2832</v>
       </c>
       <c r="J262" s="32" t="n">
-        <v>3941</v>
+        <v>2945</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="28" t="inlineStr">
         <is>
-          <t>Клаб Сэндвич с курицей (1шт)</t>
+          <t>Самса с говядиной (30 шт гофра)</t>
         </is>
       </c>
       <c r="B277" s="29" t="inlineStr">
@@ -6069,34 +6178,34 @@
         </is>
       </c>
       <c r="C277" s="30" t="n">
-        <v>488</v>
+        <v>7098</v>
       </c>
       <c r="D277" s="30" t="n">
-        <v>489</v>
+        <v>6977</v>
       </c>
       <c r="E277" s="30" t="n">
-        <v>512</v>
+        <v>7003</v>
       </c>
       <c r="F277" s="30" t="n">
-        <v>506</v>
+        <v>6964</v>
       </c>
       <c r="G277" s="30" t="n">
-        <v>509</v>
+        <v>6862</v>
       </c>
       <c r="H277" s="30" t="n">
-        <v>514</v>
+        <v>6912</v>
       </c>
       <c r="I277" s="30" t="n">
-        <v>516</v>
+        <v>6774</v>
       </c>
       <c r="J277" s="30" t="n">
-        <v>524</v>
+        <v>6805</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="31" t="inlineStr">
         <is>
-          <t>СЭНДВИЧИ · маржа 56%</t>
+          <t>Выпечка_ · маржа 44%</t>
         </is>
       </c>
       <c r="B278" s="29" t="inlineStr">
@@ -6105,34 +6214,34 @@
         </is>
       </c>
       <c r="C278" s="32" t="n">
-        <v>3237</v>
+        <v>186</v>
       </c>
       <c r="D278" s="32" t="n">
-        <v>3273</v>
+        <v>130</v>
       </c>
       <c r="E278" s="32" t="n">
-        <v>4099</v>
+        <v>217</v>
       </c>
       <c r="F278" s="32" t="n">
-        <v>4262</v>
+        <v>210</v>
       </c>
       <c r="G278" s="32" t="n">
-        <v>4270</v>
+        <v>237</v>
       </c>
       <c r="H278" s="32" t="n">
-        <v>4191</v>
+        <v>357</v>
       </c>
       <c r="I278" s="32" t="n">
-        <v>5051</v>
+        <v>256</v>
       </c>
       <c r="J278" s="32" t="n">
-        <v>5713</v>
+        <v>541</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="28" t="inlineStr">
         <is>
-          <t>Круассан миндальный (10 шт гофра)</t>
+          <t>Самса с курицей (30шт гофра )</t>
         </is>
       </c>
       <c r="B293" s="29" t="inlineStr">
@@ -6141,34 +6250,34 @@
         </is>
       </c>
       <c r="C293" s="30" t="n">
-        <v>7232</v>
+        <v>6935</v>
       </c>
       <c r="D293" s="30" t="n">
-        <v>7166</v>
+        <v>6925</v>
       </c>
       <c r="E293" s="30" t="n">
-        <v>7239</v>
+        <v>6901</v>
       </c>
       <c r="F293" s="30" t="n">
-        <v>7196</v>
+        <v>6983</v>
       </c>
       <c r="G293" s="30" t="n">
-        <v>7412</v>
+        <v>6703</v>
       </c>
       <c r="H293" s="30" t="n">
-        <v>7205</v>
+        <v>6897</v>
       </c>
       <c r="I293" s="30" t="n">
-        <v>7374</v>
+        <v>6710</v>
       </c>
       <c r="J293" s="30" t="n">
-        <v>7155</v>
+        <v>6765</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 59%</t>
+          <t>Выпечка_ · маржа 61%</t>
         </is>
       </c>
       <c r="B294" s="29" t="inlineStr">
@@ -6177,34 +6286,34 @@
         </is>
       </c>
       <c r="C294" s="32" t="n">
-        <v>108</v>
+        <v>218</v>
       </c>
       <c r="D294" s="32" t="n">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="E294" s="32" t="n">
-        <v>245</v>
+        <v>211</v>
       </c>
       <c r="F294" s="32" t="n">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="G294" s="32" t="n">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="H294" s="32" t="n">
-        <v>335</v>
+        <v>301</v>
       </c>
       <c r="I294" s="32" t="n">
-        <v>488</v>
+        <v>285</v>
       </c>
       <c r="J294" s="32" t="n">
-        <v>238</v>
+        <v>569</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="28" t="inlineStr">
         <is>
-          <t>Шницель куриный с картофельным пюре (1порц)</t>
+          <t>Круассан с индейкой (1шт)</t>
         </is>
       </c>
       <c r="B309" s="29" t="inlineStr">
@@ -6213,34 +6322,34 @@
         </is>
       </c>
       <c r="C309" s="30" t="n">
-        <v>859</v>
+        <v>590</v>
       </c>
       <c r="D309" s="30" t="n">
-        <v>841</v>
+        <v>599</v>
       </c>
       <c r="E309" s="30" t="n">
-        <v>857</v>
+        <v>593</v>
       </c>
       <c r="F309" s="30" t="n">
-        <v>856</v>
+        <v>577</v>
       </c>
       <c r="G309" s="30" t="n">
-        <v>899</v>
+        <v>587</v>
       </c>
       <c r="H309" s="30" t="n">
-        <v>812</v>
+        <v>595</v>
       </c>
       <c r="I309" s="30" t="n">
-        <v>891</v>
+        <v>611</v>
       </c>
       <c r="J309" s="30" t="n">
-        <v>911</v>
+        <v>619</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 54%</t>
+          <t>СЭНДВИЧИ · маржа 61%</t>
         </is>
       </c>
       <c r="B310" s="29" t="inlineStr">
@@ -6249,28 +6358,28 @@
         </is>
       </c>
       <c r="C310" s="32" t="n">
-        <v>2443</v>
+        <v>2352</v>
       </c>
       <c r="D310" s="32" t="n">
-        <v>2194</v>
+        <v>2345</v>
       </c>
       <c r="E310" s="32" t="n">
-        <v>1988</v>
+        <v>2472</v>
       </c>
       <c r="F310" s="32" t="n">
-        <v>2128</v>
+        <v>3314</v>
       </c>
       <c r="G310" s="32" t="n">
-        <v>2114</v>
+        <v>3960</v>
       </c>
       <c r="H310" s="32" t="n">
-        <v>2619</v>
+        <v>4761</v>
       </c>
       <c r="I310" s="32" t="n">
-        <v>2763</v>
+        <v>4156</v>
       </c>
       <c r="J310" s="32" t="n">
-        <v>3372</v>
+        <v>3941</v>
       </c>
     </row>
   </sheetData>
@@ -6285,7 +6394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A21"/>
+  <dimension ref="A2:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -6383,29 +6492,46 @@
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="33" t="inlineStr">
         <is>
+          <t>Почему позиций двадцать, а карточек в iiko больше</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="70" customHeight="1">
+      <c r="A18" s="34" t="inlineStr">
+        <is>
+          <t>Часть позиций ведётся в iiko под двумя именами: обычным и с приставкой «RP*» — под ней ту же позицию берёт сеть АЗС. Это одно и то же изделие, поэтому в отчёте оно сведено в одну строку, а из каких карточек оно собрано, написано в последней колонке. Если считать карточки порознь, один товар распадается на две строки с разной историей цены, и в ТОП-20 попадают обе половинки. «Сырая» и «готовая» при этом остаются разными позициями.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="34" t="inlineStr"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="33" t="inlineStr">
+        <is>
           <t>Как считается «Цена ±»</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="34" t="inlineStr">
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>Медиана цены последних месяцев против медианы начала окна. Медиана, а не крайние точки, потому что первый месяц новой позиции — это пробная партия по розничной цене, и выход на опт выглядел бы обвалом. Месяцы, где позицию брали меньше четверти обычного объёма, из сравнения выброшены по той же причине.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="34" t="inlineStr">
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="34" t="inlineStr">
         <is>
           <t>Цена везде — выручка, делённая на количество, по всем клиентам сразу. Это фактическая цена отгрузки со всеми скидками, а не прайс.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="34" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="31" t="inlineStr">
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="34" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="inlineStr">
         <is>
           <t>Система «Пульс» · Фуд Завод · Ольга Герасименко, финансовый директор</t>
         </is>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3586,7 +3586,7 @@
         <v>8</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>0.4990455257437672</v>
+        <v>0.4993415926155573</v>
       </c>
       <c r="J12" s="11" t="n">
         <v>0.4364613880742911</v>
@@ -3976,7 +3976,7 @@
         <v>7</v>
       </c>
       <c r="I17" s="17" t="n">
-        <v>0.6023283970574894</v>
+        <v>0.602106100043209</v>
       </c>
       <c r="J17" s="17" t="n">
         <v>0.7662152530292229</v>
@@ -4210,7 +4210,7 @@
         <v>8</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>0.624043653704491</v>
+        <v>0.622703271613879</v>
       </c>
       <c r="J20" s="11" t="n">
         <v>0.6239255014326648</v>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3274,7 +3274,7 @@
         <v>6</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.5148728308728309</v>
+        <v>0.5247456617456617</v>
       </c>
       <c r="J8" s="11" t="n">
         <v>0.6096274315858885</v>
@@ -4981,7 +4981,7 @@
     <row r="6">
       <c r="A6" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 51%</t>
+          <t>Выпечка_ · маржа 52%</t>
         </is>
       </c>
       <c r="B6" s="29" t="inlineStr">

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 07.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 08.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
         <v>6</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.5247456617456617</v>
+        <v>0.5255578002244669</v>
       </c>
       <c r="J8" s="11" t="n">
         <v>0.6096274315858885</v>
@@ -3352,7 +3352,7 @@
         <v>8</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>0.5966395603154074</v>
+        <v>0.5972994503942594</v>
       </c>
       <c r="J9" s="17" t="n">
         <v>0.402183406113537</v>
@@ -3430,7 +3430,7 @@
         <v>8</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>0.537</v>
+        <v>0.5379999999999999</v>
       </c>
       <c r="J10" s="11" t="n">
         <v>0.2044411292173514</v>
@@ -3508,7 +3508,7 @@
         <v>8</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>0.466</v>
+        <v>0.468</v>
       </c>
       <c r="J11" s="17" t="n">
         <v>0.05843357025697093</v>
@@ -3664,7 +3664,7 @@
         <v>8</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>0.5389999999999999</v>
+        <v>0.5449999999999999</v>
       </c>
       <c r="J13" s="17" t="n">
         <v>0.2232582821620803</v>
@@ -3742,7 +3742,7 @@
         <v>8</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>0.491</v>
+        <v>0.4970000000000001</v>
       </c>
       <c r="J14" s="11" t="n">
         <v>0.1162887745166225</v>
@@ -3820,7 +3820,7 @@
         <v>8</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>0.5760000000000001</v>
+        <v>0.578</v>
       </c>
       <c r="J15" s="17" t="n">
         <v>0.1776268395595348</v>
@@ -3898,7 +3898,7 @@
         <v>8</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>0.581</v>
+        <v>0.583</v>
       </c>
       <c r="J16" s="11" t="n">
         <v>0.1870989530563998</v>
@@ -3976,7 +3976,7 @@
         <v>7</v>
       </c>
       <c r="I17" s="17" t="n">
-        <v>0.602106100043209</v>
+        <v>0.603106100043209</v>
       </c>
       <c r="J17" s="17" t="n">
         <v>0.7662152530292229</v>
@@ -4054,7 +4054,7 @@
         <v>8</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>0.4849398251284082</v>
+        <v>0.4872048688463061</v>
       </c>
       <c r="J18" s="11" t="n">
         <v>0.130570758405004</v>
@@ -4132,7 +4132,7 @@
         <v>8</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>0.5856715825776243</v>
+        <v>0.5866715825776244</v>
       </c>
       <c r="J19" s="17" t="n">
         <v>0.4262948207171313</v>
@@ -4210,7 +4210,7 @@
         <v>8</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>0.622703271613879</v>
+        <v>0.6231500656440829</v>
       </c>
       <c r="J20" s="11" t="n">
         <v>0.6239255014326648</v>
@@ -4288,7 +4288,7 @@
         <v>8</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>0.419</v>
+        <v>0.5929999999999999</v>
       </c>
       <c r="J21" s="17" t="n">
         <v>-0.007476993865030646</v>
@@ -4366,7 +4366,7 @@
         <v>8</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>0.611</v>
+        <v>0.6114207541206009</v>
       </c>
       <c r="J22" s="11" t="n">
         <v>0.5880829015544042</v>
@@ -4444,7 +4444,7 @@
         <v>8</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>0.366</v>
+        <v>0.369</v>
       </c>
       <c r="J23" s="17" t="n">
         <v>0.3294866693195387</v>
@@ -4522,7 +4522,7 @@
         <v>8</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>0.493</v>
+        <v>0.498</v>
       </c>
       <c r="J24" s="11" t="n">
         <v>0.06297638385605397</v>
@@ -4600,7 +4600,7 @@
         <v>8</v>
       </c>
       <c r="I25" s="17" t="n">
-        <v>0.4429999999999999</v>
+        <v>0.445</v>
       </c>
       <c r="J25" s="17" t="n">
         <v>0.7379518072289157</v>
@@ -4678,7 +4678,7 @@
         <v>8</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>0.613</v>
+        <v>0.615</v>
       </c>
       <c r="J26" s="11" t="n">
         <v>0.6176470588235294</v>
@@ -4756,7 +4756,7 @@
         <v>8</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>0.609</v>
+        <v>0.61</v>
       </c>
       <c r="J27" s="17" t="n">
         <v>0.3193104863533758</v>
@@ -4981,7 +4981,7 @@
     <row r="6">
       <c r="A6" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 52%</t>
+          <t>Выпечка_ · маржа 53%</t>
         </is>
       </c>
       <c r="B6" s="29" t="inlineStr">
@@ -5413,7 +5413,7 @@
     <row r="102">
       <c r="A102" s="31" t="inlineStr">
         <is>
-          <t>Япония · маржа 49%</t>
+          <t>Япония · маржа 50%</t>
         </is>
       </c>
       <c r="B102" s="29" t="inlineStr">
@@ -5701,7 +5701,7 @@
     <row r="166">
       <c r="A166" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 48%</t>
+          <t>Выпечка_ · маржа 49%</t>
         </is>
       </c>
       <c r="B166" s="29" t="inlineStr">
@@ -5917,7 +5917,7 @@
     <row r="214">
       <c r="A214" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 42%</t>
+          <t>Горячее · маржа 59%</t>
         </is>
       </c>
       <c r="B214" s="29" t="inlineStr">
@@ -6133,7 +6133,7 @@
     <row r="262">
       <c r="A262" s="31" t="inlineStr">
         <is>
-          <t>Завтраки · маржа 49%</t>
+          <t>Завтраки · маржа 50%</t>
         </is>
       </c>
       <c r="B262" s="29" t="inlineStr">
@@ -6277,7 +6277,7 @@
     <row r="294">
       <c r="A294" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 61%</t>
+          <t>Выпечка_ · маржа 62%</t>
         </is>
       </c>
       <c r="B294" s="29" t="inlineStr">
@@ -6410,7 +6410,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 07.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 08.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3430,7 +3430,7 @@
         <v>8</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>0.5379999999999999</v>
+        <v>0.543</v>
       </c>
       <c r="J10" s="11" t="n">
         <v>0.2044411292173514</v>
@@ -3508,7 +3508,7 @@
         <v>8</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>0.468</v>
+        <v>0.473</v>
       </c>
       <c r="J11" s="17" t="n">
         <v>0.05843357025697093</v>
@@ -3820,7 +3820,7 @@
         <v>8</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>0.578</v>
+        <v>0.5820000000000001</v>
       </c>
       <c r="J15" s="17" t="n">
         <v>0.1776268395595348</v>
@@ -3898,7 +3898,7 @@
         <v>8</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>0.583</v>
+        <v>0.5860000000000001</v>
       </c>
       <c r="J16" s="11" t="n">
         <v>0.1870989530563998</v>
@@ -4444,7 +4444,7 @@
         <v>8</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>0.369</v>
+        <v>0.373</v>
       </c>
       <c r="J23" s="17" t="n">
         <v>0.3294866693195387</v>
@@ -4522,7 +4522,7 @@
         <v>8</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>0.498</v>
+        <v>0.503</v>
       </c>
       <c r="J24" s="11" t="n">
         <v>0.06297638385605397</v>
@@ -5557,7 +5557,7 @@
     <row r="134">
       <c r="A134" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 58%</t>
+          <t>Горячее · маржа 59%</t>
         </is>
       </c>
       <c r="B134" s="29" t="inlineStr">

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3586,7 +3586,7 @@
         <v>8</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>0.4993415926155573</v>
+        <v>0.4996376594873474</v>
       </c>
       <c r="J12" s="11" t="n">
         <v>0.4364613880742911</v>
@@ -3664,7 +3664,7 @@
         <v>8</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>0.5449999999999999</v>
+        <v>0.546</v>
       </c>
       <c r="J13" s="17" t="n">
         <v>0.2232582821620803</v>
@@ -3742,7 +3742,7 @@
         <v>8</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>0.4970000000000001</v>
+        <v>0.498</v>
       </c>
       <c r="J14" s="11" t="n">
         <v>0.1162887745166225</v>
@@ -3820,7 +3820,7 @@
         <v>8</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>0.5820000000000001</v>
+        <v>0.583</v>
       </c>
       <c r="J15" s="17" t="n">
         <v>0.1776268395595348</v>
@@ -3898,7 +3898,7 @@
         <v>8</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>0.5860000000000001</v>
+        <v>0.589</v>
       </c>
       <c r="J16" s="11" t="n">
         <v>0.1870989530563998</v>
@@ -3976,7 +3976,7 @@
         <v>7</v>
       </c>
       <c r="I17" s="17" t="n">
-        <v>0.603106100043209</v>
+        <v>0.6057729910860503</v>
       </c>
       <c r="J17" s="17" t="n">
         <v>0.7662152530292229</v>
@@ -4210,7 +4210,7 @@
         <v>8</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>0.6231500656440829</v>
+        <v>0.623596859674287</v>
       </c>
       <c r="J20" s="11" t="n">
         <v>0.6239255014326648</v>
@@ -5341,7 +5341,7 @@
     <row r="86">
       <c r="A86" s="31" t="inlineStr">
         <is>
-          <t>Япония · маржа 54%</t>
+          <t>Япония · маржа 55%</t>
         </is>
       </c>
       <c r="B86" s="29" t="inlineStr">
@@ -5629,7 +5629,7 @@
     <row r="150">
       <c r="A150" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 60%</t>
+          <t>Выпечка_ · маржа 61%</t>
         </is>
       </c>
       <c r="B150" s="29" t="inlineStr">

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -4522,7 +4522,7 @@
         <v>8</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>0.503</v>
+        <v>0.5529999999999999</v>
       </c>
       <c r="J24" s="11" t="n">
         <v>0.06297638385605397</v>
@@ -6133,7 +6133,7 @@
     <row r="262">
       <c r="A262" s="31" t="inlineStr">
         <is>
-          <t>Завтраки · маржа 50%</t>
+          <t>Завтраки · маржа 55%</t>
         </is>
       </c>
       <c r="B262" s="29" t="inlineStr">

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3820,7 +3820,7 @@
         <v>8</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>0.583</v>
+        <v>0.584</v>
       </c>
       <c r="J15" s="17" t="n">
         <v>0.1776268395595348</v>
@@ -4444,7 +4444,7 @@
         <v>8</v>
       </c>
       <c r="I23" s="17" t="n">
-        <v>0.373</v>
+        <v>0.374</v>
       </c>
       <c r="J23" s="17" t="n">
         <v>0.3294866693195387</v>
@@ -4522,7 +4522,7 @@
         <v>8</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>0.5529999999999999</v>
+        <v>0.5539999999999999</v>
       </c>
       <c r="J24" s="11" t="n">
         <v>0.06297638385605397</v>
@@ -4756,7 +4756,7 @@
         <v>8</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>0.61</v>
+        <v>0.609</v>
       </c>
       <c r="J27" s="17" t="n">
         <v>0.3193104863533758</v>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3274,7 +3274,7 @@
         <v>6</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.5255578002244669</v>
+        <v>0.5380549080549081</v>
       </c>
       <c r="J8" s="11" t="n">
         <v>0.6096274315858885</v>
@@ -3664,7 +3664,7 @@
         <v>8</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>0.546</v>
+        <v>0.547</v>
       </c>
       <c r="J13" s="17" t="n">
         <v>0.2232582821620803</v>
@@ -3742,7 +3742,7 @@
         <v>8</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>0.498</v>
+        <v>0.5</v>
       </c>
       <c r="J14" s="11" t="n">
         <v>0.1162887745166225</v>
@@ -4981,7 +4981,7 @@
     <row r="6">
       <c r="A6" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 53%</t>
+          <t>Выпечка_ · маржа 54%</t>
         </is>
       </c>
       <c r="B6" s="29" t="inlineStr">

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3274,7 +3274,7 @@
         <v>6</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.5380549080549081</v>
+        <v>0.5336184926184926</v>
       </c>
       <c r="J8" s="11" t="n">
         <v>0.6096274315858885</v>
@@ -3352,7 +3352,7 @@
         <v>8</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>0.5972994503942594</v>
+        <v>0.5936395603154074</v>
       </c>
       <c r="J9" s="17" t="n">
         <v>0.402183406113537</v>
@@ -4288,7 +4288,7 @@
         <v>8</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>0.5929999999999999</v>
+        <v>0.5940000000000001</v>
       </c>
       <c r="J21" s="17" t="n">
         <v>-0.007476993865030646</v>
@@ -4981,7 +4981,7 @@
     <row r="6">
       <c r="A6" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 54%</t>
+          <t>Выпечка_ · маржа 53%</t>
         </is>
       </c>
       <c r="B6" s="29" t="inlineStr">
@@ -5053,7 +5053,7 @@
     <row r="22">
       <c r="A22" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 60%</t>
+          <t>Выпечка_ · маржа 59%</t>
         </is>
       </c>
       <c r="B22" s="29" t="inlineStr">

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 08.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 09.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -3259,13 +3259,13 @@
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>11467170</v>
+        <v>11469333</v>
       </c>
       <c r="E8" s="10" t="n">
         <v>1627</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>7047</v>
+        <v>7048</v>
       </c>
       <c r="G8" s="11" t="n">
         <v>-0.005144146725738707</v>
@@ -3274,7 +3274,7 @@
         <v>6</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.5336184926184926</v>
+        <v>0.5378678260869565</v>
       </c>
       <c r="J8" s="11" t="n">
         <v>0.6096274315858885</v>
@@ -3337,13 +3337,13 @@
         </is>
       </c>
       <c r="D9" s="16" t="n">
-        <v>10019546</v>
+        <v>10024686</v>
       </c>
       <c r="E9" s="16" t="n">
         <v>1070</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>9361</v>
+        <v>9366</v>
       </c>
       <c r="G9" s="17" t="n">
         <v>0.01606738290323895</v>
@@ -3352,7 +3352,7 @@
         <v>8</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>0.5936395603154074</v>
+        <v>0.5939786552575863</v>
       </c>
       <c r="J9" s="17" t="n">
         <v>0.402183406113537</v>
@@ -3508,7 +3508,7 @@
         <v>8</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>0.473</v>
+        <v>0.476</v>
       </c>
       <c r="J11" s="17" t="n">
         <v>0.05843357025697093</v>
@@ -3571,31 +3571,31 @@
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>5160362</v>
+        <v>5162738</v>
       </c>
       <c r="E12" s="10" t="n">
         <v>980</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>5267</v>
+        <v>5270</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.004644817839810855</v>
+        <v>0.006092178303630735</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>0.4996376594873474</v>
+        <v>0.4996263207219167</v>
       </c>
       <c r="J12" s="11" t="n">
         <v>0.4364613880742911</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="M12" s="10">
         <f>ROUND(F12*(1+L12),0)</f>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="S12" s="14" t="inlineStr">
         <is>
-          <t>за 8 мес цена выросла на 0.5% при ориентире 5.3%; берут на 44% больше</t>
+          <t>за 8 мес цена выросла на 0.6% при ориентире 5.3%; берут на 44% больше</t>
         </is>
       </c>
       <c r="T12" s="14" t="inlineStr">
@@ -3664,7 +3664,7 @@
         <v>8</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>0.547</v>
+        <v>0.546</v>
       </c>
       <c r="J13" s="17" t="n">
         <v>0.2232582821620803</v>
@@ -3742,7 +3742,7 @@
         <v>8</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>0.5</v>
+        <v>0.499</v>
       </c>
       <c r="J14" s="11" t="n">
         <v>0.1162887745166225</v>
@@ -3961,22 +3961,22 @@
         </is>
       </c>
       <c r="D17" s="16" t="n">
-        <v>3780853</v>
+        <v>3782740</v>
       </c>
       <c r="E17" s="16" t="n">
         <v>826</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>4577</v>
+        <v>4580</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>0.07254732484211801</v>
+        <v>0.0742387783059526</v>
       </c>
       <c r="H17" s="18" t="n">
         <v>7</v>
       </c>
       <c r="I17" s="17" t="n">
-        <v>0.6057729910860503</v>
+        <v>0.6059708470579527</v>
       </c>
       <c r="J17" s="17" t="n">
         <v>0.7662152530292229</v>
@@ -4195,13 +4195,13 @@
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>3210495</v>
+        <v>3212485</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>756</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>4249</v>
+        <v>4251</v>
       </c>
       <c r="G20" s="11" t="n">
         <v>-0.01425098681656201</v>
@@ -4210,7 +4210,7 @@
         <v>8</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>0.623596859674287</v>
+        <v>0.6235704727025962</v>
       </c>
       <c r="J20" s="11" t="n">
         <v>0.6239255014326648</v>
@@ -4678,7 +4678,7 @@
         <v>8</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>0.615</v>
+        <v>0.616</v>
       </c>
       <c r="J26" s="11" t="n">
         <v>0.6176470588235294</v>
@@ -4756,7 +4756,7 @@
         <v>8</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>0.609</v>
+        <v>0.61</v>
       </c>
       <c r="J27" s="17" t="n">
         <v>0.3193104863533758</v>
@@ -4975,13 +4975,13 @@
         <v>7123</v>
       </c>
       <c r="J5" s="30" t="n">
-        <v>7010</v>
+        <v>7012</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 53%</t>
+          <t>Выпечка_ · маржа 54%</t>
         </is>
       </c>
       <c r="B6" s="29" t="inlineStr">
@@ -5047,7 +5047,7 @@
         <v>9358</v>
       </c>
       <c r="J21" s="30" t="n">
-        <v>9377</v>
+        <v>9393</v>
       </c>
     </row>
     <row r="22">
@@ -5197,7 +5197,7 @@
     <row r="54">
       <c r="A54" s="31" t="inlineStr">
         <is>
-          <t>Горячее · маржа 47%</t>
+          <t>Горячее · маржа 48%</t>
         </is>
       </c>
       <c r="B54" s="29" t="inlineStr">
@@ -5263,7 +5263,7 @@
         <v>5294</v>
       </c>
       <c r="J69" s="30" t="n">
-        <v>5280</v>
+        <v>5288</v>
       </c>
     </row>
     <row r="70">
@@ -5623,7 +5623,7 @@
         <v>4801</v>
       </c>
       <c r="J149" s="30" t="n">
-        <v>4748</v>
+        <v>4756</v>
       </c>
     </row>
     <row r="150">
@@ -5839,7 +5839,7 @@
         <v>4647</v>
       </c>
       <c r="J197" s="30" t="n">
-        <v>4723</v>
+        <v>4731</v>
       </c>
     </row>
     <row r="198">
@@ -6410,7 +6410,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 08.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 09.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3274,7 +3274,7 @@
         <v>6</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.5378678260869565</v>
+        <v>0.53968</v>
       </c>
       <c r="J8" s="11" t="n">
         <v>0.6096274315858885</v>
@@ -3352,7 +3352,7 @@
         <v>8</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>0.5939786552575863</v>
+        <v>0.594638207010115</v>
       </c>
       <c r="J9" s="17" t="n">
         <v>0.402183406113537</v>
@@ -3586,7 +3586,7 @@
         <v>8</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>0.4996263207219167</v>
+        <v>0.4993299298854</v>
       </c>
       <c r="J12" s="11" t="n">
         <v>0.4364613880742911</v>
@@ -3976,7 +3976,7 @@
         <v>7</v>
       </c>
       <c r="I17" s="17" t="n">
-        <v>0.6059708470579527</v>
+        <v>0.6057481620906185</v>
       </c>
       <c r="J17" s="17" t="n">
         <v>0.7662152530292229</v>
@@ -4132,7 +4132,7 @@
         <v>8</v>
       </c>
       <c r="I19" s="17" t="n">
-        <v>0.5866715825776244</v>
+        <v>0.5883854469281138</v>
       </c>
       <c r="J19" s="17" t="n">
         <v>0.4262948207171313</v>
@@ -4210,7 +4210,7 @@
         <v>8</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>0.6235704727025962</v>
+        <v>0.6236761992663001</v>
       </c>
       <c r="J20" s="11" t="n">
         <v>0.6239255014326648</v>
@@ -4366,7 +4366,7 @@
         <v>8</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>0.6114207541206009</v>
+        <v>0.6284698035678137</v>
       </c>
       <c r="J22" s="11" t="n">
         <v>0.5880829015544042</v>
@@ -4756,7 +4756,7 @@
         <v>8</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>0.61</v>
+        <v>0.6110000000000001</v>
       </c>
       <c r="J27" s="17" t="n">
         <v>0.3193104863533758</v>
@@ -5989,7 +5989,7 @@
     <row r="230">
       <c r="A230" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 61%</t>
+          <t>Выпечка_ · маржа 63%</t>
         </is>
       </c>
       <c r="B230" s="29" t="inlineStr">

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -4054,7 +4054,7 @@
         <v>8</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>0.4872048688463061</v>
+        <v>0.4833073032694593</v>
       </c>
       <c r="J18" s="11" t="n">
         <v>0.130570758405004</v>
@@ -5701,7 +5701,7 @@
     <row r="166">
       <c r="A166" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 49%</t>
+          <t>Выпечка_ · маржа 48%</t>
         </is>
       </c>
       <c r="B166" s="29" t="inlineStr">

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -4054,7 +4054,7 @@
         <v>8</v>
       </c>
       <c r="I18" s="11" t="n">
-        <v>0.4833073032694593</v>
+        <v>0.4937349562821021</v>
       </c>
       <c r="J18" s="11" t="n">
         <v>0.130570758405004</v>
@@ -5701,7 +5701,7 @@
     <row r="166">
       <c r="A166" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 48%</t>
+          <t>Выпечка_ · маржа 49%</t>
         </is>
       </c>
       <c r="B166" s="29" t="inlineStr">

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3820,7 +3820,7 @@
         <v>8</v>
       </c>
       <c r="I15" s="17" t="n">
-        <v>0.584</v>
+        <v>0.583</v>
       </c>
       <c r="J15" s="17" t="n">
         <v>0.1776268395595348</v>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -4210,7 +4210,7 @@
         <v>8</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>0.6236761992663001</v>
+        <v>0.6222290625481519</v>
       </c>
       <c r="J20" s="11" t="n">
         <v>0.6239255014326648</v>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 09.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 10.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3976,7 @@
         <v>7</v>
       </c>
       <c r="I17" s="17" t="n">
-        <v>0.6057481620906185</v>
+        <v>0.6046347372539482</v>
       </c>
       <c r="J17" s="17" t="n">
         <v>0.7662152530292229</v>
@@ -4210,7 +4210,7 @@
         <v>8</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>0.6222290625481519</v>
+        <v>0.6255704727025964</v>
       </c>
       <c r="J20" s="11" t="n">
         <v>0.6239255014326648</v>
@@ -4522,7 +4522,7 @@
         <v>8</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>0.5539999999999999</v>
+        <v>0.555</v>
       </c>
       <c r="J24" s="11" t="n">
         <v>0.06297638385605397</v>
@@ -5629,7 +5629,7 @@
     <row r="150">
       <c r="A150" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 61%</t>
+          <t>Выпечка_ · маржа 60%</t>
         </is>
       </c>
       <c r="B150" s="29" t="inlineStr">
@@ -5845,7 +5845,7 @@
     <row r="198">
       <c r="A198" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 62%</t>
+          <t>Выпечка_ · маржа 63%</t>
         </is>
       </c>
       <c r="B198" s="29" t="inlineStr">
@@ -6133,7 +6133,7 @@
     <row r="262">
       <c r="A262" s="31" t="inlineStr">
         <is>
-          <t>Завтраки · маржа 55%</t>
+          <t>Завтраки · маржа 56%</t>
         </is>
       </c>
       <c r="B262" s="29" t="inlineStr">
@@ -6410,7 +6410,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 09.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 10.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -6533,7 +6533,7 @@
     <row r="24">
       <c r="A24" s="31" t="inlineStr">
         <is>
-          <t>Система «Пульс» · Фуд Завод · Ольга Герасименко, финансовый директор</t>
+          <t>Система «Пульс» · Фуд Завод · Фуд Завод</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3742,7 +3742,7 @@
         <v>8</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>0.499</v>
+        <v>0.498</v>
       </c>
       <c r="J14" s="11" t="n">
         <v>0.1162887745166225</v>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 10.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 11.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
         <v>8</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>0.594638207010115</v>
+        <v>0.5969786552575863</v>
       </c>
       <c r="J9" s="17" t="n">
         <v>0.402183406113537</v>
@@ -5053,7 +5053,7 @@
     <row r="22">
       <c r="A22" s="31" t="inlineStr">
         <is>
-          <t>Выпечка_ · маржа 59%</t>
+          <t>Выпечка_ · маржа 60%</t>
         </is>
       </c>
       <c r="B22" s="29" t="inlineStr">
@@ -6410,7 +6410,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 10.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 11.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 11.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 12.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 11.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 12.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>

--- a/план_повышения_цен.xlsx
+++ b/план_повышения_цен.xlsx
@@ -3106,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Собрано 12.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
+          <t>Собрано 13.09.2026 из данных iiko. Меняйте процент в жёлтой колонке — всё пересчитается.</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="34" t="inlineStr">
         <is>
-          <t>Собрано 12.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
+          <t>Собрано 13.09.2026 из выгрузки iiko. В расчёт идут только закрытые месяцы: в текущем себестоимость ещё не разнесена, и маржа по нему завышена.</t>
         </is>
       </c>
     </row>
